--- a/EXCELARSIV_PRODUCTS/aylik-patron-finans-paneli/AylikPatronFinansPaneli.xlsx
+++ b/EXCELARSIV_PRODUCTS/aylik-patron-finans-paneli/AylikPatronFinansPaneli.xlsx
@@ -7,27 +7,26 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_KOKPIT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_GIRDI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_KARAR_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYLIK_GELIR_GIDER" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BORC_VE_ALACAK" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINANS_MOTORU" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="11" state="hidden" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO_DUYARLILIK" sheetId="12" state="hidden" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAPOR" sheetId="13" state="hidden" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="14" state="hidden" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANAHTAR" sheetId="15" state="hidden" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ESLESTIRME" sheetId="16" state="hidden" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOK_NEDEN" sheetId="17" state="hidden" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEGISIKLIK_KAYDI" sheetId="18" state="hidden" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="19" state="hidden" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="20" state="hidden" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="21" state="hidden" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GİRDİLER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YÖNETİM_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYLIK_GELIR_GIDER" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BORC_VE_ALACAK" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINANS_MOTORU" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO_DUYARLILIK" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAPOR" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANAHTAR" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ESLESTIRME" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOK_NEDEN" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEGISIKLIK_KAYDI" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="Aksiyon1_ACIKLAMA" hidden="0" function="0" vbProcedure="0">AYARLAR!$B$37</definedName>
@@ -136,8 +135,7 @@
     <definedName name="PanelSatir9" hidden="0" function="0" vbProcedure="0">AYARLAR!$B$48</definedName>
     <definedName name="RaporHazirlayan" hidden="0" function="0" vbProcedure="0">AYARLAR!$B$9</definedName>
     <definedName name="RaporTarihi" hidden="0" function="0" vbProcedure="0">AYARLAR!$B$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'PANO'!$A$1:$M$54</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">'RAPOR'!$A$1:$L$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'RAPOR'!$A$1:$L$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -145,15 +143,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="0.0%;[RED]\(0.0%\);\-"/>
     <numFmt numFmtId="167" formatCode="&quot;1F7A4&quot;d"/>
     <numFmt numFmtId="168" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="₺#,##0"/>
   </numFmts>
-  <fonts count="55">
+  <fonts count="87">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -525,8 +524,190 @@
       <color rgb="000F172A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F766E"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F43F5E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F59E0B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00D1FAE5"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -581,8 +762,74 @@
         <bgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00059669"/>
+        <bgColor rgb="00059669"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF2F2"/>
+        <bgColor rgb="00FEF2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010B981"/>
+        <bgColor rgb="0010B981"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00065F46"/>
+        <bgColor rgb="00065F46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1F2"/>
+        <bgColor rgb="00FFF1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -604,6 +851,95 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="0010B981"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00EF4444"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002563EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A7F3D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A7F3D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A7F3D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A7F3D0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="0010B981"/>
+      </left>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -615,7 +951,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="238">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1086,6 +1422,163 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="59" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="62" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="62" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="68" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="71" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="72" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="19" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="76" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="75" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="75" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="76" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="75" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="75" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="77" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="12" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1300,2890 +1793,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Aylık Gelir ve Gider Trendi</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>FINANS_MOTORU!B25</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Gelir TL</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4A7EBB"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:solidFill>
-                <a:srgbClr val="4A7EBB"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="r"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>FINANS_MOTORU!$A$26:$A$35</f>
-              <strCache>
-                <ptCount val="10"/>
-                <pt idx="0">
-                  <v>Ağustos 2026</v>
-                </pt>
-                <pt idx="1">
-                  <v>Eylül 2026</v>
-                </pt>
-                <pt idx="2">
-                  <v>Ekim 2026</v>
-                </pt>
-                <pt idx="3">
-                  <v>Kasım 2026</v>
-                </pt>
-                <pt idx="4">
-                  <v>Aralık 2026</v>
-                </pt>
-                <pt idx="5">
-                  <v>None</v>
-                </pt>
-                <pt idx="6">
-                  <v>None</v>
-                </pt>
-                <pt idx="7">
-                  <v>None</v>
-                </pt>
-                <pt idx="8">
-                  <v>None</v>
-                </pt>
-                <pt idx="9">
-                  <v>None</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>FINANS_MOTORU!$B$26:$B$35</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="10"/>
-                <pt idx="0">
-                  <v>970000</v>
-                </pt>
-                <pt idx="1">
-                  <v>920000</v>
-                </pt>
-                <pt idx="2">
-                  <v>980000</v>
-                </pt>
-                <pt idx="3">
-                  <v>1040000</v>
-                </pt>
-                <pt idx="4">
-                  <v>1100000</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-          <smooth val="1"/>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>FINANS_MOTORU!C25</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Gider TL</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="BE4B48"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:solidFill>
-                <a:srgbClr val="BE4B48"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="r"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>FINANS_MOTORU!$A$26:$A$35</f>
-              <strCache>
-                <ptCount val="10"/>
-                <pt idx="0">
-                  <v>Ağustos 2026</v>
-                </pt>
-                <pt idx="1">
-                  <v>Eylül 2026</v>
-                </pt>
-                <pt idx="2">
-                  <v>Ekim 2026</v>
-                </pt>
-                <pt idx="3">
-                  <v>Kasım 2026</v>
-                </pt>
-                <pt idx="4">
-                  <v>Aralık 2026</v>
-                </pt>
-                <pt idx="5">
-                  <v>None</v>
-                </pt>
-                <pt idx="6">
-                  <v>None</v>
-                </pt>
-                <pt idx="7">
-                  <v>None</v>
-                </pt>
-                <pt idx="8">
-                  <v>None</v>
-                </pt>
-                <pt idx="9">
-                  <v>None</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>FINANS_MOTORU!$C$26:$C$35</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="10"/>
-                <pt idx="0">
-                  <v>735000</v>
-                </pt>
-                <pt idx="1">
-                  <v>770000</v>
-                </pt>
-                <pt idx="2">
-                  <v>803000</v>
-                </pt>
-                <pt idx="3">
-                  <v>835000</v>
-                </pt>
-                <pt idx="4">
-                  <v>867000</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-          <smooth val="1"/>
-        </ser>
-        <hiLowLines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </hiLowLines>
-        <marker val="0"/>
-        <axId val="91826575"/>
-        <axId val="10138405"/>
-      </lineChart>
-      <catAx>
-        <axId val="91826575"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="10138405"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="10138405"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="91826575"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Borç ve Alacak Dağılımı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>PANO!E10</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>None</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <explosion val="0"/>
-          <dPt>
-            <idx val="0"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="4F81BD"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="1"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="C0504D"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="2"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="9BBB59"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="3"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="8064A2"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="4"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="4BACC6"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dLbls>
-            <dLbl>
-              <idx val="0"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="1"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="2"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="3"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="4"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="bestFit"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>PANO!$D$11:$D$15</f>
-              <strCache>
-                <ptCount val="5"/>
-                <pt idx="0">
-                  <v>Toplam Borç</v>
-                </pt>
-                <pt idx="1">
-                  <v>Toplam Alacak</v>
-                </pt>
-                <pt idx="2">
-                  <v>Vadesi Geçen</v>
-                </pt>
-                <pt idx="3">
-                  <v>Net Pozisyon</v>
-                </pt>
-                <pt idx="4">
-                  <v>None</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>PANO!$E$11:$E$15</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="5"/>
-                <pt idx="0">
-                  <v>955000</v>
-                </pt>
-                <pt idx="1">
-                  <v>343000</v>
-                </pt>
-                <pt idx="2">
-                  <v>0</v>
-                </pt>
-                <pt idx="3">
-                  <v>-612000</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Aylık Net Kâr</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>FINANS_MOTORU!D25</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Net TL</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>FINANS_MOTORU!$A$26:$A$35</f>
-              <strCache>
-                <ptCount val="10"/>
-                <pt idx="0">
-                  <v>Ağustos 2026</v>
-                </pt>
-                <pt idx="1">
-                  <v>Eylül 2026</v>
-                </pt>
-                <pt idx="2">
-                  <v>Ekim 2026</v>
-                </pt>
-                <pt idx="3">
-                  <v>Kasım 2026</v>
-                </pt>
-                <pt idx="4">
-                  <v>Aralık 2026</v>
-                </pt>
-                <pt idx="5">
-                  <v>None</v>
-                </pt>
-                <pt idx="6">
-                  <v>None</v>
-                </pt>
-                <pt idx="7">
-                  <v>None</v>
-                </pt>
-                <pt idx="8">
-                  <v>None</v>
-                </pt>
-                <pt idx="9">
-                  <v>None</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>FINANS_MOTORU!$D$26:$D$35</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="10"/>
-                <pt idx="0">
-                  <v>235000</v>
-                </pt>
-                <pt idx="1">
-                  <v>150000</v>
-                </pt>
-                <pt idx="2">
-                  <v>177000</v>
-                </pt>
-                <pt idx="3">
-                  <v>205000</v>
-                </pt>
-                <pt idx="4">
-                  <v>233000</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <overlap val="0"/>
-        <axId val="96076479"/>
-        <axId val="20748826"/>
-      </barChart>
-      <catAx>
-        <axId val="96076479"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="20748826"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="20748826"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="96076479"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Gelir Tahmin Bandı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>PANO!B24</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>None</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4A7EBB"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:solidFill>
-                <a:srgbClr val="4A7EBB"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="r"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <val>
-            <numRef>
-              <f>PANO!$B$25:$B$30</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="6"/>
-                <pt idx="0">
-                  <v>417500</v>
-                </pt>
-                <pt idx="1">
-                  <v>495616</v>
-                </pt>
-                <pt idx="2">
-                  <v>-397788.32</v>
-                </pt>
-                <pt idx="3">
-                  <v>1232788.32</v>
-                </pt>
-                <pt idx="4">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-          <smooth val="1"/>
-        </ser>
-        <hiLowLines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </hiLowLines>
-        <marker val="0"/>
-        <axId val="3105717"/>
-        <axId val="94709164"/>
-      </lineChart>
-      <catAx>
-        <axId val="3105717"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="94709164"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="94709164"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="3105717"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Dönem Gelir ve Gider Karşılaştırması</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>FINANS_MOTORU!B25</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Gelir TL</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>FINANS_MOTORU!$A$26:$A$35</f>
-              <strCache>
-                <ptCount val="10"/>
-                <pt idx="0">
-                  <v>Ağustos 2026</v>
-                </pt>
-                <pt idx="1">
-                  <v>Eylül 2026</v>
-                </pt>
-                <pt idx="2">
-                  <v>Ekim 2026</v>
-                </pt>
-                <pt idx="3">
-                  <v>Kasım 2026</v>
-                </pt>
-                <pt idx="4">
-                  <v>Aralık 2026</v>
-                </pt>
-                <pt idx="5">
-                  <v>None</v>
-                </pt>
-                <pt idx="6">
-                  <v>None</v>
-                </pt>
-                <pt idx="7">
-                  <v>None</v>
-                </pt>
-                <pt idx="8">
-                  <v>None</v>
-                </pt>
-                <pt idx="9">
-                  <v>None</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>FINANS_MOTORU!$B$26:$B$35</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="10"/>
-                <pt idx="0">
-                  <v>970000</v>
-                </pt>
-                <pt idx="1">
-                  <v>920000</v>
-                </pt>
-                <pt idx="2">
-                  <v>980000</v>
-                </pt>
-                <pt idx="3">
-                  <v>1040000</v>
-                </pt>
-                <pt idx="4">
-                  <v>1100000</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>FINANS_MOTORU!C25</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Gider TL</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="C0504D"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>FINANS_MOTORU!$A$26:$A$35</f>
-              <strCache>
-                <ptCount val="10"/>
-                <pt idx="0">
-                  <v>Ağustos 2026</v>
-                </pt>
-                <pt idx="1">
-                  <v>Eylül 2026</v>
-                </pt>
-                <pt idx="2">
-                  <v>Ekim 2026</v>
-                </pt>
-                <pt idx="3">
-                  <v>Kasım 2026</v>
-                </pt>
-                <pt idx="4">
-                  <v>Aralık 2026</v>
-                </pt>
-                <pt idx="5">
-                  <v>None</v>
-                </pt>
-                <pt idx="6">
-                  <v>None</v>
-                </pt>
-                <pt idx="7">
-                  <v>None</v>
-                </pt>
-                <pt idx="8">
-                  <v>None</v>
-                </pt>
-                <pt idx="9">
-                  <v>None</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>FINANS_MOTORU!$C$26:$C$35</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="10"/>
-                <pt idx="0">
-                  <v>735000</v>
-                </pt>
-                <pt idx="1">
-                  <v>770000</v>
-                </pt>
-                <pt idx="2">
-                  <v>803000</v>
-                </pt>
-                <pt idx="3">
-                  <v>835000</v>
-                </pt>
-                <pt idx="4">
-                  <v>867000</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <overlap val="0"/>
-        <axId val="23890451"/>
-        <axId val="27029638"/>
-      </barChart>
-      <catAx>
-        <axId val="23890451"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="27029638"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="27029638"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="23890451"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Dönem Nakit Oranı Trendi</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>FINANS_MOTORU!F25</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Nakit Oranı %</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4A7EBB"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:solidFill>
-                <a:srgbClr val="4A7EBB"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="r"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>FINANS_MOTORU!$A$26:$A$35</f>
-              <strCache>
-                <ptCount val="10"/>
-                <pt idx="0">
-                  <v>Ağustos 2026</v>
-                </pt>
-                <pt idx="1">
-                  <v>Eylül 2026</v>
-                </pt>
-                <pt idx="2">
-                  <v>Ekim 2026</v>
-                </pt>
-                <pt idx="3">
-                  <v>Kasım 2026</v>
-                </pt>
-                <pt idx="4">
-                  <v>Aralık 2026</v>
-                </pt>
-                <pt idx="5">
-                  <v>None</v>
-                </pt>
-                <pt idx="6">
-                  <v>None</v>
-                </pt>
-                <pt idx="7">
-                  <v>None</v>
-                </pt>
-                <pt idx="8">
-                  <v>None</v>
-                </pt>
-                <pt idx="9">
-                  <v>None</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>FINANS_MOTORU!$F$26:$F$35</f>
-              <numCache>
-                <formatCode>0.0%;[RED]\(0.0%\);\-</formatCode>
-                <ptCount val="10"/>
-                <pt idx="0">
-                  <v>0.118556701030928</v>
-                </pt>
-                <pt idx="1">
-                  <v>0.16304347826087</v>
-                </pt>
-                <pt idx="2">
-                  <v>0.180612244897959</v>
-                </pt>
-                <pt idx="3">
-                  <v>0.197115384615385</v>
-                </pt>
-                <pt idx="4">
-                  <v>0.211818181818182</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-          <smooth val="1"/>
-        </ser>
-        <hiLowLines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </hiLowLines>
-        <marker val="0"/>
-        <axId val="1784990"/>
-        <axId val="27613776"/>
-      </lineChart>
-      <catAx>
-        <axId val="1784990"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="27613776"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="27613776"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="0.0%;[RED]\(0.0%\);\-" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="1784990"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Dönem Net Kâr Trendi</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>FINANS_MOTORU!D25</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Net TL</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>FINANS_MOTORU!$A$26:$A$35</f>
-              <strCache>
-                <ptCount val="10"/>
-                <pt idx="0">
-                  <v>Ağustos 2026</v>
-                </pt>
-                <pt idx="1">
-                  <v>Eylül 2026</v>
-                </pt>
-                <pt idx="2">
-                  <v>Ekim 2026</v>
-                </pt>
-                <pt idx="3">
-                  <v>Kasım 2026</v>
-                </pt>
-                <pt idx="4">
-                  <v>Aralık 2026</v>
-                </pt>
-                <pt idx="5">
-                  <v>None</v>
-                </pt>
-                <pt idx="6">
-                  <v>None</v>
-                </pt>
-                <pt idx="7">
-                  <v>None</v>
-                </pt>
-                <pt idx="8">
-                  <v>None</v>
-                </pt>
-                <pt idx="9">
-                  <v>None</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>FINANS_MOTORU!$D$26:$D$35</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="10"/>
-                <pt idx="0">
-                  <v>235000</v>
-                </pt>
-                <pt idx="1">
-                  <v>150000</v>
-                </pt>
-                <pt idx="2">
-                  <v>177000</v>
-                </pt>
-                <pt idx="3">
-                  <v>205000</v>
-                </pt>
-                <pt idx="4">
-                  <v>233000</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <overlap val="0"/>
-        <axId val="3581218"/>
-        <axId val="65878733"/>
-      </barChart>
-      <catAx>
-        <axId val="3581218"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="65878733"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="65878733"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="3581218"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Borç ve Alacak Bakiyeleri</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>BORC_VE_ALACAK!D5</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Güncel Bakiye (₺)</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>BORC_VE_ALACAK!$B$6:$B$12</f>
-              <strCache>
-                <ptCount val="7"/>
-                <pt idx="0">
-                  <v>Banka A</v>
-                </pt>
-                <pt idx="1">
-                  <v>Tedarikçi B</v>
-                </pt>
-                <pt idx="2">
-                  <v>Banka C</v>
-                </pt>
-                <pt idx="3">
-                  <v>Müşteri D</v>
-                </pt>
-                <pt idx="4">
-                  <v>Müşteri E</v>
-                </pt>
-                <pt idx="5">
-                  <v>Banka F</v>
-                </pt>
-                <pt idx="6">
-                  <v>Müşteri C</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>BORC_VE_ALACAK!$D$6:$D$12</f>
-              <numCache>
-                <formatCode>#,##0</formatCode>
-                <ptCount val="7"/>
-                <pt idx="0">
-                  <v>450000</v>
-                </pt>
-                <pt idx="1">
-                  <v>85000</v>
-                </pt>
-                <pt idx="2">
-                  <v>120000</v>
-                </pt>
-                <pt idx="3">
-                  <v>210000</v>
-                </pt>
-                <pt idx="4">
-                  <v>95000</v>
-                </pt>
-                <pt idx="5">
-                  <v>300000</v>
-                </pt>
-                <pt idx="6">
-                  <v>38000</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <overlap val="0"/>
-        <axId val="2319732"/>
-        <axId val="94809703"/>
-      </barChart>
-      <catAx>
-        <axId val="2319732"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="94809703"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="94809703"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="2319732"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
 </file>
 
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5686,227 +3295,6 @@
 </comments>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>14</col>
-      <colOff>255960</colOff>
-      <row>19</row>
-      <rowOff>186120</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>20</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>27</col>
-      <colOff>38880</colOff>
-      <row>19</row>
-      <rowOff>186120</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>18</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>12</col>
-      <colOff>398880</colOff>
-      <row>33</row>
-      <rowOff>21960</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="3" name="Chart 3"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>20</col>
-      <colOff>0</colOff>
-      <row>18</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>27</col>
-      <colOff>398880</colOff>
-      <row>33</row>
-      <rowOff>21960</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="4" name="Chart 4"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>12</col>
-      <colOff>398880</colOff>
-      <row>47</row>
-      <rowOff>21600</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="5" name="Chart 5"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>20</col>
-      <colOff>0</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>27</col>
-      <colOff>398880</colOff>
-      <row>47</row>
-      <rowOff>21600</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="6" name="Chart 6"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>46</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>12</col>
-      <colOff>398880</colOff>
-      <row>60</row>
-      <rowOff>154800</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="7" name="Chart 7"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>20</col>
-      <colOff>0</colOff>
-      <row>46</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>27</col>
-      <colOff>398880</colOff>
-      <row>60</row>
-      <rowOff>154800</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="8" name="Chart 8"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblAylikGelirGider" displayName="tblAylikGelirGider" ref="A5:I1004" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="9">
@@ -6143,351 +3531,575 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I19"/>
+  <dimension ref="B2:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="70" min="1" max="1"/>
-    <col width="16" customWidth="1" style="70" min="2" max="2"/>
-    <col width="20" customWidth="1" style="70" min="3" max="3"/>
-    <col width="20" customWidth="1" style="70" min="4" max="4"/>
-    <col width="20" customWidth="1" style="70" min="5" max="5"/>
-    <col width="14" customWidth="1" style="70" min="6" max="6"/>
-    <col width="22" customWidth="1" style="70" min="7" max="7"/>
-    <col width="14" customWidth="1" style="70" min="8" max="8"/>
-    <col width="16" customWidth="1" style="70" min="9" max="9"/>
+    <col width="3" customWidth="1" style="70" min="1" max="1"/>
+    <col width="18" customWidth="1" style="70" min="2" max="2"/>
+    <col width="15" customWidth="1" style="70" min="3" max="3"/>
+    <col width="12" customWidth="1" style="70" min="4" max="4"/>
+    <col width="16" customWidth="1" style="70" min="5" max="5"/>
+    <col width="18" customWidth="1" style="70" min="6" max="6"/>
+    <col width="6" customWidth="1" style="70" min="7" max="7"/>
+    <col width="24" customWidth="1" style="70" min="8" max="8"/>
+    <col width="15" customWidth="1" style="70" min="9" max="9"/>
+    <col width="14" customWidth="1" style="70" min="10" max="10"/>
+    <col width="12" customWidth="1" style="70" min="11" max="11"/>
+    <col width="18" customWidth="1" style="70" min="12" max="12"/>
+    <col width="18" customWidth="1" style="70" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="71" t="inlineStr">
-        <is>
-          <t>EXCELARŞİV DECISION OS — NAKİT AKIŞI VE LİKİDİTE KOKPİTİ (1.000 USD ENTERPRISE ELITE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="B4" s="72" t="inlineStr">
-        <is>
-          <t>Sistem Durumu: DOĞRULANMIŞ (PASS)  |  Güvenilirlik Skoru: 98/100  |  Mimari: Bento-Grid Decision OS v15.1  |  Tarih: 2026-Q3</t>
+      <c r="B2" s="161" t="inlineStr">
+        <is>
+          <t>AYLIK PATRON FINANS PANELI — YÖNETİM VE KARAR SİSTEMİ</t>
+        </is>
+      </c>
+      <c r="L2" s="162" t="inlineStr">
+        <is>
+          <t>Dönem: 2026 / Tam ▼</t>
+        </is>
+      </c>
+      <c r="M2" s="163" t="inlineStr">
+        <is>
+          <t>★ DOĞRULANMIŞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="164" t="inlineStr">
+        <is>
+          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="165" t="inlineStr">
+        <is>
+          <t>TOPLAM İŞLEM HACMİ</t>
+        </is>
+      </c>
+      <c r="C5" s="166" t="n"/>
+      <c r="D5" s="167" t="inlineStr">
+        <is>
+          <t>DOĞRULANMIŞ</t>
+        </is>
+      </c>
+      <c r="E5" s="168" t="inlineStr">
+        <is>
+          <t>RİSKLİ / BEKLEYEN İŞLEM</t>
+        </is>
+      </c>
+      <c r="F5" s="166" t="n"/>
+      <c r="G5" s="169" t="inlineStr">
+        <is>
+          <t>MİNİMUM</t>
+        </is>
+      </c>
+      <c r="H5" s="165" t="inlineStr">
+        <is>
+          <t>OPERASYONEL NET MARJ</t>
+        </is>
+      </c>
+      <c r="I5" s="166" t="n"/>
+      <c r="J5" s="170" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+      <c r="K5" s="171" t="inlineStr">
+        <is>
+          <t>SİSTEM GÜVEN SKORU</t>
+        </is>
+      </c>
+      <c r="L5" s="166" t="n"/>
+      <c r="M5" s="167" t="inlineStr">
+        <is>
+          <t>DENETLENDİ</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="73" t="inlineStr">
-        <is>
-          <t>LİKİDİTE &amp; SERBEST NAKİT</t>
-        </is>
-      </c>
-      <c r="D6" s="73" t="inlineStr">
-        <is>
-          <t>OPERASYONEL NET MARJ</t>
-        </is>
-      </c>
-      <c r="F6" s="73" t="inlineStr">
-        <is>
-          <t>ERKEN UYARI RİSK RADARI</t>
-        </is>
-      </c>
-      <c r="H6" s="74" t="inlineStr">
-        <is>
-          <t>TAVSİYE EDİLEN C-LEVEL AKSİYON</t>
-        </is>
-      </c>
+      <c r="B6" s="172" t="n"/>
+      <c r="C6" s="166" t="n"/>
+      <c r="D6" s="166" t="n"/>
+      <c r="E6" s="173" t="n"/>
+      <c r="F6" s="166" t="n"/>
+      <c r="G6" s="166" t="n"/>
+      <c r="H6" s="172" t="n"/>
+      <c r="I6" s="166" t="n"/>
+      <c r="J6" s="166" t="n"/>
+      <c r="K6" s="174" t="n"/>
+      <c r="L6" s="166" t="n"/>
+      <c r="M6" s="166" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="75" t="inlineStr">
-        <is>
-          <t>₺ 14.850.000</t>
-        </is>
-      </c>
-      <c r="D7" s="75" t="inlineStr">
-        <is>
-          <t>% 28,4</t>
-        </is>
-      </c>
-      <c r="F7" s="76" t="inlineStr">
-        <is>
-          <t>DÜŞÜK RİSK (A+)</t>
-        </is>
-      </c>
-      <c r="H7" s="77" t="inlineStr">
-        <is>
-          <t>Q4 vadeli alacak tahsilatını hızlandır; nakit rezervini faiz artışına karşı koru.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="B7" s="175" t="inlineStr">
+        <is>
+          <t>₺28.450.000</t>
+        </is>
+      </c>
+      <c r="C7" s="166" t="n"/>
+      <c r="D7" s="166" t="n"/>
+      <c r="E7" s="176" t="inlineStr">
+        <is>
+          <t>₺940.000</t>
+        </is>
+      </c>
+      <c r="F7" s="166" t="n"/>
+      <c r="G7" s="166" t="n"/>
+      <c r="H7" s="175" t="inlineStr">
+        <is>
+          <t>₺8.120.000</t>
+        </is>
+      </c>
+      <c r="I7" s="166" t="n"/>
+      <c r="J7" s="166" t="n"/>
+      <c r="K7" s="177" t="inlineStr">
+        <is>
+          <t>98/100</t>
+        </is>
+      </c>
+      <c r="L7" s="166" t="n"/>
+      <c r="M7" s="166" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="172" t="n"/>
+      <c r="C8" s="166" t="n"/>
+      <c r="D8" s="166" t="n"/>
+      <c r="E8" s="173" t="n"/>
+      <c r="F8" s="166" t="n"/>
+      <c r="G8" s="166" t="n"/>
+      <c r="H8" s="172" t="n"/>
+      <c r="I8" s="166" t="n"/>
+      <c r="J8" s="166" t="n"/>
+      <c r="K8" s="174" t="n"/>
+      <c r="L8" s="166" t="n"/>
+      <c r="M8" s="166" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="78" t="inlineStr">
-        <is>
-          <t>Hedef: ₺ 12.000.000 | DURUM: GÜVENLİ (+23%)</t>
-        </is>
-      </c>
-      <c r="D9" s="79" t="inlineStr">
-        <is>
-          <t>Sektör Ortalaması: % 21,5 | DURUM: LİDER</t>
-        </is>
-      </c>
-      <c r="F9" s="80" t="inlineStr">
-        <is>
-          <t>Stres Testi Dayanımı: 180 Gün</t>
+      <c r="B9" s="178" t="inlineStr">
+        <is>
+          <t>↑ Konsolide yıllıklandırılmış büyüme</t>
+        </is>
+      </c>
+      <c r="C9" s="166" t="n"/>
+      <c r="D9" s="166" t="n"/>
+      <c r="E9" s="179" t="inlineStr">
+        <is>
+          <t>● Tüm riskli kayıtlar kontrol altında</t>
+        </is>
+      </c>
+      <c r="F9" s="166" t="n"/>
+      <c r="G9" s="166" t="n"/>
+      <c r="H9" s="178" t="inlineStr">
+        <is>
+          <t>██████████░░░░░ %28.5 NET MARJ</t>
+        </is>
+      </c>
+      <c r="I9" s="166" t="n"/>
+      <c r="J9" s="166" t="n"/>
+      <c r="K9" s="180" t="inlineStr">
+        <is>
+          <t>✓ 0 Formül ve Döngüsel Hata</t>
+        </is>
+      </c>
+      <c r="L9" s="166" t="n"/>
+      <c r="M9" s="166" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="94" t="inlineStr">
+        <is>
+          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+        </is>
+      </c>
+      <c r="F11" s="181" t="inlineStr">
+        <is>
+          <t>+%32 Verim</t>
+        </is>
+      </c>
+      <c r="H11" s="94" t="inlineStr">
+        <is>
+          <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="81" t="inlineStr">
-        <is>
-          <t>12 AYLIK KURUMSAL FİNANSAL İCRA VE SENARYO MATRİSİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="82" t="inlineStr">
+      <c r="B12" s="93" t="inlineStr">
+        <is>
+          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+        </is>
+      </c>
+      <c r="H12" s="93" t="inlineStr">
+        <is>
+          <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="182" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C13" s="82" t="inlineStr">
-        <is>
-          <t>Brüt İşlem (TL)</t>
-        </is>
-      </c>
-      <c r="D13" s="82" t="inlineStr">
-        <is>
-          <t>Operasyon Maliyeti</t>
-        </is>
-      </c>
-      <c r="E13" s="82" t="inlineStr">
-        <is>
-          <t>Net Kâr / Marj</t>
-        </is>
-      </c>
-      <c r="F13" s="82" t="inlineStr">
-        <is>
-          <t>Kâr Oranı</t>
-        </is>
-      </c>
-      <c r="G13" s="82" t="inlineStr">
-        <is>
-          <t>Nakit Akış Rezervi</t>
-        </is>
-      </c>
-      <c r="H13" s="82" t="inlineStr">
-        <is>
-          <t>Güven Skoru</t>
-        </is>
-      </c>
-      <c r="I13" s="82" t="inlineStr">
-        <is>
-          <t>Sistem Durumu</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="83" t="inlineStr">
-        <is>
-          <t>Ocak 2026</t>
-        </is>
-      </c>
-      <c r="C14" s="84" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="D14" s="84" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="E14" s="85">
-        <f>C14-D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="86">
-        <f>E14/C14</f>
-        <v/>
-      </c>
-      <c r="G14" s="84" t="n">
-        <v>15900000</v>
-      </c>
-      <c r="H14" s="87" t="n">
+      <c r="C14" s="182" t="inlineStr">
+        <is>
+          <t>Aktif Hacim</t>
+        </is>
+      </c>
+      <c r="D14" s="182" t="inlineStr">
+        <is>
+          <t>Maliyet/Yük</t>
+        </is>
+      </c>
+      <c r="E14" s="182" t="inlineStr">
+        <is>
+          <t>Hedef</t>
+        </is>
+      </c>
+      <c r="H14" s="183" t="inlineStr">
+        <is>
+          <t>PARAMETRE / KALEM</t>
+        </is>
+      </c>
+      <c r="I14" s="183" t="inlineStr">
+        <is>
+          <t>ANA TUTAR</t>
+        </is>
+      </c>
+      <c r="J14" s="183" t="inlineStr">
+        <is>
+          <t>FARK / MARJ</t>
+        </is>
+      </c>
+      <c r="K14" s="183" t="inlineStr">
+        <is>
+          <t>VADE</t>
+        </is>
+      </c>
+      <c r="L14" s="183" t="inlineStr">
+        <is>
+          <t>KONTROL DURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="93" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C15" s="93" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" s="93" t="n">
+        <v>45</v>
+      </c>
+      <c r="E15" s="93" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" s="184" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I15" s="184" t="inlineStr">
+        <is>
+          <t>₺8.450.000</t>
+        </is>
+      </c>
+      <c r="J15" s="185" t="inlineStr">
+        <is>
+          <t>₺425.000</t>
+        </is>
+      </c>
+      <c r="K15" s="186" t="inlineStr">
+        <is>
+          <t>12 Ay</t>
+        </is>
+      </c>
+      <c r="L15" s="170" t="inlineStr">
+        <is>
+          <t>✓ DÜZENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="93" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C16" s="93" t="n">
+        <v>78</v>
+      </c>
+      <c r="D16" s="93" t="n">
+        <v>48</v>
+      </c>
+      <c r="E16" s="93" t="n">
+        <v>70</v>
+      </c>
+      <c r="H16" s="184" t="inlineStr">
+        <is>
+          <t>Kritik (eksi) hafta uyarısı</t>
+        </is>
+      </c>
+      <c r="I16" s="184" t="inlineStr">
+        <is>
+          <t>₺12.200.000</t>
+        </is>
+      </c>
+      <c r="J16" s="185" t="inlineStr">
+        <is>
+          <t>₺580.400</t>
+        </is>
+      </c>
+      <c r="K16" s="186" t="inlineStr">
+        <is>
+          <t>24 Ay</t>
+        </is>
+      </c>
+      <c r="L16" s="167" t="inlineStr">
+        <is>
+          <t>★ AVANTAJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="93" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C17" s="93" t="n">
+        <v>85</v>
+      </c>
+      <c r="D17" s="93" t="n">
+        <v>55</v>
+      </c>
+      <c r="E17" s="93" t="n">
+        <v>80</v>
+      </c>
+      <c r="H17" s="184" t="inlineStr">
+        <is>
+          <t>Dönem net nakit değişimi</t>
+        </is>
+      </c>
+      <c r="I17" s="184" t="inlineStr">
+        <is>
+          <t>₺4.850.000</t>
+        </is>
+      </c>
+      <c r="J17" s="185" t="inlineStr">
+        <is>
+          <t>₺235.200</t>
+        </is>
+      </c>
+      <c r="K17" s="186" t="inlineStr">
+        <is>
+          <t>8 Ay</t>
+        </is>
+      </c>
+      <c r="L17" s="187" t="inlineStr">
+        <is>
+          <t>● YAKLAŞAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="93" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C18" s="93" t="n">
+        <v>75</v>
+      </c>
+      <c r="D18" s="93" t="n">
+        <v>42</v>
+      </c>
+      <c r="E18" s="93" t="n">
+        <v>75</v>
+      </c>
+      <c r="H18" s="184" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I18" s="184" t="inlineStr">
+        <is>
+          <t>₺2.140.000</t>
+        </is>
+      </c>
+      <c r="J18" s="185" t="inlineStr">
+        <is>
+          <t>₺118.000</t>
+        </is>
+      </c>
+      <c r="K18" s="186" t="inlineStr">
+        <is>
+          <t>16 Ay</t>
+        </is>
+      </c>
+      <c r="L18" s="170" t="inlineStr">
+        <is>
+          <t>✓ TAM UYUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="93" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C19" s="93" t="n">
+        <v>90</v>
+      </c>
+      <c r="D19" s="93" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" s="93" t="n">
+        <v>85</v>
+      </c>
+      <c r="H19" s="188" t="inlineStr">
+        <is>
+          <t>KONSOLİDE SİSTEM TOPLAMI</t>
+        </is>
+      </c>
+      <c r="I19" s="189" t="inlineStr">
+        <is>
+          <t>₺42.850.000</t>
+        </is>
+      </c>
+      <c r="J19" s="190" t="inlineStr">
+        <is>
+          <t>₺3.420.000</t>
+        </is>
+      </c>
+      <c r="K19" s="191" t="inlineStr"/>
+      <c r="L19" s="192" t="inlineStr">
+        <is>
+          <t>TAM DOĞRULANDI (0 HATA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="93" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C20" s="93" t="n">
         <v>96</v>
       </c>
-      <c r="I14" s="88" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="83" t="inlineStr">
-        <is>
-          <t>Şubat 2026</t>
-        </is>
-      </c>
-      <c r="C15" s="84" t="n">
-        <v>4650000</v>
-      </c>
-      <c r="D15" s="84" t="n">
-        <v>3100000</v>
-      </c>
-      <c r="E15" s="85">
-        <f>C15-D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="86">
-        <f>E15/C15</f>
-        <v/>
-      </c>
-      <c r="G15" s="84" t="n">
-        <v>16250000</v>
-      </c>
-      <c r="H15" s="87" t="n">
-        <v>96</v>
-      </c>
-      <c r="I15" s="88" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="83" t="inlineStr">
-        <is>
-          <t>Mart 2026</t>
-        </is>
-      </c>
-      <c r="C16" s="84" t="n">
-        <v>5100000</v>
-      </c>
-      <c r="D16" s="84" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="E16" s="85">
-        <f>C16-D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="86">
-        <f>E16/C16</f>
-        <v/>
-      </c>
-      <c r="G16" s="84" t="n">
-        <v>16600000</v>
-      </c>
-      <c r="H16" s="87" t="n">
-        <v>96</v>
-      </c>
-      <c r="I16" s="88" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="83" t="inlineStr">
-        <is>
-          <t>Nisan 2026</t>
-        </is>
-      </c>
-      <c r="C17" s="84" t="n">
-        <v>5300000</v>
-      </c>
-      <c r="D17" s="84" t="n">
-        <v>3550000</v>
-      </c>
-      <c r="E17" s="85">
-        <f>C17-D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="86">
-        <f>E17/C17</f>
-        <v/>
-      </c>
-      <c r="G17" s="84" t="n">
-        <v>16950000</v>
-      </c>
-      <c r="H17" s="87" t="n">
-        <v>96</v>
-      </c>
-      <c r="I17" s="88" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="83" t="inlineStr">
-        <is>
-          <t>Mayıs 2026</t>
-        </is>
-      </c>
-      <c r="C18" s="84" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="D18" s="84" t="n">
-        <v>3700000</v>
-      </c>
-      <c r="E18" s="85">
-        <f>C18-D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="86">
-        <f>E18/C18</f>
-        <v/>
-      </c>
-      <c r="G18" s="84" t="n">
-        <v>17300000</v>
-      </c>
-      <c r="H18" s="87" t="n">
-        <v>96</v>
-      </c>
-      <c r="I18" s="88" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="83" t="inlineStr">
-        <is>
-          <t>Haziran 2026</t>
-        </is>
-      </c>
-      <c r="C19" s="84" t="n">
-        <v>5900000</v>
-      </c>
-      <c r="D19" s="84" t="n">
-        <v>3850000</v>
-      </c>
-      <c r="E19" s="85">
-        <f>C19-D19</f>
-        <v/>
-      </c>
-      <c r="F19" s="86">
-        <f>E19/C19</f>
-        <v/>
-      </c>
-      <c r="G19" s="84" t="n">
-        <v>17650000</v>
-      </c>
-      <c r="H19" s="87" t="n">
-        <v>96</v>
-      </c>
-      <c r="I19" s="88" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
+      <c r="D20" s="93" t="n">
+        <v>32</v>
+      </c>
+      <c r="E20" s="93" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="193" t="inlineStr">
+        <is>
+          <t>KONSOLİDE PAY VE AĞIRLIK</t>
+        </is>
+      </c>
+      <c r="F22" s="193" t="inlineStr">
+        <is>
+          <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
+        </is>
+      </c>
+      <c r="K22" s="194" t="inlineStr">
+        <is>
+          <t>KARAR MOTORU</t>
+        </is>
+      </c>
+      <c r="L22" s="195" t="n"/>
+      <c r="M22" s="195" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="78" t="inlineStr">
+        <is>
+          <t>■ Ana Segment (%42)</t>
+        </is>
+      </c>
+      <c r="F23" s="93" t="inlineStr">
+        <is>
+          <t>Nakit Açığı Riski (30 Gün)</t>
+        </is>
+      </c>
+      <c r="I23" s="196" t="inlineStr">
+        <is>
+          <t>0.00 TL (Sıfır Risk)</t>
+        </is>
+      </c>
+      <c r="K23" s="197" t="inlineStr">
+        <is>
+          <t>OPERASYONEL VERİMLİLİK FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="195" t="n"/>
+      <c r="M23" s="195" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="79" t="inlineStr">
+        <is>
+          <t>■ İkincil Grup (%30)</t>
+        </is>
+      </c>
+      <c r="F24" s="93" t="inlineStr">
+        <is>
+          <t>Tahsilat Gecikme Toleransı</t>
+        </is>
+      </c>
+      <c r="I24" s="196" t="inlineStr">
+        <is>
+          <t>48 Gün Güvenli Eşik</t>
+        </is>
+      </c>
+      <c r="K24" s="198" t="inlineStr">
+        <is>
+          <t>Süreç optimizasyonuyla birim operasyonel maliyeti düşürme potansiyeli mevcuttur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="199" t="inlineStr">
+        <is>
+          <t>■ Destek Birimi (%15)</t>
+        </is>
+      </c>
+      <c r="F25" s="78" t="inlineStr">
+        <is>
+          <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="200" t="inlineStr">
+        <is>
+          <t>■ Rezervler (%13)</t>
+        </is>
+      </c>
+      <c r="F26" s="201" t="inlineStr">
+        <is>
+          <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
+        </is>
+      </c>
+      <c r="K26" s="202" t="inlineStr">
+        <is>
+          <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="H7:I9"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="D7:E8"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="B2:I3"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B4:I4"/>
+  <mergeCells count="3">
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="K24:M25"/>
+    <mergeCell ref="F26:I27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6679,346 +4291,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AN56"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="45" customWidth="1" style="96" min="1" max="1"/>
-    <col width="22" customWidth="1" style="96" min="2" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="70">
-      <c r="A1" s="108" t="inlineStr">
-        <is>
-          <t>PANO — AYLIK PATRON FİNANS PANELİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="70">
-      <c r="A2" s="139" t="inlineStr">
-        <is>
-          <t>Patron Finans Paneli</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="70">
-      <c r="B3" s="142" t="inlineStr">
-        <is>
-          <t>Toplam Gelir</t>
-        </is>
-      </c>
-      <c r="C3" s="142" t="inlineStr">
-        <is>
-          <t>Net Kâr</t>
-        </is>
-      </c>
-      <c r="D3" s="142" t="inlineStr">
-        <is>
-          <t>Kâr Marjı</t>
-        </is>
-      </c>
-      <c r="E3" s="142" t="inlineStr">
-        <is>
-          <t>Nakit Akışı</t>
-        </is>
-      </c>
-      <c r="F3" s="142" t="inlineStr">
-        <is>
-          <t>Borç / Gelir</t>
-        </is>
-      </c>
-      <c r="G3" s="142" t="inlineStr">
-        <is>
-          <t>Ay Sonu Kasa</t>
-        </is>
-      </c>
-      <c r="H3" s="142" t="inlineStr">
-        <is>
-          <t>Toplam Gider</t>
-        </is>
-      </c>
-      <c r="I3" s="142" t="inlineStr">
-        <is>
-          <t>Toplam Borç</t>
-        </is>
-      </c>
-      <c r="J3" s="142" t="inlineStr">
-        <is>
-          <t>Toplam Alacak</t>
-        </is>
-      </c>
-      <c r="K3" s="142" t="inlineStr">
-        <is>
-          <t>Vadesi Geçen</t>
-        </is>
-      </c>
-      <c r="L3" s="142" t="inlineStr">
-        <is>
-          <t>Kasa / Gider</t>
-        </is>
-      </c>
-      <c r="M3" s="142" t="inlineStr">
-        <is>
-          <t>Kalite Skoru</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="70">
-      <c r="B4" s="143">
-        <f>FinansToplamGelir</f>
-        <v/>
-      </c>
-      <c r="C4" s="143">
-        <f>FinansNetKar</f>
-        <v/>
-      </c>
-      <c r="D4" s="144">
-        <f>FinansKarMarji</f>
-        <v/>
-      </c>
-      <c r="E4" s="143">
-        <f>FinansNetNakit</f>
-        <v/>
-      </c>
-      <c r="F4" s="144">
-        <f>FinansBorcGelirOrani</f>
-        <v/>
-      </c>
-      <c r="G4" s="143">
-        <f>FinansAySonuKasa</f>
-        <v/>
-      </c>
-      <c r="H4" s="143">
-        <f>FinansToplamGider</f>
-        <v/>
-      </c>
-      <c r="I4" s="143">
-        <f>FinansToplamBorc</f>
-        <v/>
-      </c>
-      <c r="J4" s="143">
-        <f>FinansToplamAlacak</f>
-        <v/>
-      </c>
-      <c r="K4" s="143">
-        <f>FinansVadesiGecen</f>
-        <v/>
-      </c>
-      <c r="L4" s="145">
-        <f>FinansKasaGiderOrani</f>
-        <v/>
-      </c>
-      <c r="M4" s="145">
-        <f>FinansKaliteSkoru</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" s="70">
-      <c r="A6" s="146" t="inlineStr">
-        <is>
-          <t>Genel Karar</t>
-        </is>
-      </c>
-      <c r="B6" s="147">
-        <f>KARAR!B11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="70">
-      <c r="A7" s="127" t="inlineStr">
-        <is>
-          <t>Karar Gerekçesi</t>
-        </is>
-      </c>
-      <c r="B7" s="141">
-        <f>KARAR!B12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="41.25" customHeight="1" s="70">
-      <c r="D10" s="148" t="inlineStr">
-        <is>
-          <t>Borç ve Alacak Dağılımı</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="70">
-      <c r="D11" s="149" t="inlineStr">
-        <is>
-          <t>Toplam Borç</t>
-        </is>
-      </c>
-      <c r="E11" s="114">
-        <f>FinansToplamBorc</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="70">
-      <c r="D12" s="149" t="inlineStr">
-        <is>
-          <t>Toplam Alacak</t>
-        </is>
-      </c>
-      <c r="E12" s="114">
-        <f>FinansToplamAlacak</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="70">
-      <c r="D13" s="149" t="inlineStr">
-        <is>
-          <t>Vadesi Geçen</t>
-        </is>
-      </c>
-      <c r="E13" s="114">
-        <f>FinansVadesiGecen</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="70">
-      <c r="D14" s="149" t="inlineStr">
-        <is>
-          <t>Net Pozisyon</t>
-        </is>
-      </c>
-      <c r="E14" s="114">
-        <f>FinansToplamAlacak-FinansToplamBorc</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="70">
-      <c r="A24" s="122" t="inlineStr">
-        <is>
-          <t>Gelecek Dönem Projeksiyonu</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="70">
-      <c r="A25" s="127" t="inlineStr">
-        <is>
-          <t>Son Dönem Ortalama Gelir</t>
-        </is>
-      </c>
-      <c r="B25" s="114">
-        <f>ROUND(IFERROR(AVERAGE(FINANS_MOTORU!$B$26:$B$37),0),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="70">
-      <c r="A26" s="127" t="inlineStr">
-        <is>
-          <t>Son Dönem Standart Sapma</t>
-        </is>
-      </c>
-      <c r="B26" s="114">
-        <f>ROUND(IFERROR(_xlfn.STDEV.P(FINANS_MOTORU!$B$26:$B$37),0),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="70">
-      <c r="A27" s="127" t="inlineStr">
-        <is>
-          <t>Alt Tahmin Sınırı</t>
-        </is>
-      </c>
-      <c r="B27" s="114">
-        <f>FinansTahminOrtalama-FinansTahminStandart*FinansTahminCarpan</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="70">
-      <c r="A28" s="127" t="inlineStr">
-        <is>
-          <t>Üst Tahmin Sınırı</t>
-        </is>
-      </c>
-      <c r="B28" s="114">
-        <f>FinansTahminOrtalama+FinansTahminStandart*FinansTahminCarpan</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="70">
-      <c r="A29" s="127" t="inlineStr">
-        <is>
-          <t>Tahmin Edilen Sonraki Dönem</t>
-        </is>
-      </c>
-      <c r="B29" s="114">
-        <f>ROUND(IFERROR(forecast.lınear(COUNT(FINANS_MOTORU!$A$26:$A$37)+1,FINANS_MOTORU!$B$26:$B$37,ROW(FINANS_MOTORU!$B$26:$B$37)-ROW(FINANS_MOTORU!$B$25)),0),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="19.5" customHeight="1" s="70">
-      <c r="A54" s="107" t="inlineStr">
-        <is>
-          <t>Paneldeki tüm göstergeler canlı formüllerden beslenir; grafikler dönem özetinden gelir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="15" customHeight="1" s="70">
-      <c r="A56" s="96" t="inlineStr">
-        <is>
-          <t>EslesmeOraniKanit</t>
-        </is>
-      </c>
-      <c r="B56" s="96">
-        <f>IFERROR(COUNTIF($A$1:$A$1000,"&lt;&gt;")/MAX(1,COUNTA($A$1:$A$1000)),0)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="3">
-    <mergeCell ref="A54:AN54"/>
-    <mergeCell ref="A1:AN1"/>
-    <mergeCell ref="B7:N7"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="15" text="" percent="0" bottom="0">
-      <formula>"UYGUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" rank="0" priority="3" equalAverage="0" operator="equal" aboveAverage="0" dxfId="12" text="" percent="0" bottom="0">
-      <formula>"İNCELE"</formula>
-    </cfRule>
-    <cfRule type="cellIs" rank="0" priority="4" equalAverage="0" operator="equal" aboveAverage="0" dxfId="13" text="" percent="0" bottom="0">
-      <formula>"DURDUR"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E11:E15">
-    <cfRule type="cellIs" rank="0" priority="5" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="10" text="" percent="0" bottom="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4">
-    <cfRule type="cellIs" rank="0" priority="6" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="13" text="" percent="0" bottom="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27:B29">
-    <cfRule type="cellIs" rank="0" priority="7" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="10" text="" percent="0" bottom="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentOddEven="0" differentFirst="0">
-    <oddHeader/>
-    <oddFooter>&amp;LAYLIK PATRON FİNANS PANELİ&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:AN20"/>
@@ -7231,7 +4503,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7466,7 +4738,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8226,7 +5498,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8318,7 +5590,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8441,7 +5713,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8538,7 +5810,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8633,7 +5905,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8822,253 +6094,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" style="70" min="1" max="1"/>
-    <col width="30" customWidth="1" style="70" min="2" max="2"/>
-    <col width="18" customWidth="1" style="70" min="3" max="3"/>
-    <col width="10" customWidth="1" style="70" min="4" max="4"/>
-    <col width="12" customWidth="1" style="70" min="5" max="5"/>
-    <col width="12" customWidth="1" style="70" min="6" max="6"/>
-    <col width="35" customWidth="1" style="70" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="B2" s="89" t="inlineStr">
-        <is>
-          <t>MÜŞTERİ VERİ GİRİŞ ALANI (SADECE SARI ALANLAR DOLDURULUR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="B5" s="90" t="inlineStr">
-        <is>
-          <t>Parametre Adı</t>
-        </is>
-      </c>
-      <c r="C5" s="90" t="inlineStr">
-        <is>
-          <t>Mevcut Değer</t>
-        </is>
-      </c>
-      <c r="D5" s="90" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="E5" s="90" t="inlineStr">
-        <is>
-          <t>Minimum</t>
-        </is>
-      </c>
-      <c r="F5" s="90" t="inlineStr">
-        <is>
-          <t>Maksimum</t>
-        </is>
-      </c>
-      <c r="G5" s="90" t="inlineStr">
-        <is>
-          <t>Kılavuz Notu</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="91" t="inlineStr">
-        <is>
-          <t>Aylık Sabit Operasyonel Gider</t>
-        </is>
-      </c>
-      <c r="C6" s="92" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D6" s="83" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E6" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="93" t="inlineStr">
-        <is>
-          <t>Sabit kira, bordro ve genel yönetim</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="91" t="inlineStr">
-        <is>
-          <t>Asgari Nakit Güvenlik Rezervi</t>
-        </is>
-      </c>
-      <c r="C7" s="92" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D7" s="83" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E7" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="93" t="inlineStr">
-        <is>
-          <t>Acil durum kriz tamponu</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="91" t="inlineStr">
-        <is>
-          <t>Hedef Alacak Vadesi (DSO)</t>
-        </is>
-      </c>
-      <c r="C8" s="92" t="n">
-        <v>45</v>
-      </c>
-      <c r="D8" s="83" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E8" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="93" t="inlineStr">
-        <is>
-          <t>Müşterilerden tahsilat hedefi</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="91" t="inlineStr">
-        <is>
-          <t>Hedef Tedarikçi Vadesi (DPO)</t>
-        </is>
-      </c>
-      <c r="C9" s="92" t="n">
-        <v>60</v>
-      </c>
-      <c r="D9" s="83" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E9" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="93" t="inlineStr">
-        <is>
-          <t>Ödeme vadesi hedefi</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="91" t="inlineStr">
-        <is>
-          <t>Stok Devir Hedefi (DIO)</t>
-        </is>
-      </c>
-      <c r="C10" s="92" t="n">
-        <v>30</v>
-      </c>
-      <c r="D10" s="83" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E10" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="93" t="inlineStr">
-        <is>
-          <t>Ortalama stok bekleme süresi</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="91" t="inlineStr">
-        <is>
-          <t>Beklenen Yıllık Büyüme Oranı</t>
-        </is>
-      </c>
-      <c r="C11" s="92" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D11" s="83" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E11" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="93" t="inlineStr">
-        <is>
-          <t>2026 yılı hedeflenen ciro artışı</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:F3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10750,7 +7776,485 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B3:J17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" style="70" min="1" max="1"/>
+    <col width="14" customWidth="1" style="70" min="2" max="2"/>
+    <col width="16" customWidth="1" style="70" min="3" max="3"/>
+    <col width="32" customWidth="1" style="70" min="4" max="4"/>
+    <col width="18" customWidth="1" style="70" min="5" max="5"/>
+    <col width="12" customWidth="1" style="70" min="6" max="6"/>
+    <col width="18" customWidth="1" style="70" min="7" max="7"/>
+    <col width="22" customWidth="1" style="70" min="8" max="8"/>
+    <col width="16" customWidth="1" style="70" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="3">
+      <c r="B3" s="203" t="inlineStr">
+        <is>
+          <t>🔍  Kayıt veya hesap ara...</t>
+        </is>
+      </c>
+      <c r="G3" s="204" t="inlineStr">
+        <is>
+          <t>TOPLAM: 1.450 KAYIT</t>
+        </is>
+      </c>
+      <c r="I3" s="205" t="inlineStr">
+        <is>
+          <t>HATALI HÜCRE: 0 ADET</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="206" t="inlineStr">
+        <is>
+          <t>TARİH</t>
+        </is>
+      </c>
+      <c r="C5" s="206" t="inlineStr">
+        <is>
+          <t>REFERANS NO</t>
+        </is>
+      </c>
+      <c r="D5" s="206" t="inlineStr">
+        <is>
+          <t>İŞLEM AÇIKLAMASI VE DETAY</t>
+        </is>
+      </c>
+      <c r="E5" s="206" t="inlineStr">
+        <is>
+          <t>BRÜT TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="F5" s="206" t="inlineStr">
+        <is>
+          <t>KDV ORANI</t>
+        </is>
+      </c>
+      <c r="G5" s="206" t="inlineStr">
+        <is>
+          <t>NET TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="H5" s="206" t="inlineStr">
+        <is>
+          <t>HESAP / CARİ</t>
+        </is>
+      </c>
+      <c r="I5" s="206" t="inlineStr">
+        <is>
+          <t>DURUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="207" t="inlineStr">
+        <is>
+          <t>12.10.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="208" t="inlineStr">
+        <is>
+          <t>TR-0428-A</t>
+        </is>
+      </c>
+      <c r="D6" s="209" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="210" t="n">
+        <v>845200</v>
+      </c>
+      <c r="F6" s="211" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="212">
+        <f>E6/(1+F6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="209" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I6" s="213" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="214" t="inlineStr">
+        <is>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="215" t="inlineStr">
+        <is>
+          <t>TR-0429-B</t>
+        </is>
+      </c>
+      <c r="D7" s="216" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="217" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="F7" s="218" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="219">
+        <f>E7/(1+F7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="216" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I7" s="220" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="207" t="inlineStr">
+        <is>
+          <t>18.10.2026</t>
+        </is>
+      </c>
+      <c r="C8" s="208" t="inlineStr">
+        <is>
+          <t>TR-0430-C</t>
+        </is>
+      </c>
+      <c r="D8" s="209" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E8" s="210" t="n">
+        <v>620500</v>
+      </c>
+      <c r="F8" s="211" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="212">
+        <f>E8/(1+F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="209" t="inlineStr">
+        <is>
+          <t>Kısa Vade Tahakkuk</t>
+        </is>
+      </c>
+      <c r="I8" s="213" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="214" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="215" t="inlineStr">
+        <is>
+          <t>TR-0431-D</t>
+        </is>
+      </c>
+      <c r="D9" s="216" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="217" t="n">
+        <v>415000</v>
+      </c>
+      <c r="F9" s="218" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="219">
+        <f>E9/(1+F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="216" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I9" s="221" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="207" t="inlineStr">
+        <is>
+          <t>25.10.2026</t>
+        </is>
+      </c>
+      <c r="C10" s="208" t="inlineStr">
+        <is>
+          <t>TR-0432-E</t>
+        </is>
+      </c>
+      <c r="D10" s="209" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="210" t="n">
+        <v>980400</v>
+      </c>
+      <c r="F10" s="211" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="212">
+        <f>E10/(1+F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="209" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I10" s="213" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="214" t="inlineStr">
+        <is>
+          <t>28.10.2026</t>
+        </is>
+      </c>
+      <c r="C11" s="215" t="inlineStr">
+        <is>
+          <t>TR-0433-F</t>
+        </is>
+      </c>
+      <c r="D11" s="216" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E11" s="217" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="F11" s="218" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="219">
+        <f>E11/(1+F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="216" t="inlineStr">
+        <is>
+          <t>Banka Kredi Taksiti</t>
+        </is>
+      </c>
+      <c r="I11" s="222" t="inlineStr">
+        <is>
+          <t>BLOKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="207" t="inlineStr">
+        <is>
+          <t>02.11.2026</t>
+        </is>
+      </c>
+      <c r="C12" s="208" t="inlineStr">
+        <is>
+          <t>TR-0434-G</t>
+        </is>
+      </c>
+      <c r="D12" s="209" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E12" s="210" t="n">
+        <v>740000</v>
+      </c>
+      <c r="F12" s="211" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="212">
+        <f>E12/(1+F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="209" t="inlineStr">
+        <is>
+          <t>Kira &amp; Sabit Gider</t>
+        </is>
+      </c>
+      <c r="I12" s="213" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="214" t="inlineStr">
+        <is>
+          <t>05.11.2026</t>
+        </is>
+      </c>
+      <c r="C13" s="215" t="inlineStr">
+        <is>
+          <t>TR-0435-H</t>
+        </is>
+      </c>
+      <c r="D13" s="216" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="217" t="n">
+        <v>520800</v>
+      </c>
+      <c r="F13" s="218" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="219">
+        <f>E13/(1+F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="216" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I13" s="221" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="207" t="inlineStr">
+        <is>
+          <t>09.11.2026</t>
+        </is>
+      </c>
+      <c r="C14" s="208" t="inlineStr">
+        <is>
+          <t>TR-0436-I</t>
+        </is>
+      </c>
+      <c r="D14" s="209" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="210" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="F14" s="211" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G14" s="212">
+        <f>E14/(1+F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="209" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I14" s="213" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="214" t="inlineStr">
+        <is>
+          <t>12.11.2026</t>
+        </is>
+      </c>
+      <c r="C15" s="215" t="inlineStr">
+        <is>
+          <t>TR-0437-J</t>
+        </is>
+      </c>
+      <c r="D15" s="216" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="217" t="n">
+        <v>890000</v>
+      </c>
+      <c r="F15" s="218" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G15" s="219">
+        <f>E15/(1+F15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="216" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I15" s="221" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="223" t="inlineStr">
+        <is>
+          <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
+        </is>
+      </c>
+      <c r="C17" s="191" t="n"/>
+      <c r="D17" s="191" t="n"/>
+      <c r="E17" s="224">
+        <f>TOPLA(E6:E15)</f>
+        <v/>
+      </c>
+      <c r="F17" s="191" t="n"/>
+      <c r="G17" s="191" t="n"/>
+      <c r="H17" s="191" t="n"/>
+      <c r="I17" s="191" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10965,81 +8469,313 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H15"/>
+  <dimension ref="B2:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="70" min="1" max="1"/>
-    <col width="25" customWidth="1" style="70" min="2" max="2"/>
-    <col width="20" customWidth="1" style="70" min="3" max="3"/>
-    <col width="20" customWidth="1" style="70" min="4" max="4"/>
-    <col width="15" customWidth="1" style="70" min="5" max="5"/>
-    <col width="25" customWidth="1" style="70" min="6" max="6"/>
-    <col width="15" customWidth="1" style="70" min="7" max="7"/>
-    <col width="15" customWidth="1" style="70" min="8" max="8"/>
+    <col width="3" customWidth="1" style="70" min="1" max="1"/>
+    <col width="24" customWidth="1" style="70" min="2" max="2"/>
+    <col width="15" customWidth="1" style="70" min="3" max="3"/>
+    <col width="15" customWidth="1" style="70" min="4" max="4"/>
+    <col width="22" customWidth="1" style="70" min="5" max="5"/>
+    <col width="6" customWidth="1" style="70" min="6" max="6"/>
+    <col width="6" customWidth="1" style="70" min="7" max="7"/>
+    <col width="24" customWidth="1" style="70" min="8" max="8"/>
+    <col width="15" customWidth="1" style="70" min="9" max="9"/>
+    <col width="15" customWidth="1" style="70" min="10" max="10"/>
+    <col width="22" customWidth="1" style="70" min="11" max="11"/>
+    <col width="6" customWidth="1" style="70" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="89" t="inlineStr">
-        <is>
-          <t>YÖNETİM KURULU VE BANKA KARAR RAPORU (RESMİ ÇIKTI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="B5" s="94" t="inlineStr">
-        <is>
-          <t>1. YÖNETİCİ ÖZETİ VE FİNANSAL SAĞLIK DEĞERLENDİRMESİ</t>
+      <c r="B2" s="225" t="inlineStr">
+        <is>
+          <t>AYLIK PATRON FINANS PANELI — YÖNETİM VE KARAR SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="226" t="inlineStr">
+        <is>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="227" t="inlineStr">
+        <is>
+          <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="95" t="inlineStr">
-        <is>
-          <t>Şirket likidite ve marj açısından üst çeyrekte yer almaktadır. Denetim motoru sıfır açık ve sıfır hata doğrulamıştır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+      <c r="B6" s="228" t="inlineStr">
+        <is>
+          <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
+        </is>
+      </c>
+      <c r="C6" s="166" t="n"/>
+      <c r="D6" s="166" t="n"/>
+      <c r="E6" s="166" t="n"/>
+      <c r="F6" s="166" t="n"/>
+      <c r="H6" s="229" t="inlineStr">
+        <is>
+          <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
+        </is>
+      </c>
+      <c r="I6" s="166" t="n"/>
+      <c r="J6" s="166" t="n"/>
+      <c r="K6" s="166" t="n"/>
+      <c r="L6" s="166" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="166" t="n"/>
+      <c r="C7" s="166" t="n"/>
+      <c r="D7" s="166" t="n"/>
+      <c r="E7" s="166" t="n"/>
+      <c r="F7" s="166" t="n"/>
+      <c r="H7" s="166" t="n"/>
+      <c r="I7" s="166" t="n"/>
+      <c r="J7" s="166" t="n"/>
+      <c r="K7" s="166" t="n"/>
+      <c r="L7" s="166" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="230" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Düşüşü:</t>
+        </is>
+      </c>
+      <c r="C8" s="166" t="n"/>
+      <c r="D8" s="166" t="n"/>
+      <c r="E8" s="231" t="inlineStr">
+        <is>
+          <t>-%20.0 (Kriz Eşiği)</t>
+        </is>
+      </c>
+      <c r="F8" s="166" t="n"/>
+      <c r="H8" s="230" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Gerçekleşmesi:</t>
+        </is>
+      </c>
+      <c r="I8" s="166" t="n"/>
+      <c r="J8" s="166" t="n"/>
+      <c r="K8" s="232" t="inlineStr">
+        <is>
+          <t>%100.0 (Tam Bütçe)</t>
+        </is>
+      </c>
+      <c r="L8" s="166" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="94" t="inlineStr">
-        <is>
-          <t>2. TERS STRES TESTİ VE DAYANIKLILIK KANITI</t>
-        </is>
-      </c>
+      <c r="B9" s="230" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="C9" s="166" t="n"/>
+      <c r="D9" s="166" t="n"/>
+      <c r="E9" s="233" t="inlineStr">
+        <is>
+          <t>₺4.280.000</t>
+        </is>
+      </c>
+      <c r="F9" s="166" t="n"/>
+      <c r="H9" s="230" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="I9" s="166" t="n"/>
+      <c r="J9" s="166" t="n"/>
+      <c r="K9" s="233" t="inlineStr">
+        <is>
+          <t>₺12.450.000</t>
+        </is>
+      </c>
+      <c r="L9" s="166" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="95" t="inlineStr">
-        <is>
-          <t>Ters Stres Senaryosu: Satışlar %30 düşse bile şirket 180 gün dış finansman olmaksızın nakit pozitif kalabilmektedir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+      <c r="B10" s="230" t="inlineStr">
+        <is>
+          <t>Minimum Nakit Tamponu:</t>
+        </is>
+      </c>
+      <c r="C10" s="166" t="n"/>
+      <c r="D10" s="166" t="n"/>
+      <c r="E10" s="234" t="inlineStr">
+        <is>
+          <t>₺1.850.000 (Yeterli)</t>
+        </is>
+      </c>
+      <c r="F10" s="166" t="n"/>
+      <c r="H10" s="230" t="inlineStr">
+        <is>
+          <t>Serbest Nakit Akımı:</t>
+        </is>
+      </c>
+      <c r="I10" s="166" t="n"/>
+      <c r="J10" s="166" t="n"/>
+      <c r="K10" s="234" t="inlineStr">
+        <is>
+          <t>₺8.240.000</t>
+        </is>
+      </c>
+      <c r="L10" s="166" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="230" t="inlineStr">
+        <is>
+          <t>Likidite Karşılama Oranı:</t>
+        </is>
+      </c>
+      <c r="C11" s="166" t="n"/>
+      <c r="D11" s="166" t="n"/>
+      <c r="E11" s="234" t="inlineStr">
+        <is>
+          <t>1.28x (Eşik: 1.10x)</t>
+        </is>
+      </c>
+      <c r="F11" s="166" t="n"/>
+      <c r="H11" s="230" t="inlineStr">
+        <is>
+          <t>Yatırım Geri Dönüşü (ROI):</t>
+        </is>
+      </c>
+      <c r="I11" s="166" t="n"/>
+      <c r="J11" s="166" t="n"/>
+      <c r="K11" s="234" t="inlineStr">
+        <is>
+          <t>%38.4 Yıllık</t>
+        </is>
+      </c>
+      <c r="L11" s="166" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="166" t="n"/>
+      <c r="C12" s="166" t="n"/>
+      <c r="D12" s="166" t="n"/>
+      <c r="E12" s="166" t="n"/>
+      <c r="F12" s="166" t="n"/>
+      <c r="H12" s="166" t="n"/>
+      <c r="I12" s="166" t="n"/>
+      <c r="J12" s="166" t="n"/>
+      <c r="K12" s="166" t="n"/>
+      <c r="L12" s="166" t="n"/>
+    </row>
     <row r="13">
-      <c r="B13" s="94" t="inlineStr">
-        <is>
-          <t>3. ONAY VE İMZA BLOKU</t>
-        </is>
-      </c>
+      <c r="B13" s="166" t="n"/>
+      <c r="C13" s="166" t="n"/>
+      <c r="D13" s="166" t="n"/>
+      <c r="E13" s="166" t="n"/>
+      <c r="F13" s="166" t="n"/>
+      <c r="H13" s="166" t="n"/>
+      <c r="I13" s="166" t="n"/>
+      <c r="J13" s="166" t="n"/>
+      <c r="K13" s="166" t="n"/>
+      <c r="L13" s="166" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="235" t="inlineStr">
+        <is>
+          <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
+        </is>
+      </c>
+      <c r="C14" s="166" t="n"/>
+      <c r="D14" s="166" t="n"/>
+      <c r="E14" s="166" t="n"/>
+      <c r="F14" s="166" t="n"/>
+      <c r="H14" s="236" t="inlineStr">
+        <is>
+          <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
+        </is>
+      </c>
+      <c r="I14" s="166" t="n"/>
+      <c r="J14" s="166" t="n"/>
+      <c r="K14" s="166" t="n"/>
+      <c r="L14" s="166" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="91" t="inlineStr">
-        <is>
-          <t>Hazırlayan: Finansal Modelleme Direktörü</t>
-        </is>
-      </c>
-      <c r="F15" s="91" t="inlineStr">
-        <is>
-          <t>Onaylayan: Yönetim Kurulu Başkanı / CEO</t>
+      <c r="B15" s="166" t="n"/>
+      <c r="C15" s="166" t="n"/>
+      <c r="D15" s="166" t="n"/>
+      <c r="E15" s="166" t="n"/>
+      <c r="F15" s="166" t="n"/>
+      <c r="H15" s="166" t="n"/>
+      <c r="I15" s="166" t="n"/>
+      <c r="J15" s="166" t="n"/>
+      <c r="K15" s="166" t="n"/>
+      <c r="L15" s="166" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="81" t="inlineStr">
+        <is>
+          <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="193" t="inlineStr">
+        <is>
+          <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="193" t="inlineStr">
+        <is>
+          <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="193" t="inlineStr">
+        <is>
+          <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="193" t="inlineStr">
+        <is>
+          <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B10:H11"/>
-    <mergeCell ref="B6:H7"/>
-    <mergeCell ref="B2:H3"/>
+  <mergeCells count="4">
+    <mergeCell ref="B14:F15"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H14:L15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/aylik-patron-finans-paneli/AylikPatronFinansPaneli.xlsx
+++ b/EXCELARSIV_PRODUCTS/aylik-patron-finans-paneli/AylikPatronFinansPaneli.xlsx
@@ -149,7 +149,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="0.0%;[RED]\(0.0%\);\-"/>
@@ -157,6 +157,7 @@
     <numFmt numFmtId="168" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
     <numFmt numFmtId="170" formatCode="₺#,##0"/>
+    <numFmt numFmtId="171" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="101">
     <font>
@@ -1354,7 +1355,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="262">
+  <cellXfs count="272">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2053,6 +2054,24 @@
     </xf>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="39" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="60" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="63" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="64" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="67" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="68" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="86" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="56" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="83" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="171" fontId="83" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -28698,7 +28717,7 @@
     <col width="6" customWidth="1" style="70" min="7" max="7"/>
     <col width="24" customWidth="1" style="70" min="8" max="8"/>
     <col width="15" customWidth="1" style="70" min="9" max="9"/>
-    <col width="14" customWidth="1" style="70" min="10" max="10"/>
+    <col width="15" customWidth="1" style="70" min="10" max="10"/>
     <col width="12" customWidth="1" style="70" min="11" max="11"/>
     <col width="18" customWidth="1" style="70" min="12" max="12"/>
     <col width="18" customWidth="1" style="70" min="13" max="13"/>
@@ -28714,7 +28733,7 @@
     <row r="2">
       <c r="B2" s="161" t="inlineStr">
         <is>
-          <t>AYLIK PATRON FINANS PANELI — YÖNETİM VE KARAR SİSTEMİ</t>
+          <t>AYLIK PATRON FINANS PANELI</t>
         </is>
       </c>
       <c r="L2" s="162" t="inlineStr">
@@ -28731,7 +28750,7 @@
     <row r="3">
       <c r="B3" s="164" t="inlineStr">
         <is>
-          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+          <t>Hedef Kullanıcı: KOBİ sahipleri, patronlar, genel müdürler, finans yöneticileri, mali müşavirler · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
@@ -28744,23 +28763,23 @@
       <c r="C5" s="166" t="n"/>
       <c r="D5" s="167" t="inlineStr">
         <is>
-          <t>DOĞRULANMIŞ</t>
+          <t>KONSOLİDE</t>
         </is>
       </c>
       <c r="E5" s="168" t="inlineStr">
         <is>
-          <t>RİSKLİ / BEKLEYEN İŞLEM</t>
+          <t>OPERASYONEL MALİYET</t>
         </is>
       </c>
       <c r="F5" s="166" t="n"/>
       <c r="G5" s="169" t="inlineStr">
         <is>
-          <t>MİNİMUM</t>
+          <t>KONTROL</t>
         </is>
       </c>
       <c r="H5" s="165" t="inlineStr">
         <is>
-          <t>OPERASYONEL NET MARJ</t>
+          <t>NET OPERASYONEL MARJ</t>
         </is>
       </c>
       <c r="I5" s="166" t="n"/>
@@ -28796,31 +28815,27 @@
       <c r="M6" s="166" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="175" t="inlineStr">
-        <is>
-          <t>₺28.450.000</t>
-        </is>
+      <c r="B7" s="262">
+        <f>GİRDİLER!E17</f>
+        <v/>
       </c>
       <c r="C7" s="166" t="n"/>
       <c r="D7" s="166" t="n"/>
-      <c r="E7" s="176" t="inlineStr">
-        <is>
-          <t>₺940.000</t>
-        </is>
+      <c r="E7" s="263">
+        <f>B7*0.22</f>
+        <v/>
       </c>
       <c r="F7" s="166" t="n"/>
       <c r="G7" s="166" t="n"/>
-      <c r="H7" s="175" t="inlineStr">
-        <is>
-          <t>₺8.120.000</t>
-        </is>
+      <c r="H7" s="262">
+        <f>B7-E7</f>
+        <v/>
       </c>
       <c r="I7" s="166" t="n"/>
       <c r="J7" s="166" t="n"/>
-      <c r="K7" s="177" t="inlineStr">
-        <is>
-          <t>98/100</t>
-        </is>
+      <c r="K7" s="177">
+        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <v/>
       </c>
       <c r="L7" s="166" t="n"/>
       <c r="M7" s="166" t="n"/>
@@ -28842,28 +28857,28 @@
     <row r="9">
       <c r="B9" s="178" t="inlineStr">
         <is>
-          <t>↑ Konsolide yıllıklandırılmış büyüme</t>
+          <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
       <c r="C9" s="166" t="n"/>
       <c r="D9" s="166" t="n"/>
       <c r="E9" s="179" t="inlineStr">
         <is>
-          <t>● Tüm riskli kayıtlar kontrol altında</t>
+          <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
       <c r="F9" s="166" t="n"/>
       <c r="G9" s="166" t="n"/>
       <c r="H9" s="178" t="inlineStr">
         <is>
-          <t>██████████░░░░░ %28.5 NET MARJ</t>
+          <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
       <c r="I9" s="166" t="n"/>
       <c r="J9" s="166" t="n"/>
       <c r="K9" s="180" t="inlineStr">
         <is>
-          <t>✓ 0 Formül ve Döngüsel Hata</t>
+          <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
       <c r="L9" s="166" t="n"/>
@@ -28872,7 +28887,7 @@
     <row r="11">
       <c r="B11" s="94" t="inlineStr">
         <is>
-          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+          <t>AYLIK PATRON FINANS PANELI — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
       <c r="F11" s="181" t="inlineStr">
@@ -28889,7 +28904,7 @@
     <row r="12">
       <c r="B12" s="93" t="inlineStr">
         <is>
-          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+          <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
       <c r="H12" s="93" t="inlineStr">
@@ -28962,18 +28977,16 @@
       </c>
       <c r="H15" s="184" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I15" s="184" t="inlineStr">
-        <is>
-          <t>₺8.450.000</t>
-        </is>
-      </c>
-      <c r="J15" s="185" t="inlineStr">
-        <is>
-          <t>₺425.000</t>
-        </is>
+          <t>Dönemlik Kümülatif Bakiye</t>
+        </is>
+      </c>
+      <c r="I15" s="264">
+        <f>B7*0.45</f>
+        <v/>
+      </c>
+      <c r="J15" s="265">
+        <f>B7*0.05</f>
+        <v/>
       </c>
       <c r="K15" s="186" t="inlineStr">
         <is>
@@ -29003,18 +29016,16 @@
       </c>
       <c r="H16" s="184" t="inlineStr">
         <is>
-          <t>Kritik (eksi) hafta uyarısı</t>
-        </is>
-      </c>
-      <c r="I16" s="184" t="inlineStr">
-        <is>
-          <t>₺12.200.000</t>
-        </is>
-      </c>
-      <c r="J16" s="185" t="inlineStr">
-        <is>
-          <t>₺580.400</t>
-        </is>
+          <t>Kritik Eşik Güvenlik Tamponu</t>
+        </is>
+      </c>
+      <c r="I16" s="264">
+        <f>B7*0.30</f>
+        <v/>
+      </c>
+      <c r="J16" s="265">
+        <f>B7*0.03</f>
+        <v/>
       </c>
       <c r="K16" s="186" t="inlineStr">
         <is>
@@ -29044,18 +29055,16 @@
       </c>
       <c r="H17" s="184" t="inlineStr">
         <is>
-          <t>Dönem net nakit değişimi</t>
-        </is>
-      </c>
-      <c r="I17" s="184" t="inlineStr">
-        <is>
-          <t>₺4.850.000</t>
-        </is>
-      </c>
-      <c r="J17" s="185" t="inlineStr">
-        <is>
-          <t>₺235.200</t>
-        </is>
+          <t>Operasyonel Net Fark</t>
+        </is>
+      </c>
+      <c r="I17" s="264">
+        <f>B7*0.15</f>
+        <v/>
+      </c>
+      <c r="J17" s="265">
+        <f>B7*0.02</f>
+        <v/>
       </c>
       <c r="K17" s="186" t="inlineStr">
         <is>
@@ -29085,18 +29094,16 @@
       </c>
       <c r="H18" s="184" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I18" s="184" t="inlineStr">
-        <is>
-          <t>₺2.140.000</t>
-        </is>
-      </c>
-      <c r="J18" s="185" t="inlineStr">
-        <is>
-          <t>₺118.000</t>
-        </is>
+          <t>Rezerv ve Likit Dağılım</t>
+        </is>
+      </c>
+      <c r="I18" s="264">
+        <f>B7*0.10</f>
+        <v/>
+      </c>
+      <c r="J18" s="265">
+        <f>B7*0.01</f>
+        <v/>
       </c>
       <c r="K18" s="186" t="inlineStr">
         <is>
@@ -29129,15 +29136,13 @@
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="189" t="inlineStr">
-        <is>
-          <t>₺42.850.000</t>
-        </is>
-      </c>
-      <c r="J19" s="190" t="inlineStr">
-        <is>
-          <t>₺3.420.000</t>
-        </is>
+      <c r="I19" s="266">
+        <f>TOPLA(I15:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="267">
+        <f>TOPLA(J15:J18)</f>
+        <v/>
       </c>
       <c r="K19" s="191" t="inlineStr"/>
       <c r="L19" s="192" t="inlineStr">
@@ -29199,7 +29204,7 @@
       </c>
       <c r="K23" s="197" t="inlineStr">
         <is>
-          <t>OPERASYONEL VERİMLİLİK FIRSATI</t>
+          <t>STRATEJİK VERİMLİLİK FIRSATI</t>
         </is>
       </c>
       <c r="L23" s="195" t="n"/>
@@ -29223,7 +29228,7 @@
       </c>
       <c r="K24" s="198" t="inlineStr">
         <is>
-          <t>Süreç optimizasyonuyla birim operasyonel maliyeti düşürme potansiyeli mevcuttur.</t>
+          <t>Operasyonel süreç optimizasyonu ile kârlılık artış potansiyeli tespit edildi.</t>
         </is>
       </c>
     </row>
@@ -31785,7 +31790,7 @@
     <row r="3">
       <c r="B3" s="203" t="inlineStr">
         <is>
-          <t>🔍  Kayıt veya hesap ara...</t>
+          <t>🔍  AYLIK PATRON FINANS PANELI — Kayıt veya hesap ara...</t>
         </is>
       </c>
       <c r="G3" s="204" t="inlineStr">
@@ -31854,10 +31859,10 @@
       </c>
       <c r="D6" s="209" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E6" s="210" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="268" t="n">
         <v>845200</v>
       </c>
       <c r="F6" s="211" t="n">
@@ -31891,10 +31896,10 @@
       </c>
       <c r="D7" s="216" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E7" s="217" t="n">
+          <t>Operasyonel çıkış/maliyet tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="268" t="n">
         <v>1240000</v>
       </c>
       <c r="F7" s="218" t="n">
@@ -31928,10 +31933,10 @@
       </c>
       <c r="D8" s="209" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E8" s="210" t="n">
+          <t>Ödeme takvimi tahakkuku</t>
+        </is>
+      </c>
+      <c r="E8" s="268" t="n">
         <v>620500</v>
       </c>
       <c r="F8" s="211" t="n">
@@ -31965,10 +31970,10 @@
       </c>
       <c r="D9" s="216" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E9" s="217" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="268" t="n">
         <v>415000</v>
       </c>
       <c r="F9" s="218" t="n">
@@ -32002,10 +32007,10 @@
       </c>
       <c r="D10" s="209" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E10" s="210" t="n">
+          <t>Ana operasyon tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="268" t="n">
         <v>980400</v>
       </c>
       <c r="F10" s="211" t="n">
@@ -32039,10 +32044,10 @@
       </c>
       <c r="D11" s="216" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E11" s="217" t="n">
+          <t>Kredi/taksit karşılığı</t>
+        </is>
+      </c>
+      <c r="E11" s="268" t="n">
         <v>1850000</v>
       </c>
       <c r="F11" s="218" t="n">
@@ -32054,7 +32059,7 @@
       </c>
       <c r="H11" s="216" t="inlineStr">
         <is>
-          <t>Banka Kredi Taksiti</t>
+          <t>Finansman Havuzu</t>
         </is>
       </c>
       <c r="I11" s="222" t="inlineStr">
@@ -32076,10 +32081,10 @@
       </c>
       <c r="D12" s="209" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E12" s="210" t="n">
+          <t>Sabit gider ve yönetim notları</t>
+        </is>
+      </c>
+      <c r="E12" s="268" t="n">
         <v>740000</v>
       </c>
       <c r="F12" s="211" t="n">
@@ -32091,7 +32096,7 @@
       </c>
       <c r="H12" s="209" t="inlineStr">
         <is>
-          <t>Kira &amp; Sabit Gider</t>
+          <t>Genel Yönetim</t>
         </is>
       </c>
       <c r="I12" s="213" t="inlineStr">
@@ -32113,10 +32118,10 @@
       </c>
       <c r="D13" s="216" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E13" s="217" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="268" t="n">
         <v>520800</v>
       </c>
       <c r="F13" s="218" t="n">
@@ -32150,10 +32155,10 @@
       </c>
       <c r="D14" s="209" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E14" s="210" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="268" t="n">
         <v>1120000</v>
       </c>
       <c r="F14" s="211" t="n">
@@ -32187,10 +32192,10 @@
       </c>
       <c r="D15" s="216" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E15" s="217" t="n">
+          <t>Operasyonel çıkış tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="268" t="n">
         <v>890000</v>
       </c>
       <c r="F15" s="218" t="n">
@@ -32274,14 +32279,14 @@
     <row r="2">
       <c r="B2" s="225" t="inlineStr">
         <is>
-          <t>AYLIK PATRON FINANS PANELI — YÖNETİM VE KARAR SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+          <t>AYLIK PATRON FINANS PANELI — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="226" t="inlineStr">
         <is>
-          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · KOBİ sahipleri, patronlar, genel müdürler, finans yöneticileri, mali müşavirler</t>
         </is>
       </c>
     </row>
@@ -32360,10 +32365,9 @@
       </c>
       <c r="C9" s="166" t="n"/>
       <c r="D9" s="166" t="n"/>
-      <c r="E9" s="233" t="inlineStr">
-        <is>
-          <t>₺4.280.000</t>
-        </is>
+      <c r="E9" s="269">
+        <f>PANO!B7*0.8*0.22</f>
+        <v/>
       </c>
       <c r="F9" s="166" t="n"/>
       <c r="H9" s="230" t="inlineStr">
@@ -32373,10 +32377,9 @@
       </c>
       <c r="I9" s="166" t="n"/>
       <c r="J9" s="166" t="n"/>
-      <c r="K9" s="233" t="inlineStr">
-        <is>
-          <t>₺12.450.000</t>
-        </is>
+      <c r="K9" s="269">
+        <f>PANO!H7</f>
+        <v/>
       </c>
       <c r="L9" s="166" t="n"/>
     </row>
@@ -32388,10 +32391,9 @@
       </c>
       <c r="C10" s="166" t="n"/>
       <c r="D10" s="166" t="n"/>
-      <c r="E10" s="234" t="inlineStr">
-        <is>
-          <t>₺1.850.000 (Yeterli)</t>
-        </is>
+      <c r="E10" s="270">
+        <f>PANO!E7*0.75</f>
+        <v/>
       </c>
       <c r="F10" s="166" t="n"/>
       <c r="H10" s="230" t="inlineStr">
@@ -32401,10 +32403,9 @@
       </c>
       <c r="I10" s="166" t="n"/>
       <c r="J10" s="166" t="n"/>
-      <c r="K10" s="234" t="inlineStr">
-        <is>
-          <t>₺8.240.000</t>
-        </is>
+      <c r="K10" s="270">
+        <f>PANO!H7*0.75</f>
+        <v/>
       </c>
       <c r="L10" s="166" t="n"/>
     </row>
@@ -32416,10 +32417,9 @@
       </c>
       <c r="C11" s="166" t="n"/>
       <c r="D11" s="166" t="n"/>
-      <c r="E11" s="234" t="inlineStr">
-        <is>
-          <t>1.28x (Eşik: 1.10x)</t>
-        </is>
+      <c r="E11" s="271">
+        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <v/>
       </c>
       <c r="F11" s="166" t="n"/>
       <c r="H11" s="230" t="inlineStr">

--- a/EXCELARSIV_PRODUCTS/aylik-patron-finans-paneli/AylikPatronFinansPaneli.xlsx
+++ b/EXCELARSIV_PRODUCTS/aylik-patron-finans-paneli/AylikPatronFinansPaneli.xlsx
@@ -159,7 +159,7 @@
     <numFmt numFmtId="170" formatCode="₺#,##0"/>
     <numFmt numFmtId="171" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="101">
+  <fonts count="103">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -794,8 +794,20 @@
       <color rgb="FFA32D2D"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
@@ -979,6 +991,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF0E6F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
   </fills>
@@ -1355,7 +1373,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="272">
+  <cellXfs count="292">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2072,6 +2090,30 @@
     </xf>
     <xf numFmtId="171" fontId="83" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4026,20 +4068,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="70" min="1" max="1"/>
-    <col width="78" customWidth="1" style="70" min="2" max="2"/>
+    <col width="147.5" customWidth="1" style="70" min="2" max="2"/>
+    <col width="13" customWidth="1" style="70" min="3" max="3"/>
+    <col width="13" customWidth="1" style="70" min="4" max="4"/>
+    <col width="13" customWidth="1" style="70" min="5" max="5"/>
+    <col width="13" customWidth="1" style="70" min="6" max="6"/>
+    <col width="13" customWidth="1" style="70" min="7" max="7"/>
+    <col width="13" customWidth="1" style="70" min="8" max="8"/>
+    <col width="13" customWidth="1" style="70" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="70">
-      <c r="A1" s="238" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="70">
+      <c r="A1" s="272" t="inlineStr">
         <is>
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="273" t="n"/>
+      <c r="C1" s="273" t="n"/>
+      <c r="D1" s="273" t="n"/>
+      <c r="E1" s="273" t="n"/>
+      <c r="F1" s="273" t="n"/>
+      <c r="G1" s="273" t="n"/>
+      <c r="H1" s="273" t="n"/>
+      <c r="I1" s="273" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="70">
       <c r="A3" s="239" t="inlineStr">
         <is>
@@ -4304,6 +4363,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="16" customHeight="1" s="70">
       <c r="A26" s="242" t="inlineStr">
         <is>
@@ -4402,7 +4462,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4418,17 +4478,35 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="55" customWidth="1" style="96" min="1" max="3"/>
+    <col width="13" customWidth="1" style="70" min="2" max="2"/>
+    <col width="13" customWidth="1" style="70" min="3" max="3"/>
+    <col width="13" customWidth="1" style="70" min="4" max="4"/>
+    <col width="13" customWidth="1" style="70" min="5" max="5"/>
+    <col width="13" customWidth="1" style="70" min="6" max="6"/>
+    <col width="13" customWidth="1" style="70" min="7" max="7"/>
+    <col width="13" customWidth="1" style="70" min="8" max="8"/>
+    <col width="13" customWidth="1" style="70" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="70">
-      <c r="A1" s="97" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="70">
+      <c r="A1" s="272" t="inlineStr">
         <is>
           <t>AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1" s="70">
-      <c r="A3" s="98" t="inlineStr">
+      <c r="B1" s="273" t="n"/>
+      <c r="C1" s="273" t="n"/>
+      <c r="D1" s="273" t="n"/>
+      <c r="E1" s="273" t="n"/>
+      <c r="F1" s="273" t="n"/>
+      <c r="G1" s="273" t="n"/>
+      <c r="H1" s="273" t="n"/>
+      <c r="I1" s="273" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="70">
+      <c r="A3" s="291" t="inlineStr">
         <is>
           <t>İşletmenin finansal durumunu tek sayfada yorumlayan patron paneli</t>
         </is>
@@ -4463,6 +4541,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="70">
       <c r="A10" s="101" t="inlineStr">
         <is>
@@ -4472,6 +4551,7 @@
     </row>
     <row r="11" ht="15" customHeight="1" s="70"/>
     <row r="12" ht="15" customHeight="1" s="70"/>
+    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="70">
       <c r="A14" s="102" t="inlineStr">
         <is>
@@ -4491,12 +4571,12 @@
   <mergeCells count="8">
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A10:J12"/>
     <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A4:C5"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4513,8 +4593,16 @@
   <dimension ref="A1:AN17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="70" customWidth="1" style="96" min="1" max="1"/>
+    <col width="92.5" customWidth="1" style="96" min="1" max="1"/>
     <col width="20" customWidth="1" style="96" min="2" max="2"/>
+    <col width="13" customWidth="1" style="70" min="3" max="3"/>
+    <col width="13" customWidth="1" style="70" min="4" max="4"/>
+    <col width="13" customWidth="1" style="70" min="5" max="5"/>
+    <col width="13" customWidth="1" style="70" min="6" max="6"/>
+    <col width="13" customWidth="1" style="70" min="7" max="7"/>
+    <col width="13" customWidth="1" style="70" min="8" max="8"/>
+    <col width="13" customWidth="1" style="70" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4524,8 +4612,9 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="70">
-      <c r="A3" s="104" t="inlineStr">
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="70">
+      <c r="A3" s="291" t="inlineStr">
         <is>
           <t>Nasıl kullanılır?</t>
         </is>
@@ -4573,6 +4662,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="70">
       <c r="A11" s="106" t="inlineStr">
         <is>
@@ -4608,6 +4698,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="19.5" customHeight="1" s="70">
       <c r="A17" s="107" t="inlineStr">
         <is>
@@ -4617,7 +4708,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A8:AN8"/>
     <mergeCell ref="A6:AN6"/>
     <mergeCell ref="A12:AN12"/>
@@ -4625,6 +4716,7 @@
     <mergeCell ref="A15:AN15"/>
     <mergeCell ref="A7:AN7"/>
     <mergeCell ref="A5:AN5"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A13:AN13"/>
     <mergeCell ref="A14:AN14"/>
     <mergeCell ref="A17:AN17"/>
@@ -4645,25 +4737,36 @@
   <dimension ref="A1:AN1006"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="16" customWidth="1" style="96" min="1" max="1"/>
+    <col width="16.5" customWidth="1" style="96" min="1" max="1"/>
     <col width="28" customWidth="1" style="96" min="2" max="2"/>
     <col width="10" customWidth="1" style="96" min="3" max="3"/>
     <col width="16" customWidth="1" style="96" min="4" max="4"/>
-    <col width="10" customWidth="1" style="96" min="5" max="5"/>
-    <col width="16" customWidth="1" style="96" min="6" max="6"/>
-    <col width="22" customWidth="1" style="96" min="7" max="7"/>
-    <col width="16" customWidth="1" style="96" min="8" max="9"/>
+    <col width="13.5" customWidth="1" style="96" min="5" max="5"/>
+    <col width="22.5" customWidth="1" style="96" min="6" max="6"/>
+    <col width="26.5" customWidth="1" style="96" min="7" max="7"/>
+    <col width="19.5" customWidth="1" style="96" min="8" max="9"/>
+    <col width="19.5" customWidth="1" style="70" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="70">
-      <c r="A1" s="108" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="70">
+      <c r="A1" s="272" t="inlineStr">
         <is>
           <t>AYLIK GELIR GIDER — AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="35.25" customHeight="1" s="70">
-      <c r="A3" s="109" t="inlineStr">
+      <c r="B1" s="273" t="n"/>
+      <c r="C1" s="273" t="n"/>
+      <c r="D1" s="273" t="n"/>
+      <c r="E1" s="273" t="n"/>
+      <c r="F1" s="273" t="n"/>
+      <c r="G1" s="273" t="n"/>
+      <c r="H1" s="273" t="n"/>
+      <c r="I1" s="273" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="70">
+      <c r="A3" s="291" t="inlineStr">
         <is>
           <t>Aylık Gelir ve Giderler</t>
         </is>
@@ -13633,6 +13736,7 @@
       <c r="E1004" s="115" t="n"/>
       <c r="G1004" s="115" t="n"/>
     </row>
+    <row r="1005"/>
     <row r="1006" ht="19.5" customHeight="1" s="70">
       <c r="A1006" s="107" t="inlineStr">
         <is>
@@ -13642,9 +13746,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A1006:AN1006"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D1004">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="10" text="" percent="0" bottom="0">
@@ -13701,25 +13806,34 @@
   <dimension ref="A1:AN1006"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="10" customWidth="1" style="96" min="1" max="1"/>
+    <col width="10.5" customWidth="1" style="96" min="1" max="1"/>
     <col width="24" customWidth="1" style="96" min="2" max="2"/>
-    <col width="28" customWidth="1" style="96" min="3" max="3"/>
-    <col width="16" customWidth="1" style="96" min="4" max="4"/>
-    <col width="12" customWidth="1" style="96" min="5" max="5"/>
-    <col width="14" customWidth="1" style="96" min="6" max="6"/>
-    <col width="12" customWidth="1" style="96" min="7" max="7"/>
+    <col width="33.5" customWidth="1" style="96" min="3" max="3"/>
+    <col width="21.5" customWidth="1" style="96" min="4" max="4"/>
+    <col width="16.5" customWidth="1" style="96" min="5" max="5"/>
+    <col width="23.5" customWidth="1" style="96" min="6" max="6"/>
+    <col width="14.5" customWidth="1" style="96" min="7" max="7"/>
     <col width="22" customWidth="1" style="96" min="8" max="8"/>
+    <col width="13" customWidth="1" style="70" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="70">
-      <c r="A1" s="108" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="70">
+      <c r="A1" s="272" t="inlineStr">
         <is>
           <t>BORC VE ALACAK — AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="87" customHeight="1" s="70">
-      <c r="A3" s="109" t="inlineStr">
+      <c r="B1" s="273" t="n"/>
+      <c r="C1" s="273" t="n"/>
+      <c r="D1" s="273" t="n"/>
+      <c r="E1" s="273" t="n"/>
+      <c r="F1" s="273" t="n"/>
+      <c r="G1" s="273" t="n"/>
+      <c r="H1" s="273" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="70">
+      <c r="A3" s="291" t="inlineStr">
         <is>
           <t>Borç, Taksit ve Alacaklar</t>
         </is>
@@ -23091,6 +23205,7 @@
       <c r="F1004" s="115" t="n"/>
       <c r="H1004" s="115" t="n"/>
     </row>
+    <row r="1005"/>
     <row r="1006" ht="19.5" customHeight="1" s="70">
       <c r="A1006" s="107" t="inlineStr">
         <is>
@@ -23100,9 +23215,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
     <mergeCell ref="A1006:AN1006"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D1004">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="10" text="" percent="0" bottom="0">
@@ -23162,22 +23278,33 @@
     <col width="45" customWidth="1" style="96" min="1" max="1"/>
     <col width="24" customWidth="1" style="96" min="2" max="2"/>
     <col width="16" customWidth="1" style="96" min="3" max="4"/>
+    <col width="13" customWidth="1" style="70" min="4" max="4"/>
     <col width="18" customWidth="1" style="96" min="5" max="5"/>
     <col width="14" customWidth="1" style="96" min="6" max="6"/>
+    <col width="13" customWidth="1" style="70" min="7" max="7"/>
     <col width="32" customWidth="1" style="96" min="8" max="8"/>
     <col width="16" customWidth="1" style="96" min="9" max="9"/>
     <col width="70" customWidth="1" style="96" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="70">
-      <c r="A1" s="108" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="70">
+      <c r="A1" s="272" t="inlineStr">
         <is>
           <t>FINANS MOTORU — AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1" s="70">
-      <c r="A3" s="121" t="inlineStr">
+      <c r="B1" s="273" t="n"/>
+      <c r="C1" s="273" t="n"/>
+      <c r="D1" s="273" t="n"/>
+      <c r="E1" s="273" t="n"/>
+      <c r="F1" s="273" t="n"/>
+      <c r="G1" s="273" t="n"/>
+      <c r="H1" s="273" t="n"/>
+      <c r="I1" s="273" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="70">
+      <c r="A3" s="291" t="inlineStr">
         <is>
           <t>Finans Motoru — Oran ve Sinyaller</t>
         </is>
@@ -23190,6 +23317,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="70">
       <c r="A6" s="122" t="inlineStr">
         <is>
@@ -23355,6 +23483,7 @@
         <v/>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="15" customHeight="1" s="70">
       <c r="H22" s="125" t="inlineStr">
         <is>
@@ -27008,6 +27137,7 @@
     <row r="1024" ht="15" customHeight="1" s="70">
       <c r="A1024" s="115" t="n"/>
     </row>
+    <row r="1025"/>
     <row r="1026" ht="19.5" customHeight="1" s="70">
       <c r="A1026" s="107" t="inlineStr">
         <is>
@@ -27017,9 +27147,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A1026:AN1026"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:B20">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="10" text="" percent="0" bottom="0">
@@ -27072,17 +27203,34 @@
   <cols>
     <col width="45" customWidth="1" style="96" min="1" max="1"/>
     <col width="55" customWidth="1" style="96" min="2" max="2"/>
+    <col width="13" customWidth="1" style="70" min="3" max="3"/>
+    <col width="13" customWidth="1" style="70" min="4" max="4"/>
+    <col width="13" customWidth="1" style="70" min="5" max="5"/>
+    <col width="13" customWidth="1" style="70" min="6" max="6"/>
+    <col width="13" customWidth="1" style="70" min="7" max="7"/>
+    <col width="13" customWidth="1" style="70" min="8" max="8"/>
+    <col width="13" customWidth="1" style="70" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="70">
-      <c r="A1" s="108" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="70">
+      <c r="A1" s="272" t="inlineStr">
         <is>
           <t>KONTROLLER — AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1" s="70">
-      <c r="A3" s="104" t="inlineStr">
+      <c r="B1" s="273" t="n"/>
+      <c r="C1" s="273" t="n"/>
+      <c r="D1" s="273" t="n"/>
+      <c r="E1" s="273" t="n"/>
+      <c r="F1" s="273" t="n"/>
+      <c r="G1" s="273" t="n"/>
+      <c r="H1" s="273" t="n"/>
+      <c r="I1" s="273" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="70">
+      <c r="A3" s="291" t="inlineStr">
         <is>
           <t>Giriş Kalite Kontrolleri</t>
         </is>
@@ -27095,6 +27243,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="70">
       <c r="A6" s="127" t="inlineStr">
         <is>
@@ -27183,6 +27332,7 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="70">
       <c r="A15" s="126" t="inlineStr">
         <is>
@@ -27241,6 +27391,7 @@
         <v/>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="19.5" customHeight="1" s="70">
       <c r="A22" s="107" t="inlineStr">
         <is>
@@ -27250,9 +27401,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A22:AN22"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:B15">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="13" text="" percent="0" bottom="0">
@@ -27316,17 +27468,34 @@
   <cols>
     <col width="45" customWidth="1" style="96" min="1" max="1"/>
     <col width="60" customWidth="1" style="96" min="2" max="2"/>
+    <col width="13" customWidth="1" style="70" min="3" max="3"/>
+    <col width="13" customWidth="1" style="70" min="4" max="4"/>
+    <col width="13" customWidth="1" style="70" min="5" max="5"/>
+    <col width="13" customWidth="1" style="70" min="6" max="6"/>
+    <col width="13" customWidth="1" style="70" min="7" max="7"/>
+    <col width="13" customWidth="1" style="70" min="8" max="8"/>
+    <col width="13" customWidth="1" style="70" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="70">
-      <c r="A1" s="108" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="70">
+      <c r="A1" s="272" t="inlineStr">
         <is>
           <t>KARAR — AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1" s="70">
-      <c r="A3" s="104" t="inlineStr">
+      <c r="B1" s="273" t="n"/>
+      <c r="C1" s="273" t="n"/>
+      <c r="D1" s="273" t="n"/>
+      <c r="E1" s="273" t="n"/>
+      <c r="F1" s="273" t="n"/>
+      <c r="G1" s="273" t="n"/>
+      <c r="H1" s="273" t="n"/>
+      <c r="I1" s="273" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="70">
+      <c r="A3" s="291" t="inlineStr">
         <is>
           <t>Karar Kapısı — Finansal Sağlık</t>
         </is>
@@ -27339,6 +27508,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="70">
       <c r="A6" s="127" t="inlineStr">
         <is>
@@ -27383,6 +27553,7 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="21" customHeight="1" s="70">
       <c r="A11" s="139" t="inlineStr">
         <is>
@@ -27405,6 +27576,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="70">
       <c r="A14" s="126" t="inlineStr">
         <is>
@@ -27445,6 +27617,7 @@
         <v/>
       </c>
     </row>
+    <row r="18"/>
     <row r="19" ht="19.5" customHeight="1" s="70">
       <c r="A19" s="107" t="inlineStr">
         <is>
@@ -27454,13 +27627,14 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B15:J15"/>
     <mergeCell ref="B16:J16"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="B17:J17"/>
     <mergeCell ref="A19:AN19"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="B12:J12"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="B11">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="14" text="" percent="0" bottom="0">
@@ -27499,17 +27673,33 @@
     <col width="45" customWidth="1" style="96" min="1" max="1"/>
     <col width="30" customWidth="1" style="96" min="2" max="2"/>
     <col width="16" customWidth="1" style="96" min="3" max="3"/>
+    <col width="13" customWidth="1" style="70" min="4" max="4"/>
+    <col width="13" customWidth="1" style="70" min="5" max="5"/>
+    <col width="13" customWidth="1" style="70" min="6" max="6"/>
+    <col width="13" customWidth="1" style="70" min="7" max="7"/>
+    <col width="13" customWidth="1" style="70" min="8" max="8"/>
+    <col width="13" customWidth="1" style="70" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="70">
-      <c r="A1" s="108" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="70">
+      <c r="A1" s="272" t="inlineStr">
         <is>
           <t>SENARYO DUYARLILIK — AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1" s="70">
-      <c r="A3" s="104" t="inlineStr">
+      <c r="B1" s="273" t="n"/>
+      <c r="C1" s="273" t="n"/>
+      <c r="D1" s="273" t="n"/>
+      <c r="E1" s="273" t="n"/>
+      <c r="F1" s="273" t="n"/>
+      <c r="G1" s="273" t="n"/>
+      <c r="H1" s="273" t="n"/>
+      <c r="I1" s="273" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="70">
+      <c r="A3" s="291" t="inlineStr">
         <is>
           <t>Senaryo ve Duyarlılık Analizi</t>
         </is>
@@ -27522,6 +27712,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="70">
       <c r="A6" s="128" t="inlineStr">
         <is>
@@ -27601,6 +27792,7 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="70">
       <c r="A11" s="126" t="inlineStr">
         <is>
@@ -27652,6 +27844,7 @@
         <v/>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="15" customHeight="1" s="70">
       <c r="A17" s="122" t="inlineStr">
         <is>
@@ -27674,6 +27867,7 @@
         <v/>
       </c>
     </row>
+    <row r="19"/>
     <row r="20" ht="19.5" customHeight="1" s="70">
       <c r="A20" s="107" t="inlineStr">
         <is>
@@ -27683,9 +27877,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A20:AN20"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="D7:D9">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="10" text="" percent="0" bottom="0">
@@ -27714,14 +27909,30 @@
   <cols>
     <col width="45" customWidth="1" style="96" min="1" max="1"/>
     <col width="40" customWidth="1" style="96" min="2" max="2"/>
+    <col width="13" customWidth="1" style="70" min="3" max="3"/>
+    <col width="13" customWidth="1" style="70" min="4" max="4"/>
+    <col width="13" customWidth="1" style="70" min="5" max="5"/>
+    <col width="13" customWidth="1" style="70" min="6" max="6"/>
+    <col width="13" customWidth="1" style="70" min="7" max="7"/>
+    <col width="13" customWidth="1" style="70" min="8" max="8"/>
+    <col width="13" customWidth="1" style="70" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="70">
-      <c r="A1" s="151" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="70">
+      <c r="A1" s="272" t="inlineStr">
         <is>
           <t>AYLIK PATRON FİNANS PANELİ — YÖNETİCİ ÖZETİ</t>
         </is>
       </c>
+      <c r="B1" s="273" t="n"/>
+      <c r="C1" s="273" t="n"/>
+      <c r="D1" s="273" t="n"/>
+      <c r="E1" s="273" t="n"/>
+      <c r="F1" s="273" t="n"/>
+      <c r="G1" s="273" t="n"/>
+      <c r="H1" s="273" t="n"/>
+      <c r="I1" s="273" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1" s="70">
       <c r="A2" s="152">
@@ -27729,6 +27940,7 @@
         <v/>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="17.25" customHeight="1" s="70">
       <c r="A4" s="126" t="inlineStr">
         <is>
@@ -27744,6 +27956,7 @@
         <v/>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="70">
       <c r="A6" s="127" t="inlineStr">
         <is>
@@ -27843,6 +28056,7 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="70">
       <c r="A16" s="146" t="inlineStr">
         <is>
@@ -27878,6 +28092,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="15" customHeight="1" s="70">
       <c r="A22" s="146" t="inlineStr">
         <is>
@@ -27903,6 +28118,7 @@
         <v/>
       </c>
     </row>
+    <row r="26"/>
     <row r="27" ht="15" customHeight="1" s="70">
       <c r="A27" s="153" t="inlineStr">
         <is>
@@ -27920,9 +28136,9 @@
     <mergeCell ref="A19:L19"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A17:L17"/>
     <mergeCell ref="A18:L18"/>
-    <mergeCell ref="A1:AN1"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.5"/>
@@ -27947,24 +28163,36 @@
   <dimension ref="A1:AN1006"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="16" customWidth="1" style="96" min="1" max="1"/>
+    <col width="16.5" customWidth="1" style="96" min="1" max="1"/>
     <col width="28" customWidth="1" style="96" min="2" max="2"/>
     <col width="10" customWidth="1" style="96" min="3" max="3"/>
     <col width="16" customWidth="1" style="96" min="4" max="4"/>
-    <col width="10" customWidth="1" style="96" min="5" max="5"/>
-    <col width="16" customWidth="1" style="96" min="6" max="6"/>
+    <col width="13.5" customWidth="1" style="96" min="5" max="5"/>
+    <col width="22.5" customWidth="1" style="96" min="6" max="6"/>
     <col width="22" customWidth="1" style="96" min="7" max="7"/>
+    <col width="13" customWidth="1" style="70" min="8" max="8"/>
+    <col width="13" customWidth="1" style="70" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="70">
-      <c r="A1" s="108" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="70">
+      <c r="A1" s="272" t="inlineStr">
         <is>
           <t>ORNEK VERI — AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="70">
-      <c r="A3" s="126" t="inlineStr">
+      <c r="B1" s="273" t="n"/>
+      <c r="C1" s="273" t="n"/>
+      <c r="D1" s="273" t="n"/>
+      <c r="E1" s="273" t="n"/>
+      <c r="F1" s="273" t="n"/>
+      <c r="G1" s="273" t="n"/>
+      <c r="H1" s="273" t="n"/>
+      <c r="I1" s="273" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="70">
+      <c r="A3" s="291" t="inlineStr">
         <is>
           <t>Örnek Veri (Demo)</t>
         </is>
@@ -28675,6 +28903,985 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="213"/>
+    <row r="214"/>
+    <row r="215"/>
+    <row r="216"/>
+    <row r="217"/>
+    <row r="218"/>
+    <row r="219"/>
+    <row r="220"/>
+    <row r="221"/>
+    <row r="222"/>
+    <row r="223"/>
+    <row r="224"/>
+    <row r="225"/>
+    <row r="226"/>
+    <row r="227"/>
+    <row r="228"/>
+    <row r="229"/>
+    <row r="230"/>
+    <row r="231"/>
+    <row r="232"/>
+    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236"/>
+    <row r="237"/>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240"/>
+    <row r="241"/>
+    <row r="242"/>
+    <row r="243"/>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
+    <row r="266"/>
+    <row r="267"/>
+    <row r="268"/>
+    <row r="269"/>
+    <row r="270"/>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275"/>
+    <row r="276"/>
+    <row r="277"/>
+    <row r="278"/>
+    <row r="279"/>
+    <row r="280"/>
+    <row r="281"/>
+    <row r="282"/>
+    <row r="283"/>
+    <row r="284"/>
+    <row r="285"/>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288"/>
+    <row r="289"/>
+    <row r="290"/>
+    <row r="291"/>
+    <row r="292"/>
+    <row r="293"/>
+    <row r="294"/>
+    <row r="295"/>
+    <row r="296"/>
+    <row r="297"/>
+    <row r="298"/>
+    <row r="299"/>
+    <row r="300"/>
+    <row r="301"/>
+    <row r="302"/>
+    <row r="303"/>
+    <row r="304"/>
+    <row r="305"/>
+    <row r="306"/>
+    <row r="307"/>
+    <row r="308"/>
+    <row r="309"/>
+    <row r="310"/>
+    <row r="311"/>
+    <row r="312"/>
+    <row r="313"/>
+    <row r="314"/>
+    <row r="315"/>
+    <row r="316"/>
+    <row r="317"/>
+    <row r="318"/>
+    <row r="319"/>
+    <row r="320"/>
+    <row r="321"/>
+    <row r="322"/>
+    <row r="323"/>
+    <row r="324"/>
+    <row r="325"/>
+    <row r="326"/>
+    <row r="327"/>
+    <row r="328"/>
+    <row r="329"/>
+    <row r="330"/>
+    <row r="331"/>
+    <row r="332"/>
+    <row r="333"/>
+    <row r="334"/>
+    <row r="335"/>
+    <row r="336"/>
+    <row r="337"/>
+    <row r="338"/>
+    <row r="339"/>
+    <row r="340"/>
+    <row r="341"/>
+    <row r="342"/>
+    <row r="343"/>
+    <row r="344"/>
+    <row r="345"/>
+    <row r="346"/>
+    <row r="347"/>
+    <row r="348"/>
+    <row r="349"/>
+    <row r="350"/>
+    <row r="351"/>
+    <row r="352"/>
+    <row r="353"/>
+    <row r="354"/>
+    <row r="355"/>
+    <row r="356"/>
+    <row r="357"/>
+    <row r="358"/>
+    <row r="359"/>
+    <row r="360"/>
+    <row r="361"/>
+    <row r="362"/>
+    <row r="363"/>
+    <row r="364"/>
+    <row r="365"/>
+    <row r="366"/>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369"/>
+    <row r="370"/>
+    <row r="371"/>
+    <row r="372"/>
+    <row r="373"/>
+    <row r="374"/>
+    <row r="375"/>
+    <row r="376"/>
+    <row r="377"/>
+    <row r="378"/>
+    <row r="379"/>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382"/>
+    <row r="383"/>
+    <row r="384"/>
+    <row r="385"/>
+    <row r="386"/>
+    <row r="387"/>
+    <row r="388"/>
+    <row r="389"/>
+    <row r="390"/>
+    <row r="391"/>
+    <row r="392"/>
+    <row r="393"/>
+    <row r="394"/>
+    <row r="395"/>
+    <row r="396"/>
+    <row r="397"/>
+    <row r="398"/>
+    <row r="399"/>
+    <row r="400"/>
+    <row r="401"/>
+    <row r="402"/>
+    <row r="403"/>
+    <row r="404"/>
+    <row r="405"/>
+    <row r="406"/>
+    <row r="407"/>
+    <row r="408"/>
+    <row r="409"/>
+    <row r="410"/>
+    <row r="411"/>
+    <row r="412"/>
+    <row r="413"/>
+    <row r="414"/>
+    <row r="415"/>
+    <row r="416"/>
+    <row r="417"/>
+    <row r="418"/>
+    <row r="419"/>
+    <row r="420"/>
+    <row r="421"/>
+    <row r="422"/>
+    <row r="423"/>
+    <row r="424"/>
+    <row r="425"/>
+    <row r="426"/>
+    <row r="427"/>
+    <row r="428"/>
+    <row r="429"/>
+    <row r="430"/>
+    <row r="431"/>
+    <row r="432"/>
+    <row r="433"/>
+    <row r="434"/>
+    <row r="435"/>
+    <row r="436"/>
+    <row r="437"/>
+    <row r="438"/>
+    <row r="439"/>
+    <row r="440"/>
+    <row r="441"/>
+    <row r="442"/>
+    <row r="443"/>
+    <row r="444"/>
+    <row r="445"/>
+    <row r="446"/>
+    <row r="447"/>
+    <row r="448"/>
+    <row r="449"/>
+    <row r="450"/>
+    <row r="451"/>
+    <row r="452"/>
+    <row r="453"/>
+    <row r="454"/>
+    <row r="455"/>
+    <row r="456"/>
+    <row r="457"/>
+    <row r="458"/>
+    <row r="459"/>
+    <row r="460"/>
+    <row r="461"/>
+    <row r="462"/>
+    <row r="463"/>
+    <row r="464"/>
+    <row r="465"/>
+    <row r="466"/>
+    <row r="467"/>
+    <row r="468"/>
+    <row r="469"/>
+    <row r="470"/>
+    <row r="471"/>
+    <row r="472"/>
+    <row r="473"/>
+    <row r="474"/>
+    <row r="475"/>
+    <row r="476"/>
+    <row r="477"/>
+    <row r="478"/>
+    <row r="479"/>
+    <row r="480"/>
+    <row r="481"/>
+    <row r="482"/>
+    <row r="483"/>
+    <row r="484"/>
+    <row r="485"/>
+    <row r="486"/>
+    <row r="487"/>
+    <row r="488"/>
+    <row r="489"/>
+    <row r="490"/>
+    <row r="491"/>
+    <row r="492"/>
+    <row r="493"/>
+    <row r="494"/>
+    <row r="495"/>
+    <row r="496"/>
+    <row r="497"/>
+    <row r="498"/>
+    <row r="499"/>
+    <row r="500"/>
+    <row r="501"/>
+    <row r="502"/>
+    <row r="503"/>
+    <row r="504"/>
+    <row r="505"/>
+    <row r="506"/>
+    <row r="507"/>
+    <row r="508"/>
+    <row r="509"/>
+    <row r="510"/>
+    <row r="511"/>
+    <row r="512"/>
+    <row r="513"/>
+    <row r="514"/>
+    <row r="515"/>
+    <row r="516"/>
+    <row r="517"/>
+    <row r="518"/>
+    <row r="519"/>
+    <row r="520"/>
+    <row r="521"/>
+    <row r="522"/>
+    <row r="523"/>
+    <row r="524"/>
+    <row r="525"/>
+    <row r="526"/>
+    <row r="527"/>
+    <row r="528"/>
+    <row r="529"/>
+    <row r="530"/>
+    <row r="531"/>
+    <row r="532"/>
+    <row r="533"/>
+    <row r="534"/>
+    <row r="535"/>
+    <row r="536"/>
+    <row r="537"/>
+    <row r="538"/>
+    <row r="539"/>
+    <row r="540"/>
+    <row r="541"/>
+    <row r="542"/>
+    <row r="543"/>
+    <row r="544"/>
+    <row r="545"/>
+    <row r="546"/>
+    <row r="547"/>
+    <row r="548"/>
+    <row r="549"/>
+    <row r="550"/>
+    <row r="551"/>
+    <row r="552"/>
+    <row r="553"/>
+    <row r="554"/>
+    <row r="555"/>
+    <row r="556"/>
+    <row r="557"/>
+    <row r="558"/>
+    <row r="559"/>
+    <row r="560"/>
+    <row r="561"/>
+    <row r="562"/>
+    <row r="563"/>
+    <row r="564"/>
+    <row r="565"/>
+    <row r="566"/>
+    <row r="567"/>
+    <row r="568"/>
+    <row r="569"/>
+    <row r="570"/>
+    <row r="571"/>
+    <row r="572"/>
+    <row r="573"/>
+    <row r="574"/>
+    <row r="575"/>
+    <row r="576"/>
+    <row r="577"/>
+    <row r="578"/>
+    <row r="579"/>
+    <row r="580"/>
+    <row r="581"/>
+    <row r="582"/>
+    <row r="583"/>
+    <row r="584"/>
+    <row r="585"/>
+    <row r="586"/>
+    <row r="587"/>
+    <row r="588"/>
+    <row r="589"/>
+    <row r="590"/>
+    <row r="591"/>
+    <row r="592"/>
+    <row r="593"/>
+    <row r="594"/>
+    <row r="595"/>
+    <row r="596"/>
+    <row r="597"/>
+    <row r="598"/>
+    <row r="599"/>
+    <row r="600"/>
+    <row r="601"/>
+    <row r="602"/>
+    <row r="603"/>
+    <row r="604"/>
+    <row r="605"/>
+    <row r="606"/>
+    <row r="607"/>
+    <row r="608"/>
+    <row r="609"/>
+    <row r="610"/>
+    <row r="611"/>
+    <row r="612"/>
+    <row r="613"/>
+    <row r="614"/>
+    <row r="615"/>
+    <row r="616"/>
+    <row r="617"/>
+    <row r="618"/>
+    <row r="619"/>
+    <row r="620"/>
+    <row r="621"/>
+    <row r="622"/>
+    <row r="623"/>
+    <row r="624"/>
+    <row r="625"/>
+    <row r="626"/>
+    <row r="627"/>
+    <row r="628"/>
+    <row r="629"/>
+    <row r="630"/>
+    <row r="631"/>
+    <row r="632"/>
+    <row r="633"/>
+    <row r="634"/>
+    <row r="635"/>
+    <row r="636"/>
+    <row r="637"/>
+    <row r="638"/>
+    <row r="639"/>
+    <row r="640"/>
+    <row r="641"/>
+    <row r="642"/>
+    <row r="643"/>
+    <row r="644"/>
+    <row r="645"/>
+    <row r="646"/>
+    <row r="647"/>
+    <row r="648"/>
+    <row r="649"/>
+    <row r="650"/>
+    <row r="651"/>
+    <row r="652"/>
+    <row r="653"/>
+    <row r="654"/>
+    <row r="655"/>
+    <row r="656"/>
+    <row r="657"/>
+    <row r="658"/>
+    <row r="659"/>
+    <row r="660"/>
+    <row r="661"/>
+    <row r="662"/>
+    <row r="663"/>
+    <row r="664"/>
+    <row r="665"/>
+    <row r="666"/>
+    <row r="667"/>
+    <row r="668"/>
+    <row r="669"/>
+    <row r="670"/>
+    <row r="671"/>
+    <row r="672"/>
+    <row r="673"/>
+    <row r="674"/>
+    <row r="675"/>
+    <row r="676"/>
+    <row r="677"/>
+    <row r="678"/>
+    <row r="679"/>
+    <row r="680"/>
+    <row r="681"/>
+    <row r="682"/>
+    <row r="683"/>
+    <row r="684"/>
+    <row r="685"/>
+    <row r="686"/>
+    <row r="687"/>
+    <row r="688"/>
+    <row r="689"/>
+    <row r="690"/>
+    <row r="691"/>
+    <row r="692"/>
+    <row r="693"/>
+    <row r="694"/>
+    <row r="695"/>
+    <row r="696"/>
+    <row r="697"/>
+    <row r="698"/>
+    <row r="699"/>
+    <row r="700"/>
+    <row r="701"/>
+    <row r="702"/>
+    <row r="703"/>
+    <row r="704"/>
+    <row r="705"/>
+    <row r="706"/>
+    <row r="707"/>
+    <row r="708"/>
+    <row r="709"/>
+    <row r="710"/>
+    <row r="711"/>
+    <row r="712"/>
+    <row r="713"/>
+    <row r="714"/>
+    <row r="715"/>
+    <row r="716"/>
+    <row r="717"/>
+    <row r="718"/>
+    <row r="719"/>
+    <row r="720"/>
+    <row r="721"/>
+    <row r="722"/>
+    <row r="723"/>
+    <row r="724"/>
+    <row r="725"/>
+    <row r="726"/>
+    <row r="727"/>
+    <row r="728"/>
+    <row r="729"/>
+    <row r="730"/>
+    <row r="731"/>
+    <row r="732"/>
+    <row r="733"/>
+    <row r="734"/>
+    <row r="735"/>
+    <row r="736"/>
+    <row r="737"/>
+    <row r="738"/>
+    <row r="739"/>
+    <row r="740"/>
+    <row r="741"/>
+    <row r="742"/>
+    <row r="743"/>
+    <row r="744"/>
+    <row r="745"/>
+    <row r="746"/>
+    <row r="747"/>
+    <row r="748"/>
+    <row r="749"/>
+    <row r="750"/>
+    <row r="751"/>
+    <row r="752"/>
+    <row r="753"/>
+    <row r="754"/>
+    <row r="755"/>
+    <row r="756"/>
+    <row r="757"/>
+    <row r="758"/>
+    <row r="759"/>
+    <row r="760"/>
+    <row r="761"/>
+    <row r="762"/>
+    <row r="763"/>
+    <row r="764"/>
+    <row r="765"/>
+    <row r="766"/>
+    <row r="767"/>
+    <row r="768"/>
+    <row r="769"/>
+    <row r="770"/>
+    <row r="771"/>
+    <row r="772"/>
+    <row r="773"/>
+    <row r="774"/>
+    <row r="775"/>
+    <row r="776"/>
+    <row r="777"/>
+    <row r="778"/>
+    <row r="779"/>
+    <row r="780"/>
+    <row r="781"/>
+    <row r="782"/>
+    <row r="783"/>
+    <row r="784"/>
+    <row r="785"/>
+    <row r="786"/>
+    <row r="787"/>
+    <row r="788"/>
+    <row r="789"/>
+    <row r="790"/>
+    <row r="791"/>
+    <row r="792"/>
+    <row r="793"/>
+    <row r="794"/>
+    <row r="795"/>
+    <row r="796"/>
+    <row r="797"/>
+    <row r="798"/>
+    <row r="799"/>
+    <row r="800"/>
+    <row r="801"/>
+    <row r="802"/>
+    <row r="803"/>
+    <row r="804"/>
+    <row r="805"/>
+    <row r="806"/>
+    <row r="807"/>
+    <row r="808"/>
+    <row r="809"/>
+    <row r="810"/>
+    <row r="811"/>
+    <row r="812"/>
+    <row r="813"/>
+    <row r="814"/>
+    <row r="815"/>
+    <row r="816"/>
+    <row r="817"/>
+    <row r="818"/>
+    <row r="819"/>
+    <row r="820"/>
+    <row r="821"/>
+    <row r="822"/>
+    <row r="823"/>
+    <row r="824"/>
+    <row r="825"/>
+    <row r="826"/>
+    <row r="827"/>
+    <row r="828"/>
+    <row r="829"/>
+    <row r="830"/>
+    <row r="831"/>
+    <row r="832"/>
+    <row r="833"/>
+    <row r="834"/>
+    <row r="835"/>
+    <row r="836"/>
+    <row r="837"/>
+    <row r="838"/>
+    <row r="839"/>
+    <row r="840"/>
+    <row r="841"/>
+    <row r="842"/>
+    <row r="843"/>
+    <row r="844"/>
+    <row r="845"/>
+    <row r="846"/>
+    <row r="847"/>
+    <row r="848"/>
+    <row r="849"/>
+    <row r="850"/>
+    <row r="851"/>
+    <row r="852"/>
+    <row r="853"/>
+    <row r="854"/>
+    <row r="855"/>
+    <row r="856"/>
+    <row r="857"/>
+    <row r="858"/>
+    <row r="859"/>
+    <row r="860"/>
+    <row r="861"/>
+    <row r="862"/>
+    <row r="863"/>
+    <row r="864"/>
+    <row r="865"/>
+    <row r="866"/>
+    <row r="867"/>
+    <row r="868"/>
+    <row r="869"/>
+    <row r="870"/>
+    <row r="871"/>
+    <row r="872"/>
+    <row r="873"/>
+    <row r="874"/>
+    <row r="875"/>
+    <row r="876"/>
+    <row r="877"/>
+    <row r="878"/>
+    <row r="879"/>
+    <row r="880"/>
+    <row r="881"/>
+    <row r="882"/>
+    <row r="883"/>
+    <row r="884"/>
+    <row r="885"/>
+    <row r="886"/>
+    <row r="887"/>
+    <row r="888"/>
+    <row r="889"/>
+    <row r="890"/>
+    <row r="891"/>
+    <row r="892"/>
+    <row r="893"/>
+    <row r="894"/>
+    <row r="895"/>
+    <row r="896"/>
+    <row r="897"/>
+    <row r="898"/>
+    <row r="899"/>
+    <row r="900"/>
+    <row r="901"/>
+    <row r="902"/>
+    <row r="903"/>
+    <row r="904"/>
+    <row r="905"/>
+    <row r="906"/>
+    <row r="907"/>
+    <row r="908"/>
+    <row r="909"/>
+    <row r="910"/>
+    <row r="911"/>
+    <row r="912"/>
+    <row r="913"/>
+    <row r="914"/>
+    <row r="915"/>
+    <row r="916"/>
+    <row r="917"/>
+    <row r="918"/>
+    <row r="919"/>
+    <row r="920"/>
+    <row r="921"/>
+    <row r="922"/>
+    <row r="923"/>
+    <row r="924"/>
+    <row r="925"/>
+    <row r="926"/>
+    <row r="927"/>
+    <row r="928"/>
+    <row r="929"/>
+    <row r="930"/>
+    <row r="931"/>
+    <row r="932"/>
+    <row r="933"/>
+    <row r="934"/>
+    <row r="935"/>
+    <row r="936"/>
+    <row r="937"/>
+    <row r="938"/>
+    <row r="939"/>
+    <row r="940"/>
+    <row r="941"/>
+    <row r="942"/>
+    <row r="943"/>
+    <row r="944"/>
+    <row r="945"/>
+    <row r="946"/>
+    <row r="947"/>
+    <row r="948"/>
+    <row r="949"/>
+    <row r="950"/>
+    <row r="951"/>
+    <row r="952"/>
+    <row r="953"/>
+    <row r="954"/>
+    <row r="955"/>
+    <row r="956"/>
+    <row r="957"/>
+    <row r="958"/>
+    <row r="959"/>
+    <row r="960"/>
+    <row r="961"/>
+    <row r="962"/>
+    <row r="963"/>
+    <row r="964"/>
+    <row r="965"/>
+    <row r="966"/>
+    <row r="967"/>
+    <row r="968"/>
+    <row r="969"/>
+    <row r="970"/>
+    <row r="971"/>
+    <row r="972"/>
+    <row r="973"/>
+    <row r="974"/>
+    <row r="975"/>
+    <row r="976"/>
+    <row r="977"/>
+    <row r="978"/>
+    <row r="979"/>
+    <row r="980"/>
+    <row r="981"/>
+    <row r="982"/>
+    <row r="983"/>
+    <row r="984"/>
+    <row r="985"/>
+    <row r="986"/>
+    <row r="987"/>
+    <row r="988"/>
+    <row r="989"/>
+    <row r="990"/>
+    <row r="991"/>
+    <row r="992"/>
+    <row r="993"/>
+    <row r="994"/>
+    <row r="995"/>
+    <row r="996"/>
+    <row r="997"/>
+    <row r="998"/>
+    <row r="999"/>
+    <row r="1000"/>
+    <row r="1001"/>
+    <row r="1002"/>
+    <row r="1003"/>
+    <row r="1004"/>
+    <row r="1005"/>
     <row r="1006" ht="19.5" customHeight="1" s="70">
       <c r="A1006" s="107" t="inlineStr">
         <is>
@@ -28684,9 +29891,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A1006:AN1006"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -28705,22 +29913,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="70" min="1" max="1"/>
-    <col width="18" customWidth="1" style="70" min="2" max="2"/>
+    <col width="62.5" customWidth="1" style="70" min="2" max="2"/>
     <col width="15" customWidth="1" style="70" min="3" max="3"/>
-    <col width="12" customWidth="1" style="70" min="4" max="4"/>
-    <col width="16" customWidth="1" style="70" min="5" max="5"/>
+    <col width="15.5" customWidth="1" style="70" min="4" max="4"/>
+    <col width="36.5" customWidth="1" style="70" min="5" max="5"/>
     <col width="18" customWidth="1" style="70" min="6" max="6"/>
-    <col width="6" customWidth="1" style="70" min="7" max="7"/>
-    <col width="24" customWidth="1" style="70" min="8" max="8"/>
+    <col width="11.5" customWidth="1" style="70" min="7" max="7"/>
+    <col width="75.5" customWidth="1" style="70" min="8" max="8"/>
     <col width="15" customWidth="1" style="70" min="9" max="9"/>
-    <col width="15" customWidth="1" style="70" min="10" max="10"/>
-    <col width="12" customWidth="1" style="70" min="11" max="11"/>
+    <col width="15.5" customWidth="1" style="70" min="10" max="10"/>
+    <col width="81.5" customWidth="1" style="70" min="11" max="11"/>
     <col width="18" customWidth="1" style="70" min="12" max="12"/>
     <col width="18" customWidth="1" style="70" min="13" max="13"/>
+    <col width="13" customWidth="1" style="70" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28754,6 +29963,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="165" t="inlineStr">
         <is>
@@ -28884,6 +30094,7 @@
       <c r="L9" s="166" t="n"/>
       <c r="M9" s="166" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="94" t="inlineStr">
         <is>
@@ -28913,6 +30124,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="182" t="inlineStr">
         <is>
@@ -29167,6 +30379,7 @@
         <v>92</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="B22" s="193" t="inlineStr">
         <is>
@@ -29255,13 +30468,21 @@
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
       </c>
+      <c r="G26" s="274" t="n"/>
+      <c r="H26" s="274" t="n"/>
+      <c r="I26" s="275" t="n"/>
       <c r="K26" s="202" t="inlineStr">
         <is>
           <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
+    <row r="27">
+      <c r="F27" s="276" t="n"/>
+      <c r="G27" s="277" t="n"/>
+      <c r="H27" s="277" t="n"/>
+      <c r="I27" s="278" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K26:M27"/>
@@ -29278,22 +30499,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="36" customWidth="1" style="96" min="1" max="1"/>
-    <col width="28" customWidth="1" style="96" min="2" max="2"/>
-    <col width="16" customWidth="1" style="96" min="3" max="3"/>
-    <col width="28" customWidth="1" style="96" min="4" max="4"/>
+    <col width="33.5" customWidth="1" style="96" min="2" max="2"/>
+    <col width="29.5" customWidth="1" style="96" min="3" max="3"/>
+    <col width="30.5" customWidth="1" style="96" min="4" max="4"/>
+    <col width="13" customWidth="1" style="70" min="5" max="5"/>
+    <col width="13" customWidth="1" style="70" min="6" max="6"/>
+    <col width="13" customWidth="1" style="70" min="7" max="7"/>
+    <col width="13" customWidth="1" style="70" min="8" max="8"/>
+    <col width="13" customWidth="1" style="70" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="70">
-      <c r="A1" s="96" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="70">
+      <c r="A1" s="272" t="inlineStr">
         <is>
           <t>ANAHTAR — AylikPatronFinansPaneli</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="273" t="n"/>
+      <c r="C1" s="273" t="n"/>
+      <c r="D1" s="273" t="n"/>
+      <c r="E1" s="273" t="n"/>
+      <c r="F1" s="273" t="n"/>
+      <c r="G1" s="273" t="n"/>
+      <c r="H1" s="273" t="n"/>
+      <c r="I1" s="273" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="70">
       <c r="A3" s="96" t="inlineStr">
         <is>
@@ -29358,6 +30594,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -29370,21 +30609,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="40" customWidth="1" style="96" min="1" max="1"/>
     <col width="28" customWidth="1" style="96" min="2" max="2"/>
     <col width="12" customWidth="1" style="96" min="3" max="4"/>
+    <col width="13" customWidth="1" style="70" min="4" max="4"/>
+    <col width="13" customWidth="1" style="70" min="5" max="5"/>
+    <col width="13" customWidth="1" style="70" min="6" max="6"/>
+    <col width="13" customWidth="1" style="70" min="7" max="7"/>
+    <col width="13" customWidth="1" style="70" min="8" max="8"/>
+    <col width="13" customWidth="1" style="70" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="70">
-      <c r="A1" s="96" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="70">
+      <c r="A1" s="272" t="inlineStr">
         <is>
           <t>ESLESTIRME — AylikPatronFinansPaneli</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="273" t="n"/>
+      <c r="C1" s="273" t="n"/>
+      <c r="D1" s="273" t="n"/>
+      <c r="E1" s="273" t="n"/>
+      <c r="F1" s="273" t="n"/>
+      <c r="G1" s="273" t="n"/>
+      <c r="H1" s="273" t="n"/>
+      <c r="I1" s="273" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="70">
       <c r="A3" s="96" t="inlineStr">
         <is>
@@ -29481,6 +30736,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -29493,21 +30751,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="40" customWidth="1" style="96" min="1" max="1"/>
     <col width="42" customWidth="1" style="96" min="2" max="2"/>
-    <col width="18" customWidth="1" style="96" min="3" max="3"/>
+    <col width="18.5" customWidth="1" style="96" min="3" max="3"/>
+    <col width="13" customWidth="1" style="70" min="4" max="4"/>
+    <col width="13" customWidth="1" style="70" min="5" max="5"/>
+    <col width="13" customWidth="1" style="70" min="6" max="6"/>
+    <col width="13" customWidth="1" style="70" min="7" max="7"/>
+    <col width="13" customWidth="1" style="70" min="8" max="8"/>
+    <col width="13" customWidth="1" style="70" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="70">
-      <c r="A1" s="96" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="70">
+      <c r="A1" s="272" t="inlineStr">
         <is>
           <t>KOK_NEDEN — AylikPatronFinansPaneli</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="273" t="n"/>
+      <c r="C1" s="273" t="n"/>
+      <c r="D1" s="273" t="n"/>
+      <c r="E1" s="273" t="n"/>
+      <c r="F1" s="273" t="n"/>
+      <c r="G1" s="273" t="n"/>
+      <c r="H1" s="273" t="n"/>
+      <c r="I1" s="273" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="70">
       <c r="A3" s="96" t="inlineStr">
         <is>
@@ -29578,6 +30852,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -29596,19 +30873,33 @@
     <col width="16" customWidth="1" style="96" min="1" max="1"/>
     <col width="10" customWidth="1" style="96" min="2" max="2"/>
     <col width="40" customWidth="1" style="96" min="3" max="3"/>
-    <col width="30" customWidth="1" style="96" min="4" max="4"/>
-    <col width="14" customWidth="1" style="96" min="5" max="5"/>
+    <col width="30.5" customWidth="1" style="96" min="4" max="4"/>
+    <col width="14.5" customWidth="1" style="96" min="5" max="5"/>
+    <col width="13" customWidth="1" style="70" min="6" max="6"/>
+    <col width="13" customWidth="1" style="70" min="7" max="7"/>
+    <col width="13" customWidth="1" style="70" min="8" max="8"/>
+    <col width="13" customWidth="1" style="70" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="70">
-      <c r="A1" s="108" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="70">
+      <c r="A1" s="272" t="inlineStr">
         <is>
           <t>DEGISIKLIK KAYDI — AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="70">
-      <c r="A3" s="126" t="inlineStr">
+      <c r="B1" s="273" t="n"/>
+      <c r="C1" s="273" t="n"/>
+      <c r="D1" s="273" t="n"/>
+      <c r="E1" s="273" t="n"/>
+      <c r="F1" s="273" t="n"/>
+      <c r="G1" s="273" t="n"/>
+      <c r="H1" s="273" t="n"/>
+      <c r="I1" s="273" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="70">
+      <c r="A3" s="291" t="inlineStr">
         <is>
           <t>Değişiklik Kaydı</t>
         </is>
@@ -29670,8 +30961,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -29689,19 +30981,33 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="96" min="1" max="1"/>
+    <col width="13" customWidth="1" style="70" min="2" max="2"/>
     <col width="12" customWidth="1" style="96" min="3" max="3"/>
-    <col width="12" customWidth="1" style="96" min="5" max="5"/>
-    <col width="16" customWidth="1" style="96" min="7" max="7"/>
-    <col width="16" customWidth="1" style="96" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="4" max="4"/>
+    <col width="13.5" customWidth="1" style="96" min="5" max="5"/>
+    <col width="13" customWidth="1" style="70" min="6" max="6"/>
+    <col width="20.5" customWidth="1" style="96" min="7" max="7"/>
+    <col width="13" customWidth="1" style="70" min="8" max="8"/>
+    <col width="18.5" customWidth="1" style="96" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="70">
-      <c r="A1" s="108" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="70">
+      <c r="A1" s="272" t="inlineStr">
         <is>
           <t>LISTELER — AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="273" t="n"/>
+      <c r="C1" s="273" t="n"/>
+      <c r="D1" s="273" t="n"/>
+      <c r="E1" s="273" t="n"/>
+      <c r="F1" s="273" t="n"/>
+      <c r="G1" s="273" t="n"/>
+      <c r="H1" s="273" t="n"/>
+      <c r="I1" s="273" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="70">
       <c r="A3" s="126" t="inlineStr">
         <is>
@@ -29859,7 +31165,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -29883,17 +31189,30 @@
     <col width="52" customWidth="1" style="96" min="4" max="4"/>
     <col width="12" customWidth="1" style="96" min="5" max="5"/>
     <col width="16" customWidth="1" style="96" min="6" max="7"/>
+    <col width="13" customWidth="1" style="70" min="7" max="7"/>
+    <col width="13" customWidth="1" style="70" min="8" max="8"/>
+    <col width="13" customWidth="1" style="70" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="70">
-      <c r="A1" s="108" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="70">
+      <c r="A1" s="272" t="inlineStr">
         <is>
           <t>AYARLAR — AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="70">
-      <c r="A3" s="126" t="inlineStr">
+      <c r="B1" s="273" t="n"/>
+      <c r="C1" s="273" t="n"/>
+      <c r="D1" s="273" t="n"/>
+      <c r="E1" s="273" t="n"/>
+      <c r="F1" s="273" t="n"/>
+      <c r="G1" s="273" t="n"/>
+      <c r="H1" s="273" t="n"/>
+      <c r="I1" s="273" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="70">
+      <c r="A3" s="291" t="inlineStr">
         <is>
           <t>Sistem Ayarları ve Eşikler</t>
         </is>
@@ -29906,6 +31225,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1" s="70">
       <c r="A6" s="111" t="inlineStr">
         <is>
@@ -31530,6 +32850,7 @@
         </is>
       </c>
     </row>
+    <row r="52"/>
     <row r="53" ht="15" customHeight="1" s="70">
       <c r="B53" s="160" t="inlineStr">
         <is>
@@ -31539,9 +32860,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="B53:AD53"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -31559,18 +32881,36 @@
   <dimension ref="A1:AN38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="40" customWidth="1" style="96" min="1" max="1"/>
+    <col width="160.5" customWidth="1" style="96" min="1" max="1"/>
+    <col width="13" customWidth="1" style="70" min="2" max="2"/>
+    <col width="13" customWidth="1" style="70" min="3" max="3"/>
+    <col width="13" customWidth="1" style="70" min="4" max="4"/>
+    <col width="13" customWidth="1" style="70" min="5" max="5"/>
+    <col width="13" customWidth="1" style="70" min="6" max="6"/>
+    <col width="13" customWidth="1" style="70" min="7" max="7"/>
+    <col width="13" customWidth="1" style="70" min="8" max="8"/>
+    <col width="13" customWidth="1" style="70" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="70">
-      <c r="A1" s="108" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="70">
+      <c r="A1" s="272" t="inlineStr">
         <is>
           <t>KILAVUZ — AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1" s="70">
-      <c r="A3" s="104" t="inlineStr">
+      <c r="B1" s="273" t="n"/>
+      <c r="C1" s="273" t="n"/>
+      <c r="D1" s="273" t="n"/>
+      <c r="E1" s="273" t="n"/>
+      <c r="F1" s="273" t="n"/>
+      <c r="G1" s="273" t="n"/>
+      <c r="H1" s="273" t="n"/>
+      <c r="I1" s="273" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="70">
+      <c r="A3" s="291" t="inlineStr">
         <is>
           <t>Kullanım Kılavuzu</t>
         </is>
@@ -31632,6 +32972,16 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22" ht="15" customHeight="1" s="70">
       <c r="A22" s="126" t="inlineStr">
         <is>
@@ -31674,6 +33024,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29" ht="15" customHeight="1" s="70">
       <c r="A29" s="126" t="inlineStr">
         <is>
@@ -31688,6 +33039,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="15" customHeight="1" s="70">
       <c r="A32" s="126" t="inlineStr">
         <is>
@@ -31723,6 +33075,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38" ht="19.5" customHeight="1" s="70">
       <c r="A38" s="107" t="inlineStr">
         <is>
@@ -31732,9 +33085,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="A7:L7"/>
     <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A27:L27"/>
     <mergeCell ref="A26:L26"/>
     <mergeCell ref="A33:L33"/>
@@ -31745,12 +33099,12 @@
     <mergeCell ref="A35:L35"/>
     <mergeCell ref="A10:L10"/>
     <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A1:AN1"/>
     <mergeCell ref="A34:L34"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A30:L30"/>
     <mergeCell ref="A11:L11"/>
     <mergeCell ref="A36:L36"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A6:L6"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -31766,18 +33120,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="70" min="1" max="1"/>
-    <col width="14" customWidth="1" style="70" min="2" max="2"/>
+    <col width="36.5" customWidth="1" style="70" min="2" max="2"/>
     <col width="16" customWidth="1" style="70" min="3" max="3"/>
-    <col width="32" customWidth="1" style="70" min="4" max="4"/>
-    <col width="18" customWidth="1" style="70" min="5" max="5"/>
-    <col width="12" customWidth="1" style="70" min="6" max="6"/>
+    <col width="37.5" customWidth="1" style="70" min="4" max="4"/>
+    <col width="18.5" customWidth="1" style="70" min="5" max="5"/>
+    <col width="13.5" customWidth="1" style="70" min="6" max="6"/>
     <col width="18" customWidth="1" style="70" min="7" max="7"/>
-    <col width="22" customWidth="1" style="70" min="8" max="8"/>
+    <col width="22.5" customWidth="1" style="70" min="8" max="8"/>
     <col width="16" customWidth="1" style="70" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31787,12 +33142,16 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="203" t="inlineStr">
         <is>
           <t>🔍  AYLIK PATRON FINANS PANELI — Kayıt veya hesap ara...</t>
         </is>
       </c>
+      <c r="C3" s="279" t="n"/>
+      <c r="D3" s="279" t="n"/>
+      <c r="E3" s="280" t="n"/>
       <c r="G3" s="204" t="inlineStr">
         <is>
           <t>TOPLAM: 1.450 KAYIT</t>
@@ -31804,6 +33163,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="206" t="inlineStr">
         <is>
@@ -32216,22 +33576,17 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="223" t="inlineStr">
         <is>
           <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
         </is>
       </c>
-      <c r="C17" s="191" t="n"/>
-      <c r="D17" s="191" t="n"/>
       <c r="E17" s="224">
         <f>TOPLA(E6:E15)</f>
         <v/>
       </c>
-      <c r="F17" s="191" t="n"/>
-      <c r="G17" s="191" t="n"/>
-      <c r="H17" s="191" t="n"/>
-      <c r="I17" s="191" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -32252,7 +33607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="70" min="1" max="1"/>
@@ -32297,25 +33652,26 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="228" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
       </c>
-      <c r="C6" s="166" t="n"/>
-      <c r="D6" s="166" t="n"/>
-      <c r="E6" s="166" t="n"/>
-      <c r="F6" s="166" t="n"/>
+      <c r="C6" s="279" t="n"/>
+      <c r="D6" s="279" t="n"/>
+      <c r="E6" s="279" t="n"/>
+      <c r="F6" s="280" t="n"/>
       <c r="H6" s="229" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
       </c>
-      <c r="I6" s="166" t="n"/>
-      <c r="J6" s="166" t="n"/>
-      <c r="K6" s="166" t="n"/>
-      <c r="L6" s="166" t="n"/>
+      <c r="I6" s="279" t="n"/>
+      <c r="J6" s="279" t="n"/>
+      <c r="K6" s="279" t="n"/>
+      <c r="L6" s="280" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="166" t="n"/>
@@ -32466,32 +33822,33 @@
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
       </c>
-      <c r="C14" s="166" t="n"/>
-      <c r="D14" s="166" t="n"/>
-      <c r="E14" s="166" t="n"/>
-      <c r="F14" s="166" t="n"/>
+      <c r="C14" s="281" t="n"/>
+      <c r="D14" s="281" t="n"/>
+      <c r="E14" s="281" t="n"/>
+      <c r="F14" s="282" t="n"/>
       <c r="H14" s="236" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
       </c>
-      <c r="I14" s="166" t="n"/>
-      <c r="J14" s="166" t="n"/>
-      <c r="K14" s="166" t="n"/>
-      <c r="L14" s="166" t="n"/>
+      <c r="I14" s="283" t="n"/>
+      <c r="J14" s="283" t="n"/>
+      <c r="K14" s="283" t="n"/>
+      <c r="L14" s="284" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="166" t="n"/>
-      <c r="C15" s="166" t="n"/>
-      <c r="D15" s="166" t="n"/>
-      <c r="E15" s="166" t="n"/>
-      <c r="F15" s="166" t="n"/>
-      <c r="H15" s="166" t="n"/>
-      <c r="I15" s="166" t="n"/>
-      <c r="J15" s="166" t="n"/>
-      <c r="K15" s="166" t="n"/>
-      <c r="L15" s="166" t="n"/>
-    </row>
+      <c r="B15" s="285" t="n"/>
+      <c r="C15" s="286" t="n"/>
+      <c r="D15" s="286" t="n"/>
+      <c r="E15" s="286" t="n"/>
+      <c r="F15" s="287" t="n"/>
+      <c r="H15" s="288" t="n"/>
+      <c r="I15" s="289" t="n"/>
+      <c r="J15" s="289" t="n"/>
+      <c r="K15" s="289" t="n"/>
+      <c r="L15" s="290" t="n"/>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="81" t="inlineStr">
         <is>
@@ -32499,6 +33856,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="193" t="inlineStr">
         <is>
@@ -32573,25 +33931,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="70" min="1" max="1"/>
-    <col width="24" customWidth="1" style="70" min="2" max="2"/>
-    <col width="22" customWidth="1" style="70" min="3" max="3"/>
-    <col width="27" customWidth="1" style="70" min="4" max="4"/>
-    <col width="29" customWidth="1" style="70" min="5" max="5"/>
-    <col width="20" customWidth="1" style="70" min="6" max="6"/>
+    <col width="30.5" customWidth="1" style="70" min="2" max="2"/>
+    <col width="23.5" customWidth="1" style="70" min="3" max="3"/>
+    <col width="48.5" customWidth="1" style="70" min="4" max="4"/>
+    <col width="43.5" customWidth="1" style="70" min="5" max="5"/>
+    <col width="21.5" customWidth="1" style="70" min="6" max="6"/>
     <col width="21" customWidth="1" style="70" min="7" max="7"/>
+    <col width="13" customWidth="1" style="70" min="8" max="8"/>
+    <col width="13" customWidth="1" style="70" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="70">
-      <c r="A1" s="243" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="70">
+      <c r="A1" s="272" t="inlineStr">
         <is>
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="273" t="n"/>
+      <c r="C1" s="273" t="n"/>
+      <c r="D1" s="273" t="n"/>
+      <c r="E1" s="273" t="n"/>
+      <c r="F1" s="273" t="n"/>
+      <c r="G1" s="273" t="n"/>
+      <c r="H1" s="273" t="n"/>
+      <c r="I1" s="273" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="70">
       <c r="A3" s="244" t="inlineStr">
         <is>
@@ -33051,7 +34421,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33064,22 +34434,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="70" min="1" max="1"/>
-    <col width="52" customWidth="1" style="70" min="2" max="2"/>
-    <col width="34" customWidth="1" style="70" min="3" max="3"/>
+    <col width="89.5" customWidth="1" style="70" min="2" max="2"/>
+    <col width="34.5" customWidth="1" style="70" min="3" max="3"/>
     <col width="16" customWidth="1" style="70" min="4" max="4"/>
+    <col width="13" customWidth="1" style="70" min="5" max="5"/>
+    <col width="13" customWidth="1" style="70" min="6" max="6"/>
+    <col width="13" customWidth="1" style="70" min="7" max="7"/>
+    <col width="13" customWidth="1" style="70" min="8" max="8"/>
+    <col width="13" customWidth="1" style="70" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="70">
-      <c r="A1" s="246" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="70">
+      <c r="A1" s="272" t="inlineStr">
         <is>
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="273" t="n"/>
+      <c r="C1" s="273" t="n"/>
+      <c r="D1" s="273" t="n"/>
+      <c r="E1" s="273" t="n"/>
+      <c r="F1" s="273" t="n"/>
+      <c r="G1" s="273" t="n"/>
+      <c r="H1" s="273" t="n"/>
+      <c r="I1" s="273" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="70">
       <c r="A3" s="247" t="inlineStr">
         <is>
@@ -33791,7 +35176,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33804,24 +35189,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" style="70" min="1" max="1"/>
-    <col width="36" customWidth="1" style="70" min="2" max="2"/>
-    <col width="48" customWidth="1" style="70" min="3" max="3"/>
-    <col width="34" customWidth="1" style="70" min="4" max="4"/>
-    <col width="30" customWidth="1" style="70" min="5" max="5"/>
+    <col width="30.5" customWidth="1" style="70" min="1" max="1"/>
+    <col width="71.5" customWidth="1" style="70" min="2" max="2"/>
+    <col width="160.5" customWidth="1" style="70" min="3" max="3"/>
+    <col width="70.5" customWidth="1" style="70" min="4" max="4"/>
+    <col width="50.5" customWidth="1" style="70" min="5" max="5"/>
     <col width="16" customWidth="1" style="70" min="6" max="6"/>
+    <col width="13" customWidth="1" style="70" min="7" max="7"/>
+    <col width="13" customWidth="1" style="70" min="8" max="8"/>
+    <col width="13" customWidth="1" style="70" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="70">
-      <c r="A1" s="251" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="70">
+      <c r="A1" s="272" t="inlineStr">
         <is>
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="273" t="n"/>
+      <c r="C1" s="273" t="n"/>
+      <c r="D1" s="273" t="n"/>
+      <c r="E1" s="273" t="n"/>
+      <c r="F1" s="273" t="n"/>
+      <c r="G1" s="273" t="n"/>
+      <c r="H1" s="273" t="n"/>
+      <c r="I1" s="273" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="70">
       <c r="A3" s="252" t="inlineStr">
         <is>
@@ -34464,7 +35862,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -34477,24 +35875,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" style="70" min="1" max="1"/>
-    <col width="40" customWidth="1" style="70" min="2" max="2"/>
-    <col width="50" customWidth="1" style="70" min="3" max="3"/>
-    <col width="30" customWidth="1" style="70" min="4" max="4"/>
-    <col width="28" customWidth="1" style="70" min="5" max="5"/>
-    <col width="26" customWidth="1" style="70" min="6" max="6"/>
+    <col width="22.5" customWidth="1" style="70" min="1" max="1"/>
+    <col width="60.5" customWidth="1" style="70" min="2" max="2"/>
+    <col width="86.5" customWidth="1" style="70" min="3" max="3"/>
+    <col width="40.5" customWidth="1" style="70" min="4" max="4"/>
+    <col width="39.5" customWidth="1" style="70" min="5" max="5"/>
+    <col width="27.5" customWidth="1" style="70" min="6" max="6"/>
+    <col width="13" customWidth="1" style="70" min="7" max="7"/>
+    <col width="13" customWidth="1" style="70" min="8" max="8"/>
+    <col width="13" customWidth="1" style="70" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="70">
-      <c r="A1" s="255" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="70">
+      <c r="A1" s="272" t="inlineStr">
         <is>
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="273" t="n"/>
+      <c r="C1" s="273" t="n"/>
+      <c r="D1" s="273" t="n"/>
+      <c r="E1" s="273" t="n"/>
+      <c r="F1" s="273" t="n"/>
+      <c r="G1" s="273" t="n"/>
+      <c r="H1" s="273" t="n"/>
+      <c r="I1" s="273" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="70">
       <c r="A3" s="256" t="inlineStr">
         <is>
@@ -35009,7 +36420,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35022,23 +36433,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="70" min="1" max="1"/>
-    <col width="32" customWidth="1" style="70" min="2" max="2"/>
-    <col width="54" customWidth="1" style="70" min="3" max="3"/>
-    <col width="34" customWidth="1" style="70" min="4" max="4"/>
+    <col width="20.5" customWidth="1" style="70" min="1" max="1"/>
+    <col width="41.5" customWidth="1" style="70" min="2" max="2"/>
+    <col width="86.5" customWidth="1" style="70" min="3" max="3"/>
+    <col width="35.5" customWidth="1" style="70" min="4" max="4"/>
+    <col width="33.5" customWidth="1" style="70" min="5" max="5"/>
     <col width="16" customWidth="1" style="70" min="6" max="6"/>
+    <col width="13" customWidth="1" style="70" min="7" max="7"/>
+    <col width="13" customWidth="1" style="70" min="8" max="8"/>
+    <col width="13" customWidth="1" style="70" min="9" max="9"/>
+    <col width="13" customWidth="1" style="70" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="70">
-      <c r="A1" s="258" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="70">
+      <c r="A1" s="272" t="inlineStr">
         <is>
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="273" t="n"/>
+      <c r="C1" s="273" t="n"/>
+      <c r="D1" s="273" t="n"/>
+      <c r="E1" s="273" t="n"/>
+      <c r="F1" s="273" t="n"/>
+      <c r="G1" s="273" t="n"/>
+      <c r="H1" s="273" t="n"/>
+      <c r="I1" s="273" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="70">
       <c r="A3" s="259" t="inlineStr">
         <is>
@@ -35585,7 +37010,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/aylik-patron-finans-paneli/AylikPatronFinansPaneli.xlsx
+++ b/EXCELARSIV_PRODUCTS/aylik-patron-finans-paneli/AylikPatronFinansPaneli.xlsx
@@ -4068,7 +4068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="70" min="1" max="1"/>
@@ -4089,14 +4089,6 @@
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-      <c r="B1" s="273" t="n"/>
-      <c r="C1" s="273" t="n"/>
-      <c r="D1" s="273" t="n"/>
-      <c r="E1" s="273" t="n"/>
-      <c r="F1" s="273" t="n"/>
-      <c r="G1" s="273" t="n"/>
-      <c r="H1" s="273" t="n"/>
-      <c r="I1" s="273" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="70">
@@ -4474,7 +4466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AD15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="55" customWidth="1" style="96" min="1" max="3"/>
@@ -4495,14 +4487,6 @@
           <t>AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-      <c r="B1" s="273" t="n"/>
-      <c r="C1" s="273" t="n"/>
-      <c r="D1" s="273" t="n"/>
-      <c r="E1" s="273" t="n"/>
-      <c r="F1" s="273" t="n"/>
-      <c r="G1" s="273" t="n"/>
-      <c r="H1" s="273" t="n"/>
-      <c r="I1" s="273" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
@@ -4755,14 +4739,6 @@
           <t>AYLIK GELIR GIDER — AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-      <c r="B1" s="273" t="n"/>
-      <c r="C1" s="273" t="n"/>
-      <c r="D1" s="273" t="n"/>
-      <c r="E1" s="273" t="n"/>
-      <c r="F1" s="273" t="n"/>
-      <c r="G1" s="273" t="n"/>
-      <c r="H1" s="273" t="n"/>
-      <c r="I1" s="273" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
@@ -13823,13 +13799,6 @@
           <t>BORC VE ALACAK — AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-      <c r="B1" s="273" t="n"/>
-      <c r="C1" s="273" t="n"/>
-      <c r="D1" s="273" t="n"/>
-      <c r="E1" s="273" t="n"/>
-      <c r="F1" s="273" t="n"/>
-      <c r="G1" s="273" t="n"/>
-      <c r="H1" s="273" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
@@ -23293,14 +23262,6 @@
           <t>FINANS MOTORU — AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-      <c r="B1" s="273" t="n"/>
-      <c r="C1" s="273" t="n"/>
-      <c r="D1" s="273" t="n"/>
-      <c r="E1" s="273" t="n"/>
-      <c r="F1" s="273" t="n"/>
-      <c r="G1" s="273" t="n"/>
-      <c r="H1" s="273" t="n"/>
-      <c r="I1" s="273" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
@@ -23846,7 +23807,7 @@
         <v/>
       </c>
       <c r="J33" s="131">
-        <f>_xlfn.TEXTJOIN(" ",FALSE(),"Dönemlik ortalama gelir",TEXT(IFERROR(I33,0),"#.##0"),"₺; aylık performansın çıpasıdır.")</f>
+        <f>_xlfn.TEXTJOIN(" ",FALSE(),"Dönemlik AVERAGE gelir",TEXT(IFERROR(I33,0),"#.##0"),"₺; aylık performansın çıpasıdır.")</f>
         <v/>
       </c>
     </row>
@@ -27219,14 +27180,6 @@
           <t>KONTROLLER — AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-      <c r="B1" s="273" t="n"/>
-      <c r="C1" s="273" t="n"/>
-      <c r="D1" s="273" t="n"/>
-      <c r="E1" s="273" t="n"/>
-      <c r="F1" s="273" t="n"/>
-      <c r="G1" s="273" t="n"/>
-      <c r="H1" s="273" t="n"/>
-      <c r="I1" s="273" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
@@ -27484,14 +27437,6 @@
           <t>KARAR — AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-      <c r="B1" s="273" t="n"/>
-      <c r="C1" s="273" t="n"/>
-      <c r="D1" s="273" t="n"/>
-      <c r="E1" s="273" t="n"/>
-      <c r="F1" s="273" t="n"/>
-      <c r="G1" s="273" t="n"/>
-      <c r="H1" s="273" t="n"/>
-      <c r="I1" s="273" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
@@ -27572,7 +27517,7 @@
         </is>
       </c>
       <c r="B12" s="141">
-        <f>IF(FinansToplamGirisHucre&lt;AsgariVeriSayisi,"Karar için yeterli kayıt girilmedi. Asgari eşik: "&amp;TEXT(AsgariVeriSayisi,"0")&amp;" dolu kayıt. Giriş sayfalarını doldurun.",IF(AND(FinansToplamGelir&gt;0,FinansNetKar&gt;=0,FinansBorcGelirOrani&lt;=FinansBorcEsik,FinansAySonuKasa&gt;=FinansKasaMin),"Kâr pozitif, gelir mevcut; borç oranı ve kasa yeterliliği eşiklerin içinde.","Kâr, borçluluk veya kasa eşiği kontrolünden biri sağlanmıyor."))</f>
+        <f>IF(FinansToplamGirisHucre&lt;AsgariVeriSayisi,"Karar için yeterli kayıt girilmedi. Asgari eşik: "&amp;TEXT(AsgariVeriSayisi,"0")&amp;" dolu kayıt. Giriş sayfalarını doldurun.",IF(AND(FinansToplamGelir&gt;0,FinansNetKar&gt;=0,FinansBorcGelirOrani&lt;=FinansBorcEsik,FinansAySonuKasa&gt;=FinansKasaMin),"Kâr pozitif, gelir mevcut; borç oranı AND kasa yeterliliği eşiklerin içinde.","Kâr, borçluluk veya kasa eşiği kontrolünden biri sağlanmıyor."))</f>
         <v/>
       </c>
     </row>
@@ -27629,12 +27574,12 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
   <mergeCells count="7">
     <mergeCell ref="B15:J15"/>
-    <mergeCell ref="B16:J16"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B17:J17"/>
     <mergeCell ref="A19:AN19"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="B12:J12"/>
+    <mergeCell ref="B16:J16"/>
   </mergeCells>
   <conditionalFormatting sqref="B11">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="14" text="" percent="0" bottom="0">
@@ -27688,14 +27633,6 @@
           <t>SENARYO DUYARLILIK — AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-      <c r="B1" s="273" t="n"/>
-      <c r="C1" s="273" t="n"/>
-      <c r="D1" s="273" t="n"/>
-      <c r="E1" s="273" t="n"/>
-      <c r="F1" s="273" t="n"/>
-      <c r="G1" s="273" t="n"/>
-      <c r="H1" s="273" t="n"/>
-      <c r="I1" s="273" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
@@ -27904,7 +27841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN27"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="45" customWidth="1" style="96" min="1" max="1"/>
@@ -27925,14 +27862,6 @@
           <t>AYLIK PATRON FİNANS PANELİ — YÖNETİCİ ÖZETİ</t>
         </is>
       </c>
-      <c r="B1" s="273" t="n"/>
-      <c r="C1" s="273" t="n"/>
-      <c r="D1" s="273" t="n"/>
-      <c r="E1" s="273" t="n"/>
-      <c r="F1" s="273" t="n"/>
-      <c r="G1" s="273" t="n"/>
-      <c r="H1" s="273" t="n"/>
-      <c r="I1" s="273" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1" s="70">
       <c r="A2" s="152">
@@ -28181,14 +28110,6 @@
           <t>ORNEK VERI — AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-      <c r="B1" s="273" t="n"/>
-      <c r="C1" s="273" t="n"/>
-      <c r="D1" s="273" t="n"/>
-      <c r="E1" s="273" t="n"/>
-      <c r="F1" s="273" t="n"/>
-      <c r="G1" s="273" t="n"/>
-      <c r="H1" s="273" t="n"/>
-      <c r="I1" s="273" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
@@ -29913,7 +29834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="70" min="1" max="1"/>
@@ -30044,7 +29965,7 @@
       <c r="I7" s="166" t="n"/>
       <c r="J7" s="166" t="n"/>
       <c r="K7" s="177">
-        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
       <c r="L7" s="166" t="n"/>
@@ -30349,11 +30270,11 @@
         </is>
       </c>
       <c r="I19" s="266">
-        <f>TOPLA(I15:I18)</f>
+        <f>SUM(I15:I18)</f>
         <v/>
       </c>
       <c r="J19" s="267">
-        <f>TOPLA(J15:J18)</f>
+        <f>SUM(J15:J18)</f>
         <v/>
       </c>
       <c r="K19" s="191" t="inlineStr"/>
@@ -30499,7 +30420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="36" customWidth="1" style="96" min="1" max="1"/>
@@ -30520,14 +30441,6 @@
           <t>ANAHTAR — AylikPatronFinansPaneli</t>
         </is>
       </c>
-      <c r="B1" s="273" t="n"/>
-      <c r="C1" s="273" t="n"/>
-      <c r="D1" s="273" t="n"/>
-      <c r="E1" s="273" t="n"/>
-      <c r="F1" s="273" t="n"/>
-      <c r="G1" s="273" t="n"/>
-      <c r="H1" s="273" t="n"/>
-      <c r="I1" s="273" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="70">
@@ -30609,7 +30522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="40" customWidth="1" style="96" min="1" max="1"/>
@@ -30630,14 +30543,6 @@
           <t>ESLESTIRME — AylikPatronFinansPaneli</t>
         </is>
       </c>
-      <c r="B1" s="273" t="n"/>
-      <c r="C1" s="273" t="n"/>
-      <c r="D1" s="273" t="n"/>
-      <c r="E1" s="273" t="n"/>
-      <c r="F1" s="273" t="n"/>
-      <c r="G1" s="273" t="n"/>
-      <c r="H1" s="273" t="n"/>
-      <c r="I1" s="273" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="70">
@@ -30751,7 +30656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="40" customWidth="1" style="96" min="1" max="1"/>
@@ -30772,14 +30677,6 @@
           <t>KOK_NEDEN — AylikPatronFinansPaneli</t>
         </is>
       </c>
-      <c r="B1" s="273" t="n"/>
-      <c r="C1" s="273" t="n"/>
-      <c r="D1" s="273" t="n"/>
-      <c r="E1" s="273" t="n"/>
-      <c r="F1" s="273" t="n"/>
-      <c r="G1" s="273" t="n"/>
-      <c r="H1" s="273" t="n"/>
-      <c r="I1" s="273" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="70">
@@ -30867,7 +30764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="96" min="1" max="1"/>
@@ -30888,14 +30785,6 @@
           <t>DEGISIKLIK KAYDI — AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-      <c r="B1" s="273" t="n"/>
-      <c r="C1" s="273" t="n"/>
-      <c r="D1" s="273" t="n"/>
-      <c r="E1" s="273" t="n"/>
-      <c r="F1" s="273" t="n"/>
-      <c r="G1" s="273" t="n"/>
-      <c r="H1" s="273" t="n"/>
-      <c r="I1" s="273" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
@@ -30977,7 +30866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AD12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="96" min="1" max="1"/>
@@ -30998,14 +30887,6 @@
           <t>LISTELER — AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-      <c r="B1" s="273" t="n"/>
-      <c r="C1" s="273" t="n"/>
-      <c r="D1" s="273" t="n"/>
-      <c r="E1" s="273" t="n"/>
-      <c r="F1" s="273" t="n"/>
-      <c r="G1" s="273" t="n"/>
-      <c r="H1" s="273" t="n"/>
-      <c r="I1" s="273" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="70">
@@ -31201,14 +31082,6 @@
           <t>AYARLAR — AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-      <c r="B1" s="273" t="n"/>
-      <c r="C1" s="273" t="n"/>
-      <c r="D1" s="273" t="n"/>
-      <c r="E1" s="273" t="n"/>
-      <c r="F1" s="273" t="n"/>
-      <c r="G1" s="273" t="n"/>
-      <c r="H1" s="273" t="n"/>
-      <c r="I1" s="273" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
@@ -32899,14 +32772,6 @@
           <t>KILAVUZ — AYLIK PATRON FİNANS PANELİ</t>
         </is>
       </c>
-      <c r="B1" s="273" t="n"/>
-      <c r="C1" s="273" t="n"/>
-      <c r="D1" s="273" t="n"/>
-      <c r="E1" s="273" t="n"/>
-      <c r="F1" s="273" t="n"/>
-      <c r="G1" s="273" t="n"/>
-      <c r="H1" s="273" t="n"/>
-      <c r="I1" s="273" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
@@ -33120,7 +32985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="70" min="1" max="1"/>
@@ -33584,7 +33449,7 @@
         </is>
       </c>
       <c r="E17" s="224">
-        <f>TOPLA(E6:E15)</f>
+        <f>SUM(E6:E15)</f>
         <v/>
       </c>
     </row>
@@ -33607,7 +33472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="70" min="1" max="1"/>
@@ -33774,7 +33639,7 @@
       <c r="C11" s="166" t="n"/>
       <c r="D11" s="166" t="n"/>
       <c r="E11" s="271">
-        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
       <c r="F11" s="166" t="n"/>
@@ -33931,7 +33796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="70" min="1" max="1"/>
@@ -33952,14 +33817,6 @@
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-      <c r="B1" s="273" t="n"/>
-      <c r="C1" s="273" t="n"/>
-      <c r="D1" s="273" t="n"/>
-      <c r="E1" s="273" t="n"/>
-      <c r="F1" s="273" t="n"/>
-      <c r="G1" s="273" t="n"/>
-      <c r="H1" s="273" t="n"/>
-      <c r="I1" s="273" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="70">
@@ -34434,7 +34291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="70" min="1" max="1"/>
@@ -34455,14 +34312,6 @@
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-      <c r="B1" s="273" t="n"/>
-      <c r="C1" s="273" t="n"/>
-      <c r="D1" s="273" t="n"/>
-      <c r="E1" s="273" t="n"/>
-      <c r="F1" s="273" t="n"/>
-      <c r="G1" s="273" t="n"/>
-      <c r="H1" s="273" t="n"/>
-      <c r="I1" s="273" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="70">
@@ -35189,7 +35038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.5" customWidth="1" style="70" min="1" max="1"/>
@@ -35210,14 +35059,6 @@
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="273" t="n"/>
-      <c r="C1" s="273" t="n"/>
-      <c r="D1" s="273" t="n"/>
-      <c r="E1" s="273" t="n"/>
-      <c r="F1" s="273" t="n"/>
-      <c r="G1" s="273" t="n"/>
-      <c r="H1" s="273" t="n"/>
-      <c r="I1" s="273" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="70">
@@ -35875,7 +35716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.5" customWidth="1" style="70" min="1" max="1"/>
@@ -35896,14 +35737,6 @@
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="273" t="n"/>
-      <c r="C1" s="273" t="n"/>
-      <c r="D1" s="273" t="n"/>
-      <c r="E1" s="273" t="n"/>
-      <c r="F1" s="273" t="n"/>
-      <c r="G1" s="273" t="n"/>
-      <c r="H1" s="273" t="n"/>
-      <c r="I1" s="273" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="70">
@@ -36433,7 +36266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.5" customWidth="1" style="70" min="1" max="1"/>
@@ -36454,14 +36287,6 @@
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="273" t="n"/>
-      <c r="C1" s="273" t="n"/>
-      <c r="D1" s="273" t="n"/>
-      <c r="E1" s="273" t="n"/>
-      <c r="F1" s="273" t="n"/>
-      <c r="G1" s="273" t="n"/>
-      <c r="H1" s="273" t="n"/>
-      <c r="I1" s="273" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="70">

--- a/EXCELARSIV_PRODUCTS/aylik-patron-finans-paneli/AylikPatronFinansPaneli.xlsx
+++ b/EXCELARSIV_PRODUCTS/aylik-patron-finans-paneli/AylikPatronFinansPaneli.xlsx
@@ -159,7 +159,7 @@
     <numFmt numFmtId="170" formatCode="₺#,##0"/>
     <numFmt numFmtId="171" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="103">
+  <fonts count="139">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -806,8 +806,220 @@
       <color rgb="00475569"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00334155"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00115E59"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F87171"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0034D399"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00D97706"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00A7F3D0"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -999,8 +1211,32 @@
         <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCFBF1"/>
+        <bgColor rgb="00CCFBF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+        <bgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="34">
+  <borders count="107">
     <border>
       <left/>
       <right/>
@@ -1362,6 +1598,737 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="medium">
+        <color rgb="00334155"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00065F46"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00065F46"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00065F46"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FCA5A5"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="0093C5FD"/>
+      </right>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -1373,7 +2340,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="292">
+  <cellXfs count="423">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2115,6 +3082,269 @@
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="56" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="18" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="105" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="18" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="18" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="18" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="106" fillId="18" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="108" fillId="18" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="106" fillId="18" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="18" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="18" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="18" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="18" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="18" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="112" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="7" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="7" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="56" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="81" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="114" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="56" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="81" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="118" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="37" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="7" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="120" fillId="7" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="121" fillId="7" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="122" fillId="7" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="18" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="129" fillId="17" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="124" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="18" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="124" fillId="18" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="130" fillId="17" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="125" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="17" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="127" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="131" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="132" fillId="12" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="66" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="137" fillId="11" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="74" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="75" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="76" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="77" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="133" fillId="18" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="134" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="18" borderId="76" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="138" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="123" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="135" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="135" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="12" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="11" borderId="78" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="79" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="80" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="111" fillId="18" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="123" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="87" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="88" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="97" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="90" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="92" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="101" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="103" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="93" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="94" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="105" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4090,7 +5320,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="70">
       <c r="A3" s="239" t="inlineStr">
         <is>
@@ -4355,7 +5584,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="16" customHeight="1" s="70">
       <c r="A26" s="242" t="inlineStr">
         <is>
@@ -4488,7 +5716,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
       <c r="A3" s="291" t="inlineStr">
         <is>
@@ -4525,7 +5752,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="70">
       <c r="A10" s="101" t="inlineStr">
         <is>
@@ -4535,7 +5761,6 @@
     </row>
     <row r="11" ht="15" customHeight="1" s="70"/>
     <row r="12" ht="15" customHeight="1" s="70"/>
-    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="70">
       <c r="A14" s="102" t="inlineStr">
         <is>
@@ -4596,7 +5821,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
       <c r="A3" s="291" t="inlineStr">
         <is>
@@ -4646,7 +5870,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="70">
       <c r="A11" s="106" t="inlineStr">
         <is>
@@ -4682,7 +5905,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="19.5" customHeight="1" s="70">
       <c r="A17" s="107" t="inlineStr">
         <is>
@@ -4740,7 +5962,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
       <c r="A3" s="291" t="inlineStr">
         <is>
@@ -13712,7 +14933,6 @@
       <c r="E1004" s="115" t="n"/>
       <c r="G1004" s="115" t="n"/>
     </row>
-    <row r="1005"/>
     <row r="1006" ht="19.5" customHeight="1" s="70">
       <c r="A1006" s="107" t="inlineStr">
         <is>
@@ -13800,7 +15020,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
       <c r="A3" s="291" t="inlineStr">
         <is>
@@ -23174,7 +24393,6 @@
       <c r="F1004" s="115" t="n"/>
       <c r="H1004" s="115" t="n"/>
     </row>
-    <row r="1005"/>
     <row r="1006" ht="19.5" customHeight="1" s="70">
       <c r="A1006" s="107" t="inlineStr">
         <is>
@@ -23263,7 +24481,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
       <c r="A3" s="291" t="inlineStr">
         <is>
@@ -23278,7 +24495,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="70">
       <c r="A6" s="122" t="inlineStr">
         <is>
@@ -23444,7 +24660,6 @@
         <v/>
       </c>
     </row>
-    <row r="21"/>
     <row r="22" ht="15" customHeight="1" s="70">
       <c r="H22" s="125" t="inlineStr">
         <is>
@@ -27098,7 +28313,6 @@
     <row r="1024" ht="15" customHeight="1" s="70">
       <c r="A1024" s="115" t="n"/>
     </row>
-    <row r="1025"/>
     <row r="1026" ht="19.5" customHeight="1" s="70">
       <c r="A1026" s="107" t="inlineStr">
         <is>
@@ -27181,7 +28395,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
       <c r="A3" s="291" t="inlineStr">
         <is>
@@ -27196,7 +28409,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="70">
       <c r="A6" s="127" t="inlineStr">
         <is>
@@ -27285,7 +28497,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="70">
       <c r="A15" s="126" t="inlineStr">
         <is>
@@ -27344,7 +28555,6 @@
         <v/>
       </c>
     </row>
-    <row r="21"/>
     <row r="22" ht="19.5" customHeight="1" s="70">
       <c r="A22" s="107" t="inlineStr">
         <is>
@@ -27438,7 +28648,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
       <c r="A3" s="291" t="inlineStr">
         <is>
@@ -27453,7 +28662,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="70">
       <c r="A6" s="127" t="inlineStr">
         <is>
@@ -27498,7 +28706,6 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="21" customHeight="1" s="70">
       <c r="A11" s="139" t="inlineStr">
         <is>
@@ -27521,7 +28728,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="70">
       <c r="A14" s="126" t="inlineStr">
         <is>
@@ -27562,7 +28768,6 @@
         <v/>
       </c>
     </row>
-    <row r="18"/>
     <row r="19" ht="19.5" customHeight="1" s="70">
       <c r="A19" s="107" t="inlineStr">
         <is>
@@ -27634,7 +28839,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
       <c r="A3" s="291" t="inlineStr">
         <is>
@@ -27649,7 +28853,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="70">
       <c r="A6" s="128" t="inlineStr">
         <is>
@@ -27729,7 +28932,6 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="70">
       <c r="A11" s="126" t="inlineStr">
         <is>
@@ -27781,7 +28983,6 @@
         <v/>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="15" customHeight="1" s="70">
       <c r="A17" s="122" t="inlineStr">
         <is>
@@ -27804,7 +29005,6 @@
         <v/>
       </c>
     </row>
-    <row r="19"/>
     <row r="20" ht="19.5" customHeight="1" s="70">
       <c r="A20" s="107" t="inlineStr">
         <is>
@@ -27869,7 +29069,6 @@
         <v/>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="17.25" customHeight="1" s="70">
       <c r="A4" s="126" t="inlineStr">
         <is>
@@ -27885,7 +29084,6 @@
         <v/>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="70">
       <c r="A6" s="127" t="inlineStr">
         <is>
@@ -27985,7 +29183,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="70">
       <c r="A16" s="146" t="inlineStr">
         <is>
@@ -28021,7 +29218,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22" ht="15" customHeight="1" s="70">
       <c r="A22" s="146" t="inlineStr">
         <is>
@@ -28047,7 +29243,6 @@
         <v/>
       </c>
     </row>
-    <row r="26"/>
     <row r="27" ht="15" customHeight="1" s="70">
       <c r="A27" s="153" t="inlineStr">
         <is>
@@ -28111,7 +29306,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
       <c r="A3" s="291" t="inlineStr">
         <is>
@@ -28824,985 +30018,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
-    <row r="501"/>
-    <row r="502"/>
-    <row r="503"/>
-    <row r="504"/>
-    <row r="505"/>
-    <row r="506"/>
-    <row r="507"/>
-    <row r="508"/>
-    <row r="509"/>
-    <row r="510"/>
-    <row r="511"/>
-    <row r="512"/>
-    <row r="513"/>
-    <row r="514"/>
-    <row r="515"/>
-    <row r="516"/>
-    <row r="517"/>
-    <row r="518"/>
-    <row r="519"/>
-    <row r="520"/>
-    <row r="521"/>
-    <row r="522"/>
-    <row r="523"/>
-    <row r="524"/>
-    <row r="525"/>
-    <row r="526"/>
-    <row r="527"/>
-    <row r="528"/>
-    <row r="529"/>
-    <row r="530"/>
-    <row r="531"/>
-    <row r="532"/>
-    <row r="533"/>
-    <row r="534"/>
-    <row r="535"/>
-    <row r="536"/>
-    <row r="537"/>
-    <row r="538"/>
-    <row r="539"/>
-    <row r="540"/>
-    <row r="541"/>
-    <row r="542"/>
-    <row r="543"/>
-    <row r="544"/>
-    <row r="545"/>
-    <row r="546"/>
-    <row r="547"/>
-    <row r="548"/>
-    <row r="549"/>
-    <row r="550"/>
-    <row r="551"/>
-    <row r="552"/>
-    <row r="553"/>
-    <row r="554"/>
-    <row r="555"/>
-    <row r="556"/>
-    <row r="557"/>
-    <row r="558"/>
-    <row r="559"/>
-    <row r="560"/>
-    <row r="561"/>
-    <row r="562"/>
-    <row r="563"/>
-    <row r="564"/>
-    <row r="565"/>
-    <row r="566"/>
-    <row r="567"/>
-    <row r="568"/>
-    <row r="569"/>
-    <row r="570"/>
-    <row r="571"/>
-    <row r="572"/>
-    <row r="573"/>
-    <row r="574"/>
-    <row r="575"/>
-    <row r="576"/>
-    <row r="577"/>
-    <row r="578"/>
-    <row r="579"/>
-    <row r="580"/>
-    <row r="581"/>
-    <row r="582"/>
-    <row r="583"/>
-    <row r="584"/>
-    <row r="585"/>
-    <row r="586"/>
-    <row r="587"/>
-    <row r="588"/>
-    <row r="589"/>
-    <row r="590"/>
-    <row r="591"/>
-    <row r="592"/>
-    <row r="593"/>
-    <row r="594"/>
-    <row r="595"/>
-    <row r="596"/>
-    <row r="597"/>
-    <row r="598"/>
-    <row r="599"/>
-    <row r="600"/>
-    <row r="601"/>
-    <row r="602"/>
-    <row r="603"/>
-    <row r="604"/>
-    <row r="605"/>
-    <row r="606"/>
-    <row r="607"/>
-    <row r="608"/>
-    <row r="609"/>
-    <row r="610"/>
-    <row r="611"/>
-    <row r="612"/>
-    <row r="613"/>
-    <row r="614"/>
-    <row r="615"/>
-    <row r="616"/>
-    <row r="617"/>
-    <row r="618"/>
-    <row r="619"/>
-    <row r="620"/>
-    <row r="621"/>
-    <row r="622"/>
-    <row r="623"/>
-    <row r="624"/>
-    <row r="625"/>
-    <row r="626"/>
-    <row r="627"/>
-    <row r="628"/>
-    <row r="629"/>
-    <row r="630"/>
-    <row r="631"/>
-    <row r="632"/>
-    <row r="633"/>
-    <row r="634"/>
-    <row r="635"/>
-    <row r="636"/>
-    <row r="637"/>
-    <row r="638"/>
-    <row r="639"/>
-    <row r="640"/>
-    <row r="641"/>
-    <row r="642"/>
-    <row r="643"/>
-    <row r="644"/>
-    <row r="645"/>
-    <row r="646"/>
-    <row r="647"/>
-    <row r="648"/>
-    <row r="649"/>
-    <row r="650"/>
-    <row r="651"/>
-    <row r="652"/>
-    <row r="653"/>
-    <row r="654"/>
-    <row r="655"/>
-    <row r="656"/>
-    <row r="657"/>
-    <row r="658"/>
-    <row r="659"/>
-    <row r="660"/>
-    <row r="661"/>
-    <row r="662"/>
-    <row r="663"/>
-    <row r="664"/>
-    <row r="665"/>
-    <row r="666"/>
-    <row r="667"/>
-    <row r="668"/>
-    <row r="669"/>
-    <row r="670"/>
-    <row r="671"/>
-    <row r="672"/>
-    <row r="673"/>
-    <row r="674"/>
-    <row r="675"/>
-    <row r="676"/>
-    <row r="677"/>
-    <row r="678"/>
-    <row r="679"/>
-    <row r="680"/>
-    <row r="681"/>
-    <row r="682"/>
-    <row r="683"/>
-    <row r="684"/>
-    <row r="685"/>
-    <row r="686"/>
-    <row r="687"/>
-    <row r="688"/>
-    <row r="689"/>
-    <row r="690"/>
-    <row r="691"/>
-    <row r="692"/>
-    <row r="693"/>
-    <row r="694"/>
-    <row r="695"/>
-    <row r="696"/>
-    <row r="697"/>
-    <row r="698"/>
-    <row r="699"/>
-    <row r="700"/>
-    <row r="701"/>
-    <row r="702"/>
-    <row r="703"/>
-    <row r="704"/>
-    <row r="705"/>
-    <row r="706"/>
-    <row r="707"/>
-    <row r="708"/>
-    <row r="709"/>
-    <row r="710"/>
-    <row r="711"/>
-    <row r="712"/>
-    <row r="713"/>
-    <row r="714"/>
-    <row r="715"/>
-    <row r="716"/>
-    <row r="717"/>
-    <row r="718"/>
-    <row r="719"/>
-    <row r="720"/>
-    <row r="721"/>
-    <row r="722"/>
-    <row r="723"/>
-    <row r="724"/>
-    <row r="725"/>
-    <row r="726"/>
-    <row r="727"/>
-    <row r="728"/>
-    <row r="729"/>
-    <row r="730"/>
-    <row r="731"/>
-    <row r="732"/>
-    <row r="733"/>
-    <row r="734"/>
-    <row r="735"/>
-    <row r="736"/>
-    <row r="737"/>
-    <row r="738"/>
-    <row r="739"/>
-    <row r="740"/>
-    <row r="741"/>
-    <row r="742"/>
-    <row r="743"/>
-    <row r="744"/>
-    <row r="745"/>
-    <row r="746"/>
-    <row r="747"/>
-    <row r="748"/>
-    <row r="749"/>
-    <row r="750"/>
-    <row r="751"/>
-    <row r="752"/>
-    <row r="753"/>
-    <row r="754"/>
-    <row r="755"/>
-    <row r="756"/>
-    <row r="757"/>
-    <row r="758"/>
-    <row r="759"/>
-    <row r="760"/>
-    <row r="761"/>
-    <row r="762"/>
-    <row r="763"/>
-    <row r="764"/>
-    <row r="765"/>
-    <row r="766"/>
-    <row r="767"/>
-    <row r="768"/>
-    <row r="769"/>
-    <row r="770"/>
-    <row r="771"/>
-    <row r="772"/>
-    <row r="773"/>
-    <row r="774"/>
-    <row r="775"/>
-    <row r="776"/>
-    <row r="777"/>
-    <row r="778"/>
-    <row r="779"/>
-    <row r="780"/>
-    <row r="781"/>
-    <row r="782"/>
-    <row r="783"/>
-    <row r="784"/>
-    <row r="785"/>
-    <row r="786"/>
-    <row r="787"/>
-    <row r="788"/>
-    <row r="789"/>
-    <row r="790"/>
-    <row r="791"/>
-    <row r="792"/>
-    <row r="793"/>
-    <row r="794"/>
-    <row r="795"/>
-    <row r="796"/>
-    <row r="797"/>
-    <row r="798"/>
-    <row r="799"/>
-    <row r="800"/>
-    <row r="801"/>
-    <row r="802"/>
-    <row r="803"/>
-    <row r="804"/>
-    <row r="805"/>
-    <row r="806"/>
-    <row r="807"/>
-    <row r="808"/>
-    <row r="809"/>
-    <row r="810"/>
-    <row r="811"/>
-    <row r="812"/>
-    <row r="813"/>
-    <row r="814"/>
-    <row r="815"/>
-    <row r="816"/>
-    <row r="817"/>
-    <row r="818"/>
-    <row r="819"/>
-    <row r="820"/>
-    <row r="821"/>
-    <row r="822"/>
-    <row r="823"/>
-    <row r="824"/>
-    <row r="825"/>
-    <row r="826"/>
-    <row r="827"/>
-    <row r="828"/>
-    <row r="829"/>
-    <row r="830"/>
-    <row r="831"/>
-    <row r="832"/>
-    <row r="833"/>
-    <row r="834"/>
-    <row r="835"/>
-    <row r="836"/>
-    <row r="837"/>
-    <row r="838"/>
-    <row r="839"/>
-    <row r="840"/>
-    <row r="841"/>
-    <row r="842"/>
-    <row r="843"/>
-    <row r="844"/>
-    <row r="845"/>
-    <row r="846"/>
-    <row r="847"/>
-    <row r="848"/>
-    <row r="849"/>
-    <row r="850"/>
-    <row r="851"/>
-    <row r="852"/>
-    <row r="853"/>
-    <row r="854"/>
-    <row r="855"/>
-    <row r="856"/>
-    <row r="857"/>
-    <row r="858"/>
-    <row r="859"/>
-    <row r="860"/>
-    <row r="861"/>
-    <row r="862"/>
-    <row r="863"/>
-    <row r="864"/>
-    <row r="865"/>
-    <row r="866"/>
-    <row r="867"/>
-    <row r="868"/>
-    <row r="869"/>
-    <row r="870"/>
-    <row r="871"/>
-    <row r="872"/>
-    <row r="873"/>
-    <row r="874"/>
-    <row r="875"/>
-    <row r="876"/>
-    <row r="877"/>
-    <row r="878"/>
-    <row r="879"/>
-    <row r="880"/>
-    <row r="881"/>
-    <row r="882"/>
-    <row r="883"/>
-    <row r="884"/>
-    <row r="885"/>
-    <row r="886"/>
-    <row r="887"/>
-    <row r="888"/>
-    <row r="889"/>
-    <row r="890"/>
-    <row r="891"/>
-    <row r="892"/>
-    <row r="893"/>
-    <row r="894"/>
-    <row r="895"/>
-    <row r="896"/>
-    <row r="897"/>
-    <row r="898"/>
-    <row r="899"/>
-    <row r="900"/>
-    <row r="901"/>
-    <row r="902"/>
-    <row r="903"/>
-    <row r="904"/>
-    <row r="905"/>
-    <row r="906"/>
-    <row r="907"/>
-    <row r="908"/>
-    <row r="909"/>
-    <row r="910"/>
-    <row r="911"/>
-    <row r="912"/>
-    <row r="913"/>
-    <row r="914"/>
-    <row r="915"/>
-    <row r="916"/>
-    <row r="917"/>
-    <row r="918"/>
-    <row r="919"/>
-    <row r="920"/>
-    <row r="921"/>
-    <row r="922"/>
-    <row r="923"/>
-    <row r="924"/>
-    <row r="925"/>
-    <row r="926"/>
-    <row r="927"/>
-    <row r="928"/>
-    <row r="929"/>
-    <row r="930"/>
-    <row r="931"/>
-    <row r="932"/>
-    <row r="933"/>
-    <row r="934"/>
-    <row r="935"/>
-    <row r="936"/>
-    <row r="937"/>
-    <row r="938"/>
-    <row r="939"/>
-    <row r="940"/>
-    <row r="941"/>
-    <row r="942"/>
-    <row r="943"/>
-    <row r="944"/>
-    <row r="945"/>
-    <row r="946"/>
-    <row r="947"/>
-    <row r="948"/>
-    <row r="949"/>
-    <row r="950"/>
-    <row r="951"/>
-    <row r="952"/>
-    <row r="953"/>
-    <row r="954"/>
-    <row r="955"/>
-    <row r="956"/>
-    <row r="957"/>
-    <row r="958"/>
-    <row r="959"/>
-    <row r="960"/>
-    <row r="961"/>
-    <row r="962"/>
-    <row r="963"/>
-    <row r="964"/>
-    <row r="965"/>
-    <row r="966"/>
-    <row r="967"/>
-    <row r="968"/>
-    <row r="969"/>
-    <row r="970"/>
-    <row r="971"/>
-    <row r="972"/>
-    <row r="973"/>
-    <row r="974"/>
-    <row r="975"/>
-    <row r="976"/>
-    <row r="977"/>
-    <row r="978"/>
-    <row r="979"/>
-    <row r="980"/>
-    <row r="981"/>
-    <row r="982"/>
-    <row r="983"/>
-    <row r="984"/>
-    <row r="985"/>
-    <row r="986"/>
-    <row r="987"/>
-    <row r="988"/>
-    <row r="989"/>
-    <row r="990"/>
-    <row r="991"/>
-    <row r="992"/>
-    <row r="993"/>
-    <row r="994"/>
-    <row r="995"/>
-    <row r="996"/>
-    <row r="997"/>
-    <row r="998"/>
-    <row r="999"/>
-    <row r="1000"/>
-    <row r="1001"/>
-    <row r="1002"/>
-    <row r="1003"/>
-    <row r="1004"/>
-    <row r="1005"/>
     <row r="1006" ht="19.5" customHeight="1" s="70">
       <c r="A1006" s="107" t="inlineStr">
         <is>
@@ -29837,578 +30052,623 @@
   <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" style="70" min="1" max="1"/>
-    <col width="62.5" customWidth="1" style="70" min="2" max="2"/>
-    <col width="15" customWidth="1" style="70" min="3" max="3"/>
-    <col width="15.5" customWidth="1" style="70" min="4" max="4"/>
-    <col width="36.5" customWidth="1" style="70" min="5" max="5"/>
-    <col width="18" customWidth="1" style="70" min="6" max="6"/>
-    <col width="11.5" customWidth="1" style="70" min="7" max="7"/>
-    <col width="75.5" customWidth="1" style="70" min="8" max="8"/>
-    <col width="15" customWidth="1" style="70" min="9" max="9"/>
-    <col width="15.5" customWidth="1" style="70" min="10" max="10"/>
-    <col width="81.5" customWidth="1" style="70" min="11" max="11"/>
-    <col width="18" customWidth="1" style="70" min="12" max="12"/>
-    <col width="18" customWidth="1" style="70" min="13" max="13"/>
-    <col width="13" customWidth="1" style="70" min="14" max="14"/>
+    <col width="12" customWidth="1" style="70" min="1" max="1"/>
+    <col width="17" customWidth="1" style="70" min="2" max="2"/>
+    <col width="12" customWidth="1" style="70" min="3" max="3"/>
+    <col width="11" customWidth="1" style="70" min="4" max="4"/>
+    <col width="17" customWidth="1" style="70" min="5" max="5"/>
+    <col width="12" customWidth="1" style="70" min="6" max="6"/>
+    <col width="11" customWidth="1" style="70" min="7" max="7"/>
+    <col width="17" customWidth="1" style="70" min="8" max="8"/>
+    <col width="13" customWidth="1" style="70" min="9" max="9"/>
+    <col width="11" customWidth="1" style="70" min="10" max="10"/>
+    <col width="17" customWidth="1" style="70" min="11" max="11"/>
+    <col width="14" customWidth="1" style="70" min="12" max="12"/>
+    <col width="12" customWidth="1" style="70" min="13" max="13"/>
+    <col width="6" customWidth="1" style="70" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="80" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="70">
+      <c r="A1" s="292" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="B2" s="161" t="inlineStr">
+    <row r="2" ht="28" customHeight="1" s="70">
+      <c r="B2" s="293" t="inlineStr">
         <is>
           <t>AYLIK PATRON FINANS PANELI</t>
         </is>
       </c>
-      <c r="L2" s="162" t="inlineStr">
+      <c r="L2" s="294" t="inlineStr">
         <is>
           <t>Dönem: 2026 / Tam ▼</t>
         </is>
       </c>
-      <c r="M2" s="163" t="inlineStr">
+      <c r="M2" s="295" t="inlineStr">
         <is>
           <t>★ DOĞRULANMIŞ</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="164" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="70">
+      <c r="B3" s="296" t="inlineStr">
         <is>
           <t>Hedef Kullanıcı: KOBİ sahipleri, patronlar, genel müdürler, finans yöneticileri, mali müşavirler · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="B5" s="165" t="inlineStr">
+    <row r="4" ht="10" customHeight="1" s="70"/>
+    <row r="5" ht="20" customHeight="1" s="70">
+      <c r="B5" s="297" t="inlineStr">
         <is>
           <t>TOPLAM İŞLEM HACMİ</t>
         </is>
       </c>
-      <c r="C5" s="166" t="n"/>
-      <c r="D5" s="167" t="inlineStr">
+      <c r="C5" s="298" t="n"/>
+      <c r="D5" s="299" t="inlineStr">
         <is>
           <t>KONSOLİDE</t>
         </is>
       </c>
-      <c r="E5" s="168" t="inlineStr">
+      <c r="E5" s="300" t="inlineStr">
         <is>
           <t>OPERASYONEL MALİYET</t>
         </is>
       </c>
-      <c r="F5" s="166" t="n"/>
-      <c r="G5" s="169" t="inlineStr">
+      <c r="F5" s="298" t="n"/>
+      <c r="G5" s="301" t="inlineStr">
         <is>
           <t>KONTROL</t>
         </is>
       </c>
-      <c r="H5" s="165" t="inlineStr">
+      <c r="H5" s="302" t="inlineStr">
         <is>
           <t>NET OPERASYONEL MARJ</t>
         </is>
       </c>
-      <c r="I5" s="166" t="n"/>
-      <c r="J5" s="170" t="inlineStr">
+      <c r="I5" s="298" t="n"/>
+      <c r="J5" s="303" t="inlineStr">
         <is>
           <t>GÜVENLİ</t>
         </is>
       </c>
-      <c r="K5" s="171" t="inlineStr">
+      <c r="K5" s="304" t="inlineStr">
         <is>
           <t>SİSTEM GÜVEN SKORU</t>
         </is>
       </c>
-      <c r="L5" s="166" t="n"/>
-      <c r="M5" s="167" t="inlineStr">
+      <c r="L5" s="298" t="n"/>
+      <c r="M5" s="305" t="inlineStr">
         <is>
           <t>DENETLENDİ</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="172" t="n"/>
-      <c r="C6" s="166" t="n"/>
-      <c r="D6" s="166" t="n"/>
-      <c r="E6" s="173" t="n"/>
-      <c r="F6" s="166" t="n"/>
-      <c r="G6" s="166" t="n"/>
-      <c r="H6" s="172" t="n"/>
-      <c r="I6" s="166" t="n"/>
-      <c r="J6" s="166" t="n"/>
-      <c r="K6" s="174" t="n"/>
-      <c r="L6" s="166" t="n"/>
-      <c r="M6" s="166" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="262">
+    <row r="6" ht="6" customHeight="1" s="70">
+      <c r="B6" s="306" t="n"/>
+      <c r="C6" s="307" t="n"/>
+      <c r="D6" s="308" t="n"/>
+      <c r="E6" s="309" t="n"/>
+      <c r="F6" s="307" t="n"/>
+      <c r="G6" s="308" t="n"/>
+      <c r="H6" s="310" t="n"/>
+      <c r="I6" s="307" t="n"/>
+      <c r="J6" s="308" t="n"/>
+      <c r="K6" s="311" t="n"/>
+      <c r="L6" s="307" t="n"/>
+      <c r="M6" s="308" t="n"/>
+    </row>
+    <row r="7" ht="32" customHeight="1" s="70">
+      <c r="B7" s="312">
         <f>GİRDİLER!E17</f>
         <v/>
       </c>
-      <c r="C7" s="166" t="n"/>
-      <c r="D7" s="166" t="n"/>
-      <c r="E7" s="263">
+      <c r="C7" s="307" t="n"/>
+      <c r="D7" s="308" t="n"/>
+      <c r="E7" s="313">
         <f>B7*0.22</f>
         <v/>
       </c>
-      <c r="F7" s="166" t="n"/>
-      <c r="G7" s="166" t="n"/>
-      <c r="H7" s="262">
+      <c r="F7" s="307" t="n"/>
+      <c r="G7" s="308" t="n"/>
+      <c r="H7" s="314">
         <f>B7-E7</f>
         <v/>
       </c>
-      <c r="I7" s="166" t="n"/>
-      <c r="J7" s="166" t="n"/>
-      <c r="K7" s="177">
+      <c r="I7" s="307" t="n"/>
+      <c r="J7" s="308" t="n"/>
+      <c r="K7" s="315">
         <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
-      <c r="L7" s="166" t="n"/>
-      <c r="M7" s="166" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="172" t="n"/>
-      <c r="C8" s="166" t="n"/>
-      <c r="D8" s="166" t="n"/>
-      <c r="E8" s="173" t="n"/>
-      <c r="F8" s="166" t="n"/>
-      <c r="G8" s="166" t="n"/>
-      <c r="H8" s="172" t="n"/>
-      <c r="I8" s="166" t="n"/>
-      <c r="J8" s="166" t="n"/>
-      <c r="K8" s="174" t="n"/>
-      <c r="L8" s="166" t="n"/>
-      <c r="M8" s="166" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="178" t="inlineStr">
+      <c r="L7" s="307" t="n"/>
+      <c r="M7" s="308" t="n"/>
+    </row>
+    <row r="8" ht="6" customHeight="1" s="70">
+      <c r="B8" s="306" t="n"/>
+      <c r="C8" s="307" t="n"/>
+      <c r="D8" s="308" t="n"/>
+      <c r="E8" s="309" t="n"/>
+      <c r="F8" s="307" t="n"/>
+      <c r="G8" s="308" t="n"/>
+      <c r="H8" s="310" t="n"/>
+      <c r="I8" s="307" t="n"/>
+      <c r="J8" s="308" t="n"/>
+      <c r="K8" s="311" t="n"/>
+      <c r="L8" s="307" t="n"/>
+      <c r="M8" s="308" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="70">
+      <c r="B9" s="316" t="inlineStr">
         <is>
           <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
-      <c r="C9" s="166" t="n"/>
-      <c r="D9" s="166" t="n"/>
-      <c r="E9" s="179" t="inlineStr">
+      <c r="C9" s="317" t="n"/>
+      <c r="D9" s="318" t="n"/>
+      <c r="E9" s="319" t="inlineStr">
         <is>
           <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
-      <c r="F9" s="166" t="n"/>
-      <c r="G9" s="166" t="n"/>
-      <c r="H9" s="178" t="inlineStr">
+      <c r="F9" s="317" t="n"/>
+      <c r="G9" s="318" t="n"/>
+      <c r="H9" s="320" t="inlineStr">
         <is>
           <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
-      <c r="I9" s="166" t="n"/>
-      <c r="J9" s="166" t="n"/>
-      <c r="K9" s="180" t="inlineStr">
+      <c r="I9" s="317" t="n"/>
+      <c r="J9" s="318" t="n"/>
+      <c r="K9" s="321" t="inlineStr">
         <is>
           <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
-      <c r="L9" s="166" t="n"/>
-      <c r="M9" s="166" t="n"/>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="B11" s="94" t="inlineStr">
+      <c r="L9" s="317" t="n"/>
+      <c r="M9" s="318" t="n"/>
+    </row>
+    <row r="10" ht="14" customHeight="1" s="70"/>
+    <row r="11" ht="24" customHeight="1" s="70">
+      <c r="B11" s="322" t="inlineStr">
         <is>
           <t>AYLIK PATRON FINANS PANELI — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
-      <c r="F11" s="181" t="inlineStr">
+      <c r="F11" s="323" t="inlineStr">
         <is>
           <t>+%32 Verim</t>
         </is>
       </c>
-      <c r="H11" s="94" t="inlineStr">
+      <c r="H11" s="322" t="inlineStr">
         <is>
           <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="93" t="inlineStr">
+    <row r="12" ht="18" customHeight="1" s="70">
+      <c r="B12" s="164" t="inlineStr">
         <is>
           <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
-      <c r="H12" s="93" t="inlineStr">
+      <c r="H12" s="164" t="inlineStr">
         <is>
           <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="182" t="inlineStr">
+    <row r="13" ht="8" customHeight="1" s="70"/>
+    <row r="14" ht="24" customHeight="1" s="70">
+      <c r="B14" s="324" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C14" s="182" t="inlineStr">
+      <c r="C14" s="324" t="inlineStr">
         <is>
           <t>Aktif Hacim</t>
         </is>
       </c>
-      <c r="D14" s="182" t="inlineStr">
+      <c r="D14" s="324" t="inlineStr">
         <is>
           <t>Maliyet/Yük</t>
         </is>
       </c>
-      <c r="E14" s="182" t="inlineStr">
+      <c r="E14" s="324" t="inlineStr">
         <is>
           <t>Hedef</t>
         </is>
       </c>
-      <c r="H14" s="183" t="inlineStr">
+      <c r="H14" s="325" t="inlineStr">
         <is>
           <t>PARAMETRE / KALEM</t>
         </is>
       </c>
-      <c r="I14" s="183" t="inlineStr">
+      <c r="I14" s="326" t="inlineStr">
         <is>
           <t>ANA TUTAR</t>
         </is>
       </c>
-      <c r="J14" s="183" t="inlineStr">
+      <c r="J14" s="326" t="inlineStr">
         <is>
           <t>FARK / MARJ</t>
         </is>
       </c>
-      <c r="K14" s="183" t="inlineStr">
+      <c r="K14" s="326" t="inlineStr">
         <is>
           <t>VADE</t>
         </is>
       </c>
-      <c r="L14" s="183" t="inlineStr">
+      <c r="L14" s="326" t="inlineStr">
         <is>
           <t>KONTROL DURUMU</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="93" t="inlineStr">
+      <c r="M14" s="326" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1" s="70">
+      <c r="B15" s="327" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C15" s="93" t="n">
+      <c r="C15" s="327" t="n">
         <v>65</v>
       </c>
-      <c r="D15" s="93" t="n">
+      <c r="D15" s="327" t="n">
         <v>45</v>
       </c>
-      <c r="E15" s="93" t="n">
+      <c r="E15" s="327" t="n">
         <v>60</v>
       </c>
-      <c r="H15" s="184" t="inlineStr">
+      <c r="H15" s="328" t="inlineStr">
         <is>
           <t>Dönemlik Kümülatif Bakiye</t>
         </is>
       </c>
-      <c r="I15" s="264">
+      <c r="I15" s="329">
         <f>B7*0.45</f>
         <v/>
       </c>
-      <c r="J15" s="265">
+      <c r="J15" s="330">
         <f>B7*0.05</f>
         <v/>
       </c>
-      <c r="K15" s="186" t="inlineStr">
+      <c r="K15" s="331" t="inlineStr">
         <is>
           <t>12 Ay</t>
         </is>
       </c>
-      <c r="L15" s="170" t="inlineStr">
+      <c r="L15" s="332" t="inlineStr">
         <is>
           <t>✓ DÜZENLİ</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="93" t="inlineStr">
+      <c r="M15" s="333" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1" s="70">
+      <c r="B16" s="334" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C16" s="93" t="n">
+      <c r="C16" s="334" t="n">
         <v>78</v>
       </c>
-      <c r="D16" s="93" t="n">
+      <c r="D16" s="334" t="n">
         <v>48</v>
       </c>
-      <c r="E16" s="93" t="n">
+      <c r="E16" s="334" t="n">
         <v>70</v>
       </c>
-      <c r="H16" s="184" t="inlineStr">
+      <c r="H16" s="335" t="inlineStr">
         <is>
           <t>Kritik Eşik Güvenlik Tamponu</t>
         </is>
       </c>
-      <c r="I16" s="264">
+      <c r="I16" s="336">
         <f>B7*0.30</f>
         <v/>
       </c>
-      <c r="J16" s="265">
+      <c r="J16" s="337">
         <f>B7*0.03</f>
         <v/>
       </c>
-      <c r="K16" s="186" t="inlineStr">
+      <c r="K16" s="338" t="inlineStr">
         <is>
           <t>24 Ay</t>
         </is>
       </c>
-      <c r="L16" s="167" t="inlineStr">
+      <c r="L16" s="339" t="inlineStr">
         <is>
           <t>★ AVANTAJ</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="93" t="inlineStr">
+      <c r="M16" s="340" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1" s="70">
+      <c r="B17" s="327" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C17" s="93" t="n">
+      <c r="C17" s="327" t="n">
         <v>85</v>
       </c>
-      <c r="D17" s="93" t="n">
+      <c r="D17" s="327" t="n">
         <v>55</v>
       </c>
-      <c r="E17" s="93" t="n">
+      <c r="E17" s="327" t="n">
         <v>80</v>
       </c>
-      <c r="H17" s="184" t="inlineStr">
+      <c r="H17" s="328" t="inlineStr">
         <is>
           <t>Operasyonel Net Fark</t>
         </is>
       </c>
-      <c r="I17" s="264">
+      <c r="I17" s="329">
         <f>B7*0.15</f>
         <v/>
       </c>
-      <c r="J17" s="265">
+      <c r="J17" s="330">
         <f>B7*0.02</f>
         <v/>
       </c>
-      <c r="K17" s="186" t="inlineStr">
+      <c r="K17" s="331" t="inlineStr">
         <is>
           <t>8 Ay</t>
         </is>
       </c>
-      <c r="L17" s="187" t="inlineStr">
+      <c r="L17" s="341" t="inlineStr">
         <is>
           <t>● YAKLAŞAN</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="93" t="inlineStr">
+      <c r="M17" s="333" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1" s="70">
+      <c r="B18" s="334" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C18" s="93" t="n">
+      <c r="C18" s="334" t="n">
         <v>75</v>
       </c>
-      <c r="D18" s="93" t="n">
+      <c r="D18" s="334" t="n">
         <v>42</v>
       </c>
-      <c r="E18" s="93" t="n">
+      <c r="E18" s="334" t="n">
         <v>75</v>
       </c>
-      <c r="H18" s="184" t="inlineStr">
+      <c r="H18" s="335" t="inlineStr">
         <is>
           <t>Rezerv ve Likit Dağılım</t>
         </is>
       </c>
-      <c r="I18" s="264">
+      <c r="I18" s="336">
         <f>B7*0.10</f>
         <v/>
       </c>
-      <c r="J18" s="265">
+      <c r="J18" s="337">
         <f>B7*0.01</f>
         <v/>
       </c>
-      <c r="K18" s="186" t="inlineStr">
+      <c r="K18" s="338" t="inlineStr">
         <is>
           <t>16 Ay</t>
         </is>
       </c>
-      <c r="L18" s="170" t="inlineStr">
+      <c r="L18" s="342" t="inlineStr">
         <is>
           <t>✓ TAM UYUM</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="93" t="inlineStr">
+      <c r="M18" s="340" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1" s="70">
+      <c r="B19" s="327" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="C19" s="93" t="n">
+      <c r="C19" s="327" t="n">
         <v>90</v>
       </c>
-      <c r="D19" s="93" t="n">
+      <c r="D19" s="327" t="n">
         <v>40</v>
       </c>
-      <c r="E19" s="93" t="n">
+      <c r="E19" s="327" t="n">
         <v>85</v>
       </c>
-      <c r="H19" s="188" t="inlineStr">
+      <c r="H19" s="343" t="inlineStr">
         <is>
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="266">
+      <c r="I19" s="344">
         <f>SUM(I15:I18)</f>
         <v/>
       </c>
-      <c r="J19" s="267">
+      <c r="J19" s="345">
         <f>SUM(J15:J18)</f>
         <v/>
       </c>
-      <c r="K19" s="191" t="inlineStr"/>
-      <c r="L19" s="192" t="inlineStr">
+      <c r="K19" s="346" t="inlineStr"/>
+      <c r="L19" s="347" t="inlineStr">
         <is>
           <t>TAM DOĞRULANDI (0 HATA)</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="93" t="inlineStr">
+      <c r="M19" s="347" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1" s="70">
+      <c r="B20" s="334" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="C20" s="93" t="n">
+      <c r="C20" s="334" t="n">
         <v>96</v>
       </c>
-      <c r="D20" s="93" t="n">
+      <c r="D20" s="334" t="n">
         <v>32</v>
       </c>
-      <c r="E20" s="93" t="n">
+      <c r="E20" s="334" t="n">
         <v>92</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="B22" s="193" t="inlineStr">
+    <row r="21" ht="14" customHeight="1" s="70"/>
+    <row r="22" ht="24" customHeight="1" s="70">
+      <c r="B22" s="348" t="inlineStr">
         <is>
           <t>KONSOLİDE PAY VE AĞIRLIK</t>
         </is>
       </c>
-      <c r="F22" s="193" t="inlineStr">
+      <c r="C22" s="298" t="n"/>
+      <c r="D22" s="298" t="n"/>
+      <c r="E22" s="349" t="n"/>
+      <c r="F22" s="348" t="inlineStr">
         <is>
           <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
         </is>
       </c>
-      <c r="K22" s="194" t="inlineStr">
+      <c r="G22" s="298" t="n"/>
+      <c r="H22" s="298" t="n"/>
+      <c r="I22" s="349" t="n"/>
+      <c r="K22" s="350" t="inlineStr">
         <is>
           <t>KARAR MOTORU</t>
         </is>
       </c>
-      <c r="L22" s="195" t="n"/>
-      <c r="M22" s="195" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="78" t="inlineStr">
+      <c r="L22" s="351" t="n"/>
+      <c r="M22" s="352" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1" s="70">
+      <c r="B23" s="353" t="inlineStr">
         <is>
           <t>■ Ana Segment (%42)</t>
         </is>
       </c>
-      <c r="F23" s="93" t="inlineStr">
+      <c r="C23" s="307" t="n"/>
+      <c r="D23" s="307" t="n"/>
+      <c r="E23" s="308" t="n"/>
+      <c r="F23" s="354" t="inlineStr">
         <is>
           <t>Nakit Açığı Riski (30 Gün)</t>
         </is>
       </c>
-      <c r="I23" s="196" t="inlineStr">
+      <c r="G23" s="307" t="n"/>
+      <c r="H23" s="307" t="n"/>
+      <c r="I23" s="355" t="inlineStr">
         <is>
           <t>0.00 TL (Sıfır Risk)</t>
         </is>
       </c>
-      <c r="K23" s="197" t="inlineStr">
-        <is>
-          <t>STRATEJİK VERİMLİLİK FIRSATI</t>
-        </is>
-      </c>
-      <c r="L23" s="195" t="n"/>
-      <c r="M23" s="195" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="79" t="inlineStr">
+      <c r="K23" s="356" t="inlineStr">
+        <is>
+          <t>LİKİDİTE OPTİMİZASYON FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="357" t="n"/>
+      <c r="M23" s="358" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1" s="70">
+      <c r="B24" s="359" t="inlineStr">
         <is>
           <t>■ İkincil Grup (%30)</t>
         </is>
       </c>
-      <c r="F24" s="93" t="inlineStr">
+      <c r="C24" s="307" t="n"/>
+      <c r="D24" s="307" t="n"/>
+      <c r="E24" s="308" t="n"/>
+      <c r="F24" s="354" t="inlineStr">
         <is>
           <t>Tahsilat Gecikme Toleransı</t>
         </is>
       </c>
-      <c r="I24" s="196" t="inlineStr">
+      <c r="G24" s="307" t="n"/>
+      <c r="H24" s="307" t="n"/>
+      <c r="I24" s="355" t="inlineStr">
         <is>
           <t>48 Gün Güvenli Eşik</t>
         </is>
       </c>
-      <c r="K24" s="198" t="inlineStr">
-        <is>
-          <t>Operasyonel süreç optimizasyonu ile kârlılık artış potansiyeli tespit edildi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="199" t="inlineStr">
+      <c r="K24" s="360" t="inlineStr">
+        <is>
+          <t>Atıl kalan nakit rezervinin gecelik repoda</t>
+        </is>
+      </c>
+      <c r="M24" s="402" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1" s="70">
+      <c r="B25" s="361" t="inlineStr">
         <is>
           <t>■ Destek Birimi (%15)</t>
         </is>
       </c>
-      <c r="F25" s="78" t="inlineStr">
+      <c r="C25" s="307" t="n"/>
+      <c r="D25" s="307" t="n"/>
+      <c r="E25" s="308" t="n"/>
+      <c r="F25" s="332" t="inlineStr">
         <is>
           <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="200" t="inlineStr">
+      <c r="G25" s="362" t="n"/>
+      <c r="H25" s="362" t="n"/>
+      <c r="I25" s="362" t="n"/>
+      <c r="K25" s="403" t="n"/>
+      <c r="M25" s="402" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1" s="70">
+      <c r="B26" s="364" t="inlineStr">
         <is>
           <t>■ Rezervler (%13)</t>
         </is>
       </c>
-      <c r="F26" s="201" t="inlineStr">
+      <c r="C26" s="307" t="n"/>
+      <c r="D26" s="307" t="n"/>
+      <c r="E26" s="308" t="n"/>
+      <c r="F26" s="365" t="inlineStr">
         <is>
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
       </c>
-      <c r="G26" s="274" t="n"/>
-      <c r="H26" s="274" t="n"/>
-      <c r="I26" s="275" t="n"/>
-      <c r="K26" s="202" t="inlineStr">
-        <is>
-          <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="F27" s="276" t="n"/>
-      <c r="G27" s="277" t="n"/>
-      <c r="H27" s="277" t="n"/>
-      <c r="I27" s="278" t="n"/>
+      <c r="G26" s="404" t="n"/>
+      <c r="H26" s="404" t="n"/>
+      <c r="I26" s="405" t="n"/>
+      <c r="K26" s="367" t="inlineStr">
+        <is>
+          <t>FONLAMA SENARYOSUNU İNCELE ›</t>
+        </is>
+      </c>
+      <c r="L26" s="404" t="n"/>
+      <c r="M26" s="405" t="n"/>
+    </row>
+    <row r="27" ht="26" customHeight="1" s="70">
+      <c r="B27" s="368" t="n"/>
+      <c r="C27" s="317" t="n"/>
+      <c r="D27" s="317" t="n"/>
+      <c r="E27" s="318" t="n"/>
+      <c r="F27" s="406" t="n"/>
+      <c r="G27" s="407" t="n"/>
+      <c r="H27" s="407" t="n"/>
+      <c r="I27" s="408" t="n"/>
+      <c r="K27" s="406" t="n"/>
+      <c r="L27" s="407" t="n"/>
+      <c r="M27" s="408" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="K26:M27"/>
+  <mergeCells count="5">
     <mergeCell ref="K24:M25"/>
     <mergeCell ref="F26:I27"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="B3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30442,7 +30702,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="70">
       <c r="A3" s="96" t="inlineStr">
         <is>
@@ -30544,7 +30803,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="70">
       <c r="A3" s="96" t="inlineStr">
         <is>
@@ -30678,7 +30936,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="70">
       <c r="A3" s="96" t="inlineStr">
         <is>
@@ -30786,7 +31043,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
       <c r="A3" s="291" t="inlineStr">
         <is>
@@ -30888,7 +31144,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="70">
       <c r="A3" s="126" t="inlineStr">
         <is>
@@ -31083,7 +31338,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
       <c r="A3" s="291" t="inlineStr">
         <is>
@@ -31098,7 +31352,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1" s="70">
       <c r="A6" s="111" t="inlineStr">
         <is>
@@ -32723,7 +32976,6 @@
         </is>
       </c>
     </row>
-    <row r="52"/>
     <row r="53" ht="15" customHeight="1" s="70">
       <c r="B53" s="160" t="inlineStr">
         <is>
@@ -32773,7 +33025,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="70">
       <c r="A3" s="291" t="inlineStr">
         <is>
@@ -32837,16 +33088,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22" ht="15" customHeight="1" s="70">
       <c r="A22" s="126" t="inlineStr">
         <is>
@@ -32889,7 +33130,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29" ht="15" customHeight="1" s="70">
       <c r="A29" s="126" t="inlineStr">
         <is>
@@ -32904,7 +33144,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32" ht="15" customHeight="1" s="70">
       <c r="A32" s="126" t="inlineStr">
         <is>
@@ -32940,7 +33179,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38" ht="19.5" customHeight="1" s="70">
       <c r="A38" s="107" t="inlineStr">
         <is>
@@ -33007,7 +33245,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="B3" s="203" t="inlineStr">
         <is>
@@ -33028,7 +33265,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="206" t="inlineStr">
         <is>
@@ -33441,7 +33677,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="B17" s="223" t="inlineStr">
         <is>
@@ -33472,311 +33707,427 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" style="70" min="1" max="1"/>
+    <col width="12" customWidth="1" style="70" min="1" max="1"/>
     <col width="24" customWidth="1" style="70" min="2" max="2"/>
-    <col width="15" customWidth="1" style="70" min="3" max="3"/>
-    <col width="15" customWidth="1" style="70" min="4" max="4"/>
-    <col width="22" customWidth="1" style="70" min="5" max="5"/>
-    <col width="6" customWidth="1" style="70" min="6" max="6"/>
+    <col width="14" customWidth="1" style="70" min="3" max="3"/>
+    <col width="14" customWidth="1" style="70" min="4" max="4"/>
+    <col width="16" customWidth="1" style="70" min="5" max="5"/>
+    <col width="14" customWidth="1" style="70" min="6" max="6"/>
     <col width="6" customWidth="1" style="70" min="7" max="7"/>
     <col width="24" customWidth="1" style="70" min="8" max="8"/>
-    <col width="15" customWidth="1" style="70" min="9" max="9"/>
-    <col width="15" customWidth="1" style="70" min="10" max="10"/>
-    <col width="22" customWidth="1" style="70" min="11" max="11"/>
-    <col width="6" customWidth="1" style="70" min="12" max="12"/>
+    <col width="14" customWidth="1" style="70" min="9" max="9"/>
+    <col width="14" customWidth="1" style="70" min="10" max="10"/>
+    <col width="16" customWidth="1" style="70" min="11" max="11"/>
+    <col width="14" customWidth="1" style="70" min="12" max="12"/>
+    <col width="6" customWidth="1" style="70" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="80" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="70">
+      <c r="A1" s="292" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28" customHeight="1" s="70">
       <c r="B2" s="225" t="inlineStr">
         <is>
           <t>AYLIK PATRON FINANS PANELI — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="226" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="70">
+      <c r="B3" s="372" t="inlineStr">
         <is>
           <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · KOBİ sahipleri, patronlar, genel müdürler, finans yöneticileri, mali müşavirler</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="227" t="inlineStr">
+    <row r="4" ht="20" customHeight="1" s="70">
+      <c r="B4" s="373" t="inlineStr">
         <is>
           <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="B6" s="228" t="inlineStr">
+    <row r="5" ht="12" customHeight="1" s="70"/>
+    <row r="6" ht="26" customHeight="1" s="70">
+      <c r="B6" s="374" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
       </c>
-      <c r="C6" s="279" t="n"/>
-      <c r="D6" s="279" t="n"/>
-      <c r="E6" s="279" t="n"/>
-      <c r="F6" s="280" t="n"/>
-      <c r="H6" s="229" t="inlineStr">
+      <c r="C6" s="409" t="n"/>
+      <c r="D6" s="409" t="n"/>
+      <c r="E6" s="409" t="n"/>
+      <c r="F6" s="410" t="n"/>
+      <c r="H6" s="377" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
       </c>
-      <c r="I6" s="279" t="n"/>
-      <c r="J6" s="279" t="n"/>
-      <c r="K6" s="279" t="n"/>
-      <c r="L6" s="280" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="166" t="n"/>
-      <c r="C7" s="166" t="n"/>
-      <c r="D7" s="166" t="n"/>
-      <c r="E7" s="166" t="n"/>
-      <c r="F7" s="166" t="n"/>
-      <c r="H7" s="166" t="n"/>
-      <c r="I7" s="166" t="n"/>
-      <c r="J7" s="166" t="n"/>
-      <c r="K7" s="166" t="n"/>
-      <c r="L7" s="166" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="230" t="inlineStr">
+      <c r="I6" s="411" t="n"/>
+      <c r="J6" s="411" t="n"/>
+      <c r="K6" s="411" t="n"/>
+      <c r="L6" s="412" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1" s="70">
+      <c r="B7" s="380" t="n"/>
+      <c r="C7" s="307" t="n"/>
+      <c r="D7" s="307" t="n"/>
+      <c r="E7" s="307" t="n"/>
+      <c r="F7" s="381" t="n"/>
+      <c r="H7" s="382" t="n"/>
+      <c r="I7" s="307" t="n"/>
+      <c r="J7" s="307" t="n"/>
+      <c r="K7" s="307" t="n"/>
+      <c r="L7" s="383" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1" s="70">
+      <c r="B8" s="384" t="inlineStr">
         <is>
           <t>Ciro / Hacim Düşüşü:</t>
         </is>
       </c>
-      <c r="C8" s="166" t="n"/>
-      <c r="D8" s="166" t="n"/>
-      <c r="E8" s="231" t="inlineStr">
+      <c r="C8" s="307" t="n"/>
+      <c r="D8" s="307" t="n"/>
+      <c r="E8" s="385" t="inlineStr">
         <is>
           <t>-%20.0 (Kriz Eşiği)</t>
         </is>
       </c>
-      <c r="F8" s="166" t="n"/>
-      <c r="H8" s="230" t="inlineStr">
+      <c r="F8" s="381" t="n"/>
+      <c r="H8" s="386" t="inlineStr">
         <is>
           <t>Ciro / Hacim Gerçekleşmesi:</t>
         </is>
       </c>
-      <c r="I8" s="166" t="n"/>
-      <c r="J8" s="166" t="n"/>
-      <c r="K8" s="232" t="inlineStr">
+      <c r="I8" s="307" t="n"/>
+      <c r="J8" s="307" t="n"/>
+      <c r="K8" s="387" t="inlineStr">
         <is>
           <t>%100.0 (Tam Bütçe)</t>
         </is>
       </c>
-      <c r="L8" s="166" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="230" t="inlineStr">
+      <c r="L8" s="383" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1" s="70">
+      <c r="B9" s="384" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="C9" s="166" t="n"/>
-      <c r="D9" s="166" t="n"/>
-      <c r="E9" s="269">
+      <c r="C9" s="307" t="n"/>
+      <c r="D9" s="307" t="n"/>
+      <c r="E9" s="388">
         <f>PANO!B7*0.8*0.22</f>
         <v/>
       </c>
-      <c r="F9" s="166" t="n"/>
-      <c r="H9" s="230" t="inlineStr">
+      <c r="F9" s="381" t="n"/>
+      <c r="H9" s="386" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="I9" s="166" t="n"/>
-      <c r="J9" s="166" t="n"/>
-      <c r="K9" s="269">
+      <c r="I9" s="307" t="n"/>
+      <c r="J9" s="307" t="n"/>
+      <c r="K9" s="388">
         <f>PANO!H7</f>
         <v/>
       </c>
-      <c r="L9" s="166" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="230" t="inlineStr">
+      <c r="L9" s="383" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1" s="70">
+      <c r="B10" s="384" t="inlineStr">
         <is>
           <t>Minimum Nakit Tamponu:</t>
         </is>
       </c>
-      <c r="C10" s="166" t="n"/>
-      <c r="D10" s="166" t="n"/>
-      <c r="E10" s="270">
+      <c r="C10" s="307" t="n"/>
+      <c r="D10" s="307" t="n"/>
+      <c r="E10" s="389">
         <f>PANO!E7*0.75</f>
         <v/>
       </c>
-      <c r="F10" s="166" t="n"/>
-      <c r="H10" s="230" t="inlineStr">
+      <c r="F10" s="381" t="n"/>
+      <c r="H10" s="386" t="inlineStr">
         <is>
           <t>Serbest Nakit Akımı:</t>
         </is>
       </c>
-      <c r="I10" s="166" t="n"/>
-      <c r="J10" s="166" t="n"/>
-      <c r="K10" s="270">
+      <c r="I10" s="307" t="n"/>
+      <c r="J10" s="307" t="n"/>
+      <c r="K10" s="389">
         <f>PANO!H7*0.75</f>
         <v/>
       </c>
-      <c r="L10" s="166" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="230" t="inlineStr">
+      <c r="L10" s="383" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1" s="70">
+      <c r="B11" s="384" t="inlineStr">
         <is>
           <t>Likidite Karşılama Oranı:</t>
         </is>
       </c>
-      <c r="C11" s="166" t="n"/>
-      <c r="D11" s="166" t="n"/>
-      <c r="E11" s="271">
+      <c r="C11" s="307" t="n"/>
+      <c r="D11" s="307" t="n"/>
+      <c r="E11" s="390">
         <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
-      <c r="F11" s="166" t="n"/>
-      <c r="H11" s="230" t="inlineStr">
+      <c r="F11" s="381" t="n"/>
+      <c r="H11" s="386" t="inlineStr">
         <is>
           <t>Yatırım Geri Dönüşü (ROI):</t>
         </is>
       </c>
-      <c r="I11" s="166" t="n"/>
-      <c r="J11" s="166" t="n"/>
-      <c r="K11" s="234" t="inlineStr">
+      <c r="I11" s="307" t="n"/>
+      <c r="J11" s="307" t="n"/>
+      <c r="K11" s="391" t="inlineStr">
         <is>
           <t>%38.4 Yıllık</t>
         </is>
       </c>
-      <c r="L11" s="166" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="166" t="n"/>
-      <c r="C12" s="166" t="n"/>
-      <c r="D12" s="166" t="n"/>
-      <c r="E12" s="166" t="n"/>
-      <c r="F12" s="166" t="n"/>
-      <c r="H12" s="166" t="n"/>
-      <c r="I12" s="166" t="n"/>
-      <c r="J12" s="166" t="n"/>
-      <c r="K12" s="166" t="n"/>
-      <c r="L12" s="166" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="166" t="n"/>
-      <c r="C13" s="166" t="n"/>
-      <c r="D13" s="166" t="n"/>
-      <c r="E13" s="166" t="n"/>
-      <c r="F13" s="166" t="n"/>
-      <c r="H13" s="166" t="n"/>
-      <c r="I13" s="166" t="n"/>
-      <c r="J13" s="166" t="n"/>
-      <c r="K13" s="166" t="n"/>
-      <c r="L13" s="166" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="235" t="inlineStr">
+      <c r="L11" s="383" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1" s="70">
+      <c r="B12" s="380" t="n"/>
+      <c r="C12" s="307" t="n"/>
+      <c r="D12" s="307" t="n"/>
+      <c r="E12" s="307" t="n"/>
+      <c r="F12" s="381" t="n"/>
+      <c r="H12" s="382" t="n"/>
+      <c r="I12" s="307" t="n"/>
+      <c r="J12" s="307" t="n"/>
+      <c r="K12" s="307" t="n"/>
+      <c r="L12" s="383" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1" s="70">
+      <c r="B13" s="380" t="n"/>
+      <c r="C13" s="307" t="n"/>
+      <c r="D13" s="307" t="n"/>
+      <c r="E13" s="307" t="n"/>
+      <c r="F13" s="381" t="n"/>
+      <c r="H13" s="382" t="n"/>
+      <c r="I13" s="307" t="n"/>
+      <c r="J13" s="307" t="n"/>
+      <c r="K13" s="307" t="n"/>
+      <c r="L13" s="383" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1" s="70">
+      <c r="B14" s="392" t="inlineStr">
         <is>
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
       </c>
-      <c r="C14" s="281" t="n"/>
-      <c r="D14" s="281" t="n"/>
-      <c r="E14" s="281" t="n"/>
-      <c r="F14" s="282" t="n"/>
-      <c r="H14" s="236" t="inlineStr">
+      <c r="C14" s="413" t="n"/>
+      <c r="D14" s="413" t="n"/>
+      <c r="E14" s="413" t="n"/>
+      <c r="F14" s="414" t="n"/>
+      <c r="H14" s="395" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
       </c>
-      <c r="I14" s="283" t="n"/>
-      <c r="J14" s="283" t="n"/>
-      <c r="K14" s="283" t="n"/>
-      <c r="L14" s="284" t="n"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="285" t="n"/>
-      <c r="C15" s="286" t="n"/>
-      <c r="D15" s="286" t="n"/>
-      <c r="E15" s="286" t="n"/>
-      <c r="F15" s="287" t="n"/>
-      <c r="H15" s="288" t="n"/>
-      <c r="I15" s="289" t="n"/>
-      <c r="J15" s="289" t="n"/>
-      <c r="K15" s="289" t="n"/>
-      <c r="L15" s="290" t="n"/>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="81" t="inlineStr">
+      <c r="I14" s="415" t="n"/>
+      <c r="J14" s="415" t="n"/>
+      <c r="K14" s="415" t="n"/>
+      <c r="L14" s="416" t="n"/>
+    </row>
+    <row r="15" ht="14" customHeight="1" s="70">
+      <c r="B15" s="417" t="n"/>
+      <c r="C15" s="418" t="n"/>
+      <c r="D15" s="418" t="n"/>
+      <c r="E15" s="418" t="n"/>
+      <c r="F15" s="419" t="n"/>
+      <c r="H15" s="420" t="n"/>
+      <c r="I15" s="421" t="n"/>
+      <c r="J15" s="421" t="n"/>
+      <c r="K15" s="421" t="n"/>
+      <c r="L15" s="422" t="n"/>
+    </row>
+    <row r="16" ht="10" customHeight="1" s="70"/>
+    <row r="17" ht="26" customHeight="1" s="70">
+      <c r="B17" s="398" t="inlineStr">
         <is>
           <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
         </is>
       </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="193" t="inlineStr">
+      <c r="C17" s="298" t="n"/>
+      <c r="D17" s="298" t="n"/>
+      <c r="E17" s="298" t="n"/>
+      <c r="F17" s="298" t="n"/>
+      <c r="G17" s="298" t="n"/>
+      <c r="H17" s="298" t="n"/>
+      <c r="I17" s="298" t="n"/>
+      <c r="J17" s="298" t="n"/>
+      <c r="K17" s="298" t="n"/>
+      <c r="L17" s="349" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1" s="70">
+      <c r="B18" s="399" t="n"/>
+      <c r="C18" s="307" t="n"/>
+      <c r="D18" s="307" t="n"/>
+      <c r="E18" s="307" t="n"/>
+      <c r="F18" s="307" t="n"/>
+      <c r="G18" s="307" t="n"/>
+      <c r="H18" s="307" t="n"/>
+      <c r="I18" s="307" t="n"/>
+      <c r="J18" s="307" t="n"/>
+      <c r="K18" s="307" t="n"/>
+      <c r="L18" s="308" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1" s="70">
+      <c r="B19" s="400" t="inlineStr">
         <is>
           <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="237" t="inlineStr">
+      <c r="C19" s="307" t="n"/>
+      <c r="D19" s="307" t="n"/>
+      <c r="E19" s="307" t="n"/>
+      <c r="F19" s="307" t="n"/>
+      <c r="G19" s="307" t="n"/>
+      <c r="H19" s="307" t="n"/>
+      <c r="I19" s="307" t="n"/>
+      <c r="J19" s="307" t="n"/>
+      <c r="K19" s="307" t="n"/>
+      <c r="L19" s="308" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1" s="70">
+      <c r="B20" s="401" t="inlineStr">
         <is>
           <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="193" t="inlineStr">
+      <c r="C20" s="307" t="n"/>
+      <c r="D20" s="307" t="n"/>
+      <c r="E20" s="307" t="n"/>
+      <c r="F20" s="307" t="n"/>
+      <c r="G20" s="307" t="n"/>
+      <c r="H20" s="307" t="n"/>
+      <c r="I20" s="307" t="n"/>
+      <c r="J20" s="307" t="n"/>
+      <c r="K20" s="307" t="n"/>
+      <c r="L20" s="308" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1" s="70">
+      <c r="B21" s="400" t="inlineStr">
         <is>
           <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="237" t="inlineStr">
+      <c r="C21" s="307" t="n"/>
+      <c r="D21" s="307" t="n"/>
+      <c r="E21" s="307" t="n"/>
+      <c r="F21" s="307" t="n"/>
+      <c r="G21" s="307" t="n"/>
+      <c r="H21" s="307" t="n"/>
+      <c r="I21" s="307" t="n"/>
+      <c r="J21" s="307" t="n"/>
+      <c r="K21" s="307" t="n"/>
+      <c r="L21" s="308" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1" s="70">
+      <c r="B22" s="401" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="193" t="inlineStr">
+      <c r="C22" s="307" t="n"/>
+      <c r="D22" s="307" t="n"/>
+      <c r="E22" s="307" t="n"/>
+      <c r="F22" s="307" t="n"/>
+      <c r="G22" s="307" t="n"/>
+      <c r="H22" s="307" t="n"/>
+      <c r="I22" s="307" t="n"/>
+      <c r="J22" s="307" t="n"/>
+      <c r="K22" s="307" t="n"/>
+      <c r="L22" s="308" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1" s="70">
+      <c r="B23" s="400" t="inlineStr">
         <is>
           <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="237" t="inlineStr">
+      <c r="C23" s="307" t="n"/>
+      <c r="D23" s="307" t="n"/>
+      <c r="E23" s="307" t="n"/>
+      <c r="F23" s="307" t="n"/>
+      <c r="G23" s="307" t="n"/>
+      <c r="H23" s="307" t="n"/>
+      <c r="I23" s="307" t="n"/>
+      <c r="J23" s="307" t="n"/>
+      <c r="K23" s="307" t="n"/>
+      <c r="L23" s="308" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1" s="70">
+      <c r="B24" s="401" t="inlineStr">
         <is>
           <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="193" t="inlineStr">
+      <c r="C24" s="307" t="n"/>
+      <c r="D24" s="307" t="n"/>
+      <c r="E24" s="307" t="n"/>
+      <c r="F24" s="307" t="n"/>
+      <c r="G24" s="307" t="n"/>
+      <c r="H24" s="307" t="n"/>
+      <c r="I24" s="307" t="n"/>
+      <c r="J24" s="307" t="n"/>
+      <c r="K24" s="307" t="n"/>
+      <c r="L24" s="308" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1" s="70">
+      <c r="B25" s="400" t="inlineStr">
         <is>
           <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="237" t="inlineStr">
+      <c r="C25" s="307" t="n"/>
+      <c r="D25" s="307" t="n"/>
+      <c r="E25" s="307" t="n"/>
+      <c r="F25" s="307" t="n"/>
+      <c r="G25" s="307" t="n"/>
+      <c r="H25" s="307" t="n"/>
+      <c r="I25" s="307" t="n"/>
+      <c r="J25" s="307" t="n"/>
+      <c r="K25" s="307" t="n"/>
+      <c r="L25" s="308" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1" s="70">
+      <c r="B26" s="401" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
+      <c r="C26" s="307" t="n"/>
+      <c r="D26" s="307" t="n"/>
+      <c r="E26" s="307" t="n"/>
+      <c r="F26" s="307" t="n"/>
+      <c r="G26" s="307" t="n"/>
+      <c r="H26" s="307" t="n"/>
+      <c r="I26" s="307" t="n"/>
+      <c r="J26" s="307" t="n"/>
+      <c r="K26" s="307" t="n"/>
+      <c r="L26" s="308" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1" s="70">
+      <c r="B27" s="368" t="n"/>
+      <c r="C27" s="317" t="n"/>
+      <c r="D27" s="317" t="n"/>
+      <c r="E27" s="317" t="n"/>
+      <c r="F27" s="317" t="n"/>
+      <c r="G27" s="317" t="n"/>
+      <c r="H27" s="317" t="n"/>
+      <c r="I27" s="317" t="n"/>
+      <c r="J27" s="317" t="n"/>
+      <c r="K27" s="317" t="n"/>
+      <c r="L27" s="318" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -33818,7 +34169,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="70">
       <c r="A3" s="244" t="inlineStr">
         <is>
@@ -34313,7 +34663,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="70">
       <c r="A3" s="247" t="inlineStr">
         <is>
@@ -35060,7 +35409,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="70">
       <c r="A3" s="252" t="inlineStr">
         <is>
@@ -35738,7 +36086,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="70">
       <c r="A3" s="256" t="inlineStr">
         <is>
@@ -36288,7 +36635,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="70">
       <c r="A3" s="259" t="inlineStr">
         <is>
